--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MR_Rank</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Conf</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>N_games</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MR_Score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Exp_Wins_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Elo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>POM</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>

--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -510,7 +510,7 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3283</v>
+        <v>3.3286</v>
       </c>
       <c r="I2" t="n">
         <v>95.09</v>
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2213</v>
+        <v>3.2216</v>
       </c>
       <c r="I3" t="n">
         <v>92.56999999999999</v>
@@ -600,7 +600,7 @@
         <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1234</v>
+        <v>3.1237</v>
       </c>
       <c r="I4" t="n">
         <v>91.51000000000001</v>
@@ -645,7 +645,7 @@
         <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>3.097</v>
+        <v>3.0973</v>
       </c>
       <c r="I5" t="n">
         <v>92.8</v>
@@ -690,10 +690,10 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0281</v>
+        <v>3.0286</v>
       </c>
       <c r="I6" t="n">
-        <v>91.56999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="J6" t="n">
         <v>2102.9</v>
@@ -735,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9857</v>
+        <v>2.9859</v>
       </c>
       <c r="I7" t="n">
         <v>91.20999999999999</v>
@@ -780,7 +780,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8733</v>
+        <v>2.8736</v>
       </c>
       <c r="I8" t="n">
         <v>90.11</v>
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8555</v>
+        <v>2.8557</v>
       </c>
       <c r="I9" t="n">
         <v>89.23999999999999</v>
@@ -870,7 +870,7 @@
         <v>23</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8495</v>
+        <v>2.8498</v>
       </c>
       <c r="I10" t="n">
         <v>88.68000000000001</v>
@@ -915,7 +915,7 @@
         <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8217</v>
+        <v>2.822</v>
       </c>
       <c r="I11" t="n">
         <v>90.41</v>
@@ -960,7 +960,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>2.722</v>
+        <v>2.7222</v>
       </c>
       <c r="I12" t="n">
         <v>84.92</v>
@@ -1005,7 +1005,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7003</v>
+        <v>2.7006</v>
       </c>
       <c r="I13" t="n">
         <v>87.01000000000001</v>
@@ -1050,7 +1050,7 @@
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6984</v>
+        <v>2.6986</v>
       </c>
       <c r="I14" t="n">
         <v>87.73999999999999</v>
@@ -1095,7 +1095,7 @@
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6147</v>
+        <v>2.6146</v>
       </c>
       <c r="I15" t="n">
         <v>87.27</v>
@@ -1140,7 +1140,7 @@
         <v>23</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5936</v>
+        <v>2.5938</v>
       </c>
       <c r="I16" t="n">
         <v>87.05</v>
@@ -1185,7 +1185,7 @@
         <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>2.562</v>
+        <v>2.5622</v>
       </c>
       <c r="I17" t="n">
         <v>86.45</v>
@@ -1230,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5396</v>
+        <v>2.5398</v>
       </c>
       <c r="I18" t="n">
         <v>86.69</v>
@@ -1275,7 +1275,7 @@
         <v>24</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5329</v>
+        <v>2.5331</v>
       </c>
       <c r="I19" t="n">
         <v>83.64</v>
@@ -1320,7 +1320,7 @@
         <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5199</v>
+        <v>2.5201</v>
       </c>
       <c r="I20" t="n">
         <v>87.28</v>
@@ -1365,7 +1365,7 @@
         <v>22</v>
       </c>
       <c r="H21" t="n">
-        <v>2.498</v>
+        <v>2.4982</v>
       </c>
       <c r="I21" t="n">
         <v>86.63</v>
@@ -1410,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4847</v>
+        <v>2.4849</v>
       </c>
       <c r="I22" t="n">
         <v>85.29000000000001</v>
@@ -1455,10 +1455,10 @@
         <v>24</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4482</v>
+        <v>2.4484</v>
       </c>
       <c r="I23" t="n">
-        <v>82.79000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="J23" t="n">
         <v>1924.5</v>
@@ -1500,7 +1500,7 @@
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4002</v>
+        <v>2.4004</v>
       </c>
       <c r="I24" t="n">
         <v>82.5</v>
@@ -1545,7 +1545,7 @@
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3919</v>
+        <v>2.392</v>
       </c>
       <c r="I25" t="n">
         <v>84.53</v>
@@ -1590,10 +1590,10 @@
         <v>22</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3712</v>
+        <v>2.3715</v>
       </c>
       <c r="I26" t="n">
-        <v>83.55</v>
+        <v>83.56</v>
       </c>
       <c r="J26" t="n">
         <v>1851.2</v>
@@ -1635,7 +1635,7 @@
         <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3285</v>
+        <v>2.3287</v>
       </c>
       <c r="I27" t="n">
         <v>82.44</v>
@@ -1680,7 +1680,7 @@
         <v>23</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3048</v>
+        <v>2.305</v>
       </c>
       <c r="I28" t="n">
         <v>82.58</v>
@@ -1725,7 +1725,7 @@
         <v>24</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3032</v>
+        <v>2.3033</v>
       </c>
       <c r="I29" t="n">
         <v>84.2</v>
@@ -1770,10 +1770,10 @@
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2964</v>
+        <v>2.2966</v>
       </c>
       <c r="I30" t="n">
-        <v>82.97</v>
+        <v>82.98</v>
       </c>
       <c r="J30" t="n">
         <v>1816.9</v>
@@ -1815,7 +1815,7 @@
         <v>24</v>
       </c>
       <c r="H31" t="n">
-        <v>2.255</v>
+        <v>2.2552</v>
       </c>
       <c r="I31" t="n">
         <v>83.2</v>
@@ -1860,7 +1860,7 @@
         <v>23</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2178</v>
+        <v>2.2179</v>
       </c>
       <c r="I32" t="n">
         <v>78.95999999999999</v>
@@ -1905,7 +1905,7 @@
         <v>23</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1687</v>
+        <v>2.1689</v>
       </c>
       <c r="I33" t="n">
         <v>82.43000000000001</v>
@@ -1950,7 +1950,7 @@
         <v>24</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1592</v>
+        <v>2.1593</v>
       </c>
       <c r="I34" t="n">
         <v>80.59</v>
@@ -1995,7 +1995,7 @@
         <v>22</v>
       </c>
       <c r="H35" t="n">
-        <v>2.1524</v>
+        <v>2.1525</v>
       </c>
       <c r="I35" t="n">
         <v>82.04000000000001</v>
@@ -2040,7 +2040,7 @@
         <v>23</v>
       </c>
       <c r="H36" t="n">
-        <v>2.1414</v>
+        <v>2.1416</v>
       </c>
       <c r="I36" t="n">
         <v>81.36</v>
@@ -2085,7 +2085,7 @@
         <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1338</v>
+        <v>2.1339</v>
       </c>
       <c r="I37" t="n">
         <v>81.73999999999999</v>
@@ -2130,7 +2130,7 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>2.1304</v>
+        <v>2.1305</v>
       </c>
       <c r="I38" t="n">
         <v>81.48</v>
@@ -2175,7 +2175,7 @@
         <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>2.1266</v>
+        <v>2.1268</v>
       </c>
       <c r="I39" t="n">
         <v>81.90000000000001</v>
@@ -2220,7 +2220,7 @@
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>2.0503</v>
+        <v>2.0504</v>
       </c>
       <c r="I40" t="n">
         <v>80.56999999999999</v>
@@ -2265,10 +2265,10 @@
         <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0436</v>
+        <v>2.0438</v>
       </c>
       <c r="I41" t="n">
-        <v>79.26000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="J41" t="n">
         <v>1838.2</v>
@@ -2310,7 +2310,7 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0136</v>
+        <v>2.0137</v>
       </c>
       <c r="I42" t="n">
         <v>78.81999999999999</v>
@@ -2333,7 +2333,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C43" t="n">
         <v>1433</v>
@@ -2355,7 +2355,7 @@
         <v>23</v>
       </c>
       <c r="H43" t="n">
-        <v>1.9808</v>
+        <v>1.9809</v>
       </c>
       <c r="I43" t="n">
         <v>79.8</v>
@@ -2400,10 +2400,10 @@
         <v>23</v>
       </c>
       <c r="H44" t="n">
-        <v>1.9798</v>
+        <v>1.9796</v>
       </c>
       <c r="I44" t="n">
-        <v>78.91</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>1738.3</v>
@@ -2445,10 +2445,10 @@
         <v>24</v>
       </c>
       <c r="H45" t="n">
-        <v>1.968</v>
+        <v>1.9681</v>
       </c>
       <c r="I45" t="n">
-        <v>77.19</v>
+        <v>77.2</v>
       </c>
       <c r="J45" t="n">
         <v>1741.9</v>
@@ -2490,10 +2490,10 @@
         <v>22</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9624</v>
+        <v>1.9626</v>
       </c>
       <c r="I46" t="n">
-        <v>79.8</v>
+        <v>79.81</v>
       </c>
       <c r="J46" t="n">
         <v>1694.4</v>
@@ -2535,7 +2535,7 @@
         <v>23</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9589</v>
+        <v>1.959</v>
       </c>
       <c r="I47" t="n">
         <v>78.3</v>
@@ -2580,10 +2580,10 @@
         <v>23</v>
       </c>
       <c r="H48" t="n">
-        <v>1.9438</v>
+        <v>1.944</v>
       </c>
       <c r="I48" t="n">
-        <v>75.77</v>
+        <v>75.78</v>
       </c>
       <c r="J48" t="n">
         <v>1678.5</v>
@@ -2625,10 +2625,10 @@
         <v>23</v>
       </c>
       <c r="H49" t="n">
-        <v>1.937</v>
+        <v>1.9371</v>
       </c>
       <c r="I49" t="n">
-        <v>78.34999999999999</v>
+        <v>78.36</v>
       </c>
       <c r="J49" t="n">
         <v>1811.2</v>
@@ -2670,10 +2670,10 @@
         <v>22</v>
       </c>
       <c r="H50" t="n">
-        <v>1.9369</v>
+        <v>1.9367</v>
       </c>
       <c r="I50" t="n">
-        <v>78.42</v>
+        <v>78.41</v>
       </c>
       <c r="J50" t="n">
         <v>1820.5</v>
@@ -2715,10 +2715,10 @@
         <v>22</v>
       </c>
       <c r="H51" t="n">
-        <v>1.909</v>
+        <v>1.9093</v>
       </c>
       <c r="I51" t="n">
-        <v>76.84</v>
+        <v>76.86</v>
       </c>
       <c r="J51" t="n">
         <v>1757.5</v>
@@ -2760,10 +2760,10 @@
         <v>23</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8923</v>
+        <v>1.893</v>
       </c>
       <c r="I52" t="n">
-        <v>76.59999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="J52" t="n">
         <v>1724.3</v>
@@ -2805,7 +2805,7 @@
         <v>21</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8819</v>
+        <v>1.882</v>
       </c>
       <c r="I53" t="n">
         <v>78.78</v>
@@ -2850,7 +2850,7 @@
         <v>23</v>
       </c>
       <c r="H54" t="n">
-        <v>1.8803</v>
+        <v>1.8805</v>
       </c>
       <c r="I54" t="n">
         <v>77.05</v>
@@ -2895,7 +2895,7 @@
         <v>23</v>
       </c>
       <c r="H55" t="n">
-        <v>1.8179</v>
+        <v>1.818</v>
       </c>
       <c r="I55" t="n">
         <v>75.86</v>
@@ -2940,7 +2940,7 @@
         <v>22</v>
       </c>
       <c r="H56" t="n">
-        <v>1.7906</v>
+        <v>1.7907</v>
       </c>
       <c r="I56" t="n">
         <v>75.76000000000001</v>
@@ -2985,7 +2985,7 @@
         <v>22</v>
       </c>
       <c r="H57" t="n">
-        <v>1.7861</v>
+        <v>1.7862</v>
       </c>
       <c r="I57" t="n">
         <v>77.16</v>
@@ -3030,10 +3030,10 @@
         <v>23</v>
       </c>
       <c r="H58" t="n">
-        <v>1.773</v>
+        <v>1.7732</v>
       </c>
       <c r="I58" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J58" t="n">
         <v>1718.7</v>
@@ -3075,7 +3075,7 @@
         <v>23</v>
       </c>
       <c r="H59" t="n">
-        <v>1.7583</v>
+        <v>1.7584</v>
       </c>
       <c r="I59" t="n">
         <v>74.87</v>
@@ -3120,7 +3120,7 @@
         <v>23</v>
       </c>
       <c r="H60" t="n">
-        <v>1.7572</v>
+        <v>1.7573</v>
       </c>
       <c r="I60" t="n">
         <v>75.09999999999999</v>
@@ -3165,7 +3165,7 @@
         <v>23</v>
       </c>
       <c r="H61" t="n">
-        <v>1.7517</v>
+        <v>1.7518</v>
       </c>
       <c r="I61" t="n">
         <v>74.93000000000001</v>
@@ -3210,7 +3210,7 @@
         <v>24</v>
       </c>
       <c r="H62" t="n">
-        <v>1.7359</v>
+        <v>1.736</v>
       </c>
       <c r="I62" t="n">
         <v>74.19</v>
@@ -3255,7 +3255,7 @@
         <v>24</v>
       </c>
       <c r="H63" t="n">
-        <v>1.6872</v>
+        <v>1.6873</v>
       </c>
       <c r="I63" t="n">
         <v>73.39</v>
@@ -3300,7 +3300,7 @@
         <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>1.6706</v>
+        <v>1.6707</v>
       </c>
       <c r="I64" t="n">
         <v>73.78</v>
@@ -3345,7 +3345,7 @@
         <v>24</v>
       </c>
       <c r="H65" t="n">
-        <v>1.6634</v>
+        <v>1.6631</v>
       </c>
       <c r="I65" t="n">
         <v>72.51000000000001</v>
@@ -3390,7 +3390,7 @@
         <v>23</v>
       </c>
       <c r="H66" t="n">
-        <v>1.64</v>
+        <v>1.6401</v>
       </c>
       <c r="I66" t="n">
         <v>72.09</v>
@@ -3435,10 +3435,10 @@
         <v>23</v>
       </c>
       <c r="H67" t="n">
-        <v>1.6322</v>
+        <v>1.6328</v>
       </c>
       <c r="I67" t="n">
-        <v>70.09999999999999</v>
+        <v>70.11</v>
       </c>
       <c r="J67" t="n">
         <v>1678.6</v>
@@ -3480,7 +3480,7 @@
         <v>18</v>
       </c>
       <c r="H68" t="n">
-        <v>1.6314</v>
+        <v>1.6315</v>
       </c>
       <c r="I68" t="n">
         <v>73.03</v>
@@ -3615,7 +3615,7 @@
         <v>22</v>
       </c>
       <c r="H71" t="n">
-        <v>1.6135</v>
+        <v>1.6136</v>
       </c>
       <c r="I71" t="n">
         <v>72.34999999999999</v>
@@ -3660,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="H72" t="n">
-        <v>1.6071</v>
+        <v>1.6072</v>
       </c>
       <c r="I72" t="n">
         <v>71.95999999999999</v>
@@ -3705,7 +3705,7 @@
         <v>22</v>
       </c>
       <c r="H73" t="n">
-        <v>1.5994</v>
+        <v>1.5995</v>
       </c>
       <c r="I73" t="n">
         <v>72.43000000000001</v>
@@ -3728,7 +3728,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C74" t="n">
         <v>1321</v>
@@ -3750,7 +3750,7 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.5954</v>
+        <v>1.5952</v>
       </c>
       <c r="I74" t="n">
         <v>70.56</v>
@@ -3795,10 +3795,10 @@
         <v>23</v>
       </c>
       <c r="H75" t="n">
-        <v>1.5787</v>
+        <v>1.5789</v>
       </c>
       <c r="I75" t="n">
-        <v>70.81999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="J75" t="n">
         <v>1621.9</v>
@@ -3840,7 +3840,7 @@
         <v>22</v>
       </c>
       <c r="H76" t="n">
-        <v>1.565</v>
+        <v>1.5651</v>
       </c>
       <c r="I76" t="n">
         <v>71.61</v>
@@ -3885,7 +3885,7 @@
         <v>23</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5536</v>
+        <v>1.5537</v>
       </c>
       <c r="I77" t="n">
         <v>69.39</v>
@@ -3930,7 +3930,7 @@
         <v>23</v>
       </c>
       <c r="H78" t="n">
-        <v>1.5214</v>
+        <v>1.5217</v>
       </c>
       <c r="I78" t="n">
         <v>69.20999999999999</v>
@@ -3975,7 +3975,7 @@
         <v>23</v>
       </c>
       <c r="H79" t="n">
-        <v>1.5194</v>
+        <v>1.5195</v>
       </c>
       <c r="I79" t="n">
         <v>69.43000000000001</v>
@@ -3998,44 +3998,44 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C80" t="n">
-        <v>1320</v>
+        <v>1173</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>mvc</t>
+          <t>a_ten</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G80" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H80" t="n">
-        <v>1.5067</v>
+        <v>1.5068</v>
       </c>
       <c r="I80" t="n">
-        <v>69.23</v>
+        <v>70.58</v>
       </c>
       <c r="J80" t="n">
-        <v>1567</v>
+        <v>1663.4</v>
       </c>
       <c r="K80" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L80" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M80" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
@@ -4043,44 +4043,44 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C81" t="n">
-        <v>1173</v>
+        <v>1320</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>a_ten</t>
+          <t>mvc</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H81" t="n">
-        <v>1.5061</v>
+        <v>1.5067</v>
       </c>
       <c r="I81" t="n">
-        <v>70.56</v>
+        <v>69.23</v>
       </c>
       <c r="J81" t="n">
-        <v>1663.4</v>
+        <v>1567</v>
       </c>
       <c r="K81" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L81" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M81" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
@@ -4200,7 +4200,7 @@
         <v>23</v>
       </c>
       <c r="H84" t="n">
-        <v>1.4813</v>
+        <v>1.4814</v>
       </c>
       <c r="I84" t="n">
         <v>68.36</v>
@@ -4290,7 +4290,7 @@
         <v>22</v>
       </c>
       <c r="H86" t="n">
-        <v>1.4516</v>
+        <v>1.4517</v>
       </c>
       <c r="I86" t="n">
         <v>68.15000000000001</v>
@@ -4335,7 +4335,7 @@
         <v>23</v>
       </c>
       <c r="H87" t="n">
-        <v>1.451</v>
+        <v>1.4511</v>
       </c>
       <c r="I87" t="n">
         <v>67.29000000000001</v>
@@ -4425,10 +4425,10 @@
         <v>23</v>
       </c>
       <c r="H89" t="n">
-        <v>1.4408</v>
+        <v>1.4416</v>
       </c>
       <c r="I89" t="n">
-        <v>67.68000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="J89" t="n">
         <v>1626.2</v>
@@ -4470,7 +4470,7 @@
         <v>23</v>
       </c>
       <c r="H90" t="n">
-        <v>1.435</v>
+        <v>1.4351</v>
       </c>
       <c r="I90" t="n">
         <v>66.98999999999999</v>
@@ -4560,10 +4560,10 @@
         <v>23</v>
       </c>
       <c r="H92" t="n">
-        <v>1.4218</v>
+        <v>1.4219</v>
       </c>
       <c r="I92" t="n">
-        <v>67.56</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>1583.1</v>
@@ -4605,7 +4605,7 @@
         <v>22</v>
       </c>
       <c r="H93" t="n">
-        <v>1.4039</v>
+        <v>1.404</v>
       </c>
       <c r="I93" t="n">
         <v>68.48</v>
@@ -4650,10 +4650,10 @@
         <v>22</v>
       </c>
       <c r="H94" t="n">
-        <v>1.3653</v>
+        <v>1.3657</v>
       </c>
       <c r="I94" t="n">
-        <v>65.79000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="J94" t="n">
         <v>1544.3</v>
@@ -4695,10 +4695,10 @@
         <v>24</v>
       </c>
       <c r="H95" t="n">
-        <v>1.3515</v>
+        <v>1.3516</v>
       </c>
       <c r="I95" t="n">
-        <v>66.23</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="J95" t="n">
         <v>1558.3</v>
@@ -4740,7 +4740,7 @@
         <v>22</v>
       </c>
       <c r="H96" t="n">
-        <v>1.3404</v>
+        <v>1.3405</v>
       </c>
       <c r="I96" t="n">
         <v>66.88</v>
@@ -4785,7 +4785,7 @@
         <v>23</v>
       </c>
       <c r="H97" t="n">
-        <v>1.3379</v>
+        <v>1.338</v>
       </c>
       <c r="I97" t="n">
         <v>63.9</v>
@@ -4830,7 +4830,7 @@
         <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>1.3328</v>
+        <v>1.3329</v>
       </c>
       <c r="I98" t="n">
         <v>66.09</v>
@@ -4875,10 +4875,10 @@
         <v>22</v>
       </c>
       <c r="H99" t="n">
-        <v>1.3323</v>
+        <v>1.3324</v>
       </c>
       <c r="I99" t="n">
-        <v>65.18000000000001</v>
+        <v>65.19</v>
       </c>
       <c r="J99" t="n">
         <v>1521</v>
@@ -5055,10 +5055,10 @@
         <v>23</v>
       </c>
       <c r="H103" t="n">
-        <v>1.2932</v>
+        <v>1.2926</v>
       </c>
       <c r="I103" t="n">
-        <v>64.97</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>1733.1</v>
@@ -5100,7 +5100,7 @@
         <v>23</v>
       </c>
       <c r="H104" t="n">
-        <v>1.2879</v>
+        <v>1.288</v>
       </c>
       <c r="I104" t="n">
         <v>64</v>
@@ -5145,7 +5145,7 @@
         <v>24</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2805</v>
+        <v>1.2806</v>
       </c>
       <c r="I105" t="n">
         <v>63.93</v>
@@ -5280,7 +5280,7 @@
         <v>22</v>
       </c>
       <c r="H108" t="n">
-        <v>1.2657</v>
+        <v>1.2658</v>
       </c>
       <c r="I108" t="n">
         <v>64.05</v>
@@ -5325,7 +5325,7 @@
         <v>24</v>
       </c>
       <c r="H109" t="n">
-        <v>1.2631</v>
+        <v>1.2632</v>
       </c>
       <c r="I109" t="n">
         <v>64.22</v>
@@ -5415,7 +5415,7 @@
         <v>23</v>
       </c>
       <c r="H111" t="n">
-        <v>1.2607</v>
+        <v>1.2606</v>
       </c>
       <c r="I111" t="n">
         <v>63.76</v>
@@ -5438,7 +5438,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C112" t="n">
         <v>1424</v>
@@ -5463,7 +5463,7 @@
         <v>1.2572</v>
       </c>
       <c r="I112" t="n">
-        <v>64.20999999999999</v>
+        <v>64.22</v>
       </c>
       <c r="J112" t="n">
         <v>1644.6</v>
@@ -5820,7 +5820,7 @@
         <v>24</v>
       </c>
       <c r="H120" t="n">
-        <v>1.1574</v>
+        <v>1.1576</v>
       </c>
       <c r="I120" t="n">
         <v>59.8</v>
@@ -5865,10 +5865,10 @@
         <v>23</v>
       </c>
       <c r="H121" t="n">
-        <v>1.147</v>
+        <v>1.1477</v>
       </c>
       <c r="I121" t="n">
-        <v>61.69</v>
+        <v>61.71</v>
       </c>
       <c r="J121" t="n">
         <v>1617.1</v>
@@ -5910,7 +5910,7 @@
         <v>24</v>
       </c>
       <c r="H122" t="n">
-        <v>1.146</v>
+        <v>1.1461</v>
       </c>
       <c r="I122" t="n">
         <v>59.52</v>
@@ -5955,10 +5955,10 @@
         <v>24</v>
       </c>
       <c r="H123" t="n">
-        <v>1.143</v>
+        <v>1.1431</v>
       </c>
       <c r="I123" t="n">
-        <v>61.1</v>
+        <v>61.11</v>
       </c>
       <c r="J123" t="n">
         <v>1560.2</v>
@@ -5978,7 +5978,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C124" t="n">
         <v>1443</v>
@@ -6000,10 +6000,10 @@
         <v>23</v>
       </c>
       <c r="H124" t="n">
-        <v>1.14</v>
+        <v>1.1394</v>
       </c>
       <c r="I124" t="n">
-        <v>59.52</v>
+        <v>59.51</v>
       </c>
       <c r="J124" t="n">
         <v>1483.2</v>
@@ -6045,7 +6045,7 @@
         <v>22</v>
       </c>
       <c r="H125" t="n">
-        <v>1.138</v>
+        <v>1.1377</v>
       </c>
       <c r="I125" t="n">
         <v>61.67</v>
@@ -6090,7 +6090,7 @@
         <v>21</v>
       </c>
       <c r="H126" t="n">
-        <v>1.1357</v>
+        <v>1.1358</v>
       </c>
       <c r="I126" t="n">
         <v>60.29</v>
@@ -6135,7 +6135,7 @@
         <v>21</v>
       </c>
       <c r="H127" t="n">
-        <v>1.133</v>
+        <v>1.1331</v>
       </c>
       <c r="I127" t="n">
         <v>60.32</v>
@@ -6225,10 +6225,10 @@
         <v>21</v>
       </c>
       <c r="H129" t="n">
-        <v>1.106</v>
+        <v>1.1062</v>
       </c>
       <c r="I129" t="n">
-        <v>59.89</v>
+        <v>59.9</v>
       </c>
       <c r="J129" t="n">
         <v>1535.7</v>
@@ -6270,7 +6270,7 @@
         <v>21</v>
       </c>
       <c r="H130" t="n">
-        <v>1.1019</v>
+        <v>1.102</v>
       </c>
       <c r="I130" t="n">
         <v>59.17</v>
@@ -6315,7 +6315,7 @@
         <v>21</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0867</v>
+        <v>1.0868</v>
       </c>
       <c r="I131" t="n">
         <v>57.25</v>
@@ -6405,10 +6405,10 @@
         <v>21</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0753</v>
+        <v>1.0752</v>
       </c>
       <c r="I133" t="n">
-        <v>59.73</v>
+        <v>59.72</v>
       </c>
       <c r="J133" t="n">
         <v>1532.8</v>
@@ -6450,7 +6450,7 @@
         <v>23</v>
       </c>
       <c r="H134" t="n">
-        <v>1.0656</v>
+        <v>1.0639</v>
       </c>
       <c r="I134" t="n">
         <v>59.09</v>
@@ -6540,7 +6540,7 @@
         <v>22</v>
       </c>
       <c r="H136" t="n">
-        <v>1.0594</v>
+        <v>1.0595</v>
       </c>
       <c r="I136" t="n">
         <v>58.2</v>
@@ -6585,7 +6585,7 @@
         <v>22</v>
       </c>
       <c r="H137" t="n">
-        <v>1.0358</v>
+        <v>1.0359</v>
       </c>
       <c r="I137" t="n">
         <v>58.73</v>
@@ -6630,10 +6630,10 @@
         <v>24</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0178</v>
+        <v>1.0176</v>
       </c>
       <c r="I138" t="n">
-        <v>56.37</v>
+        <v>56.36</v>
       </c>
       <c r="J138" t="n">
         <v>1464.5</v>
@@ -6675,7 +6675,7 @@
         <v>21</v>
       </c>
       <c r="H139" t="n">
-        <v>1.0173</v>
+        <v>1.0171</v>
       </c>
       <c r="I139" t="n">
         <v>55.67</v>
@@ -6720,10 +6720,10 @@
         <v>22</v>
       </c>
       <c r="H140" t="n">
-        <v>1.0119</v>
+        <v>1.012</v>
       </c>
       <c r="I140" t="n">
-        <v>58.13</v>
+        <v>58.14</v>
       </c>
       <c r="J140" t="n">
         <v>1536.2</v>
@@ -6765,10 +6765,10 @@
         <v>22</v>
       </c>
       <c r="H141" t="n">
-        <v>1.008</v>
+        <v>1.0081</v>
       </c>
       <c r="I141" t="n">
-        <v>57.79</v>
+        <v>57.8</v>
       </c>
       <c r="J141" t="n">
         <v>1481.5</v>
@@ -6833,7 +6833,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C143" t="n">
         <v>1405</v>
@@ -6900,10 +6900,10 @@
         <v>23</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9991</v>
+        <v>0.9989</v>
       </c>
       <c r="I144" t="n">
-        <v>56.27</v>
+        <v>56.26</v>
       </c>
       <c r="J144" t="n">
         <v>1440.5</v>
@@ -6945,7 +6945,7 @@
         <v>23</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9909</v>
+        <v>0.991</v>
       </c>
       <c r="I145" t="n">
         <v>55.58</v>
@@ -6990,10 +6990,10 @@
         <v>24</v>
       </c>
       <c r="H146" t="n">
-        <v>0.982</v>
+        <v>0.9812</v>
       </c>
       <c r="I146" t="n">
-        <v>55.26</v>
+        <v>55.25</v>
       </c>
       <c r="J146" t="n">
         <v>1456.8</v>
@@ -7038,7 +7038,7 @@
         <v>0.9791</v>
       </c>
       <c r="I147" t="n">
-        <v>57.04</v>
+        <v>57.05</v>
       </c>
       <c r="J147" t="n">
         <v>1515.6</v>
@@ -7170,7 +7170,7 @@
         <v>24</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9607</v>
+        <v>0.9606</v>
       </c>
       <c r="I150" t="n">
         <v>55.77</v>
@@ -7215,7 +7215,7 @@
         <v>23</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9407</v>
+        <v>0.9406</v>
       </c>
       <c r="I151" t="n">
         <v>54.71</v>
@@ -7305,7 +7305,7 @@
         <v>23</v>
       </c>
       <c r="H153" t="n">
-        <v>0.9225</v>
+        <v>0.9224</v>
       </c>
       <c r="I153" t="n">
         <v>54.65</v>
@@ -7350,10 +7350,10 @@
         <v>22</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9191</v>
+        <v>0.9193</v>
       </c>
       <c r="I154" t="n">
-        <v>54.62</v>
+        <v>54.64</v>
       </c>
       <c r="J154" t="n">
         <v>1471.5</v>
@@ -7395,7 +7395,7 @@
         <v>22</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9136</v>
+        <v>0.9135</v>
       </c>
       <c r="I155" t="n">
         <v>54.33</v>
@@ -7418,7 +7418,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C156" t="n">
         <v>1426</v>
@@ -7440,10 +7440,10 @@
         <v>21</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8994</v>
+        <v>0.8995</v>
       </c>
       <c r="I156" t="n">
-        <v>50.84</v>
+        <v>50.85</v>
       </c>
       <c r="J156" t="n">
         <v>1458.1</v>
@@ -7508,7 +7508,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C158" t="n">
         <v>1201</v>
@@ -7530,10 +7530,10 @@
         <v>22</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8844</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>53.12</v>
+        <v>53.14</v>
       </c>
       <c r="J158" t="n">
         <v>1420.6</v>
@@ -7553,44 +7553,44 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C159" t="n">
-        <v>1286</v>
+        <v>1335</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Montana St</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>big_sky</t>
+          <t>ivy</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G159" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8778</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>52.55</v>
+        <v>52.51</v>
       </c>
       <c r="J159" t="n">
-        <v>1436.3</v>
+        <v>1419.8</v>
       </c>
       <c r="K159" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L159" t="n">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="M159" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="160">
@@ -7598,44 +7598,44 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C160" t="n">
-        <v>1335</v>
+        <v>1286</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Penn</t>
+          <t>Montana St</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ivy</t>
+          <t>big_sky</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G160" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H160" t="n">
         <v>0.8774999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>52.51</v>
+        <v>52.54</v>
       </c>
       <c r="J160" t="n">
-        <v>1419.8</v>
+        <v>1436.3</v>
       </c>
       <c r="K160" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="L160" t="n">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="M160" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161">
@@ -7665,10 +7665,10 @@
         <v>23</v>
       </c>
       <c r="H161" t="n">
-        <v>0.8732</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>52.6</v>
+        <v>52.62</v>
       </c>
       <c r="J161" t="n">
         <v>1457.4</v>
@@ -7710,7 +7710,7 @@
         <v>23</v>
       </c>
       <c r="H162" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8706</v>
       </c>
       <c r="I162" t="n">
         <v>52.23</v>
@@ -7755,10 +7755,10 @@
         <v>21</v>
       </c>
       <c r="H163" t="n">
-        <v>0.8582</v>
+        <v>0.8583</v>
       </c>
       <c r="I163" t="n">
-        <v>52.87</v>
+        <v>52.88</v>
       </c>
       <c r="J163" t="n">
         <v>1421.6</v>
@@ -7778,7 +7778,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C164" t="n">
         <v>1292</v>
@@ -7890,7 +7890,7 @@
         <v>24</v>
       </c>
       <c r="H166" t="n">
-        <v>0.8429</v>
+        <v>0.8428</v>
       </c>
       <c r="I166" t="n">
         <v>50.3</v>
@@ -7958,44 +7958,44 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C168" t="n">
-        <v>1324</v>
+        <v>1210</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Oakland</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>horizon</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G168" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8377</v>
+        <v>0.8381</v>
       </c>
       <c r="I168" t="n">
-        <v>52.37</v>
+        <v>51.91</v>
       </c>
       <c r="J168" t="n">
-        <v>1505.3</v>
+        <v>1472.7</v>
       </c>
       <c r="K168" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L168" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="M168" t="n">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="169">
@@ -8003,44 +8003,44 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C169" t="n">
-        <v>1210</v>
+        <v>1324</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Oakland</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>horizon</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G169" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H169" t="n">
         <v>0.8377</v>
       </c>
       <c r="I169" t="n">
-        <v>51.88</v>
+        <v>52.36</v>
       </c>
       <c r="J169" t="n">
-        <v>1472.7</v>
+        <v>1505.3</v>
       </c>
       <c r="K169" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L169" t="n">
+        <v>161</v>
+      </c>
+      <c r="M169" t="n">
         <v>166</v>
-      </c>
-      <c r="M169" t="n">
-        <v>138</v>
       </c>
     </row>
     <row r="170">
@@ -8070,7 +8070,7 @@
         <v>19</v>
       </c>
       <c r="H170" t="n">
-        <v>0.8373</v>
+        <v>0.8375</v>
       </c>
       <c r="I170" t="n">
         <v>52.18</v>
@@ -8205,7 +8205,7 @@
         <v>23</v>
       </c>
       <c r="H173" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="I173" t="n">
         <v>49.31</v>
@@ -8385,10 +8385,10 @@
         <v>22</v>
       </c>
       <c r="H177" t="n">
-        <v>0.7974</v>
+        <v>0.7973</v>
       </c>
       <c r="I177" t="n">
-        <v>50.64</v>
+        <v>50.63</v>
       </c>
       <c r="J177" t="n">
         <v>1450.7</v>
@@ -8475,10 +8475,10 @@
         <v>23</v>
       </c>
       <c r="H179" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="I179" t="n">
-        <v>49.5</v>
+        <v>49.51</v>
       </c>
       <c r="J179" t="n">
         <v>1436.3</v>
@@ -8543,7 +8543,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C181" t="n">
         <v>1346</v>
@@ -8565,7 +8565,7 @@
         <v>24</v>
       </c>
       <c r="H181" t="n">
-        <v>0.7791</v>
+        <v>0.7786</v>
       </c>
       <c r="I181" t="n">
         <v>48</v>
@@ -8655,10 +8655,10 @@
         <v>25</v>
       </c>
       <c r="H183" t="n">
-        <v>0.7678</v>
+        <v>0.7675</v>
       </c>
       <c r="I183" t="n">
-        <v>48.2</v>
+        <v>48.18</v>
       </c>
       <c r="J183" t="n">
         <v>1424.9</v>
@@ -8700,7 +8700,7 @@
         <v>24</v>
       </c>
       <c r="H184" t="n">
-        <v>0.7631</v>
+        <v>0.7634</v>
       </c>
       <c r="I184" t="n">
         <v>47.87</v>
@@ -8748,7 +8748,7 @@
         <v>0.7628</v>
       </c>
       <c r="I185" t="n">
-        <v>48.32</v>
+        <v>48.33</v>
       </c>
       <c r="J185" t="n">
         <v>1443.6</v>
@@ -8993,7 +8993,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C191" t="n">
         <v>1111</v>
@@ -9015,10 +9015,10 @@
         <v>22</v>
       </c>
       <c r="H191" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7335</v>
       </c>
       <c r="I191" t="n">
-        <v>48</v>
+        <v>48.01</v>
       </c>
       <c r="J191" t="n">
         <v>1488.7</v>
@@ -9060,10 +9060,10 @@
         <v>23</v>
       </c>
       <c r="H192" t="n">
-        <v>0.7269</v>
+        <v>0.7262</v>
       </c>
       <c r="I192" t="n">
-        <v>47.22</v>
+        <v>47.21</v>
       </c>
       <c r="J192" t="n">
         <v>1475.9</v>
@@ -9105,10 +9105,10 @@
         <v>24</v>
       </c>
       <c r="H193" t="n">
-        <v>0.7217</v>
+        <v>0.7214</v>
       </c>
       <c r="I193" t="n">
-        <v>47.25</v>
+        <v>47.26</v>
       </c>
       <c r="J193" t="n">
         <v>1399.2</v>
@@ -9150,7 +9150,7 @@
         <v>23</v>
       </c>
       <c r="H194" t="n">
-        <v>0.721</v>
+        <v>0.7209</v>
       </c>
       <c r="I194" t="n">
         <v>45.46</v>
@@ -9195,7 +9195,7 @@
         <v>22</v>
       </c>
       <c r="H195" t="n">
-        <v>0.7205</v>
+        <v>0.7204</v>
       </c>
       <c r="I195" t="n">
         <v>44.44</v>
@@ -9285,10 +9285,10 @@
         <v>23</v>
       </c>
       <c r="H197" t="n">
-        <v>0.7097</v>
+        <v>0.7099</v>
       </c>
       <c r="I197" t="n">
-        <v>46.62</v>
+        <v>46.65</v>
       </c>
       <c r="J197" t="n">
         <v>1393.6</v>
@@ -9330,7 +9330,7 @@
         <v>24</v>
       </c>
       <c r="H198" t="n">
-        <v>0.7068</v>
+        <v>0.7067</v>
       </c>
       <c r="I198" t="n">
         <v>46.96</v>
@@ -9375,10 +9375,10 @@
         <v>21</v>
       </c>
       <c r="H199" t="n">
-        <v>0.7054</v>
+        <v>0.7045</v>
       </c>
       <c r="I199" t="n">
-        <v>45.69</v>
+        <v>45.67</v>
       </c>
       <c r="J199" t="n">
         <v>1383.1</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7043</v>
+        <v>0.7044</v>
       </c>
       <c r="I200" t="n">
         <v>45.57</v>
@@ -9465,10 +9465,10 @@
         <v>23</v>
       </c>
       <c r="H201" t="n">
-        <v>0.7022</v>
+        <v>0.7023</v>
       </c>
       <c r="I201" t="n">
-        <v>45.54</v>
+        <v>45.55</v>
       </c>
       <c r="J201" t="n">
         <v>1506</v>
@@ -9735,10 +9735,10 @@
         <v>23</v>
       </c>
       <c r="H207" t="n">
-        <v>0.6771</v>
+        <v>0.677</v>
       </c>
       <c r="I207" t="n">
-        <v>45.4</v>
+        <v>45.39</v>
       </c>
       <c r="J207" t="n">
         <v>1478.9</v>
@@ -9780,10 +9780,10 @@
         <v>24</v>
       </c>
       <c r="H208" t="n">
-        <v>0.6767</v>
+        <v>0.6765</v>
       </c>
       <c r="I208" t="n">
-        <v>45.42</v>
+        <v>45.43</v>
       </c>
       <c r="J208" t="n">
         <v>1385.5</v>
@@ -9870,10 +9870,10 @@
         <v>24</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6669</v>
+        <v>0.6667</v>
       </c>
       <c r="I210" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
       <c r="J210" t="n">
         <v>1501.6</v>
@@ -9915,10 +9915,10 @@
         <v>23</v>
       </c>
       <c r="H211" t="n">
-        <v>0.6627</v>
+        <v>0.6624</v>
       </c>
       <c r="I211" t="n">
-        <v>43.34</v>
+        <v>43.33</v>
       </c>
       <c r="J211" t="n">
         <v>1381.1</v>
@@ -10005,10 +10005,10 @@
         <v>22</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6559</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="I213" t="n">
-        <v>42.44</v>
+        <v>42.43</v>
       </c>
       <c r="J213" t="n">
         <v>1407.5</v>
@@ -10143,7 +10143,7 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>41.23</v>
+        <v>41.24</v>
       </c>
       <c r="J216" t="n">
         <v>1383.6</v>
@@ -10185,10 +10185,10 @@
         <v>22</v>
       </c>
       <c r="H217" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6365</v>
       </c>
       <c r="I217" t="n">
-        <v>41.17</v>
+        <v>41.16</v>
       </c>
       <c r="J217" t="n">
         <v>1434.3</v>
@@ -10230,10 +10230,10 @@
         <v>23</v>
       </c>
       <c r="H218" t="n">
-        <v>0.6324</v>
+        <v>0.6325</v>
       </c>
       <c r="I218" t="n">
-        <v>43.77</v>
+        <v>43.79</v>
       </c>
       <c r="J218" t="n">
         <v>1427.8</v>
@@ -10275,7 +10275,7 @@
         <v>24</v>
       </c>
       <c r="H219" t="n">
-        <v>0.6298</v>
+        <v>0.6297</v>
       </c>
       <c r="I219" t="n">
         <v>42.77</v>
@@ -10320,10 +10320,10 @@
         <v>27</v>
       </c>
       <c r="H220" t="n">
-        <v>0.6287</v>
+        <v>0.6284</v>
       </c>
       <c r="I220" t="n">
-        <v>42.01</v>
+        <v>41.99</v>
       </c>
       <c r="J220" t="n">
         <v>1417.3</v>
@@ -10455,7 +10455,7 @@
         <v>24</v>
       </c>
       <c r="H223" t="n">
-        <v>0.6264</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I223" t="n">
         <v>42.98</v>
@@ -10545,10 +10545,10 @@
         <v>22</v>
       </c>
       <c r="H225" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6214</v>
       </c>
       <c r="I225" t="n">
-        <v>40.91</v>
+        <v>40.9</v>
       </c>
       <c r="J225" t="n">
         <v>1446.4</v>
@@ -10590,7 +10590,7 @@
         <v>24</v>
       </c>
       <c r="H226" t="n">
-        <v>0.6159</v>
+        <v>0.6158</v>
       </c>
       <c r="I226" t="n">
         <v>42.32</v>
@@ -10725,10 +10725,10 @@
         <v>23</v>
       </c>
       <c r="H229" t="n">
-        <v>0.6093</v>
+        <v>0.6088</v>
       </c>
       <c r="I229" t="n">
-        <v>40.72</v>
+        <v>40.71</v>
       </c>
       <c r="J229" t="n">
         <v>1481.7</v>
@@ -10905,10 +10905,10 @@
         <v>24</v>
       </c>
       <c r="H233" t="n">
-        <v>0.5727</v>
+        <v>0.5726</v>
       </c>
       <c r="I233" t="n">
-        <v>38.81</v>
+        <v>38.8</v>
       </c>
       <c r="J233" t="n">
         <v>1442.9</v>
@@ -10995,10 +10995,10 @@
         <v>25</v>
       </c>
       <c r="H235" t="n">
-        <v>0.5587</v>
+        <v>0.5585</v>
       </c>
       <c r="I235" t="n">
-        <v>39.02</v>
+        <v>39.03</v>
       </c>
       <c r="J235" t="n">
         <v>1442.3</v>
@@ -11040,10 +11040,10 @@
         <v>25</v>
       </c>
       <c r="H236" t="n">
-        <v>0.5579</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>37.87</v>
+        <v>37.88</v>
       </c>
       <c r="J236" t="n">
         <v>1352.5</v>
@@ -11355,10 +11355,10 @@
         <v>23</v>
       </c>
       <c r="H243" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5315</v>
       </c>
       <c r="I243" t="n">
-        <v>39.18</v>
+        <v>39.17</v>
       </c>
       <c r="J243" t="n">
         <v>1361.4</v>
@@ -11400,10 +11400,10 @@
         <v>22</v>
       </c>
       <c r="H244" t="n">
-        <v>0.5261</v>
+        <v>0.5262</v>
       </c>
       <c r="I244" t="n">
-        <v>37.44</v>
+        <v>37.45</v>
       </c>
       <c r="J244" t="n">
         <v>1457.9</v>
@@ -11625,7 +11625,7 @@
         <v>23</v>
       </c>
       <c r="H249" t="n">
-        <v>0.518</v>
+        <v>0.5173</v>
       </c>
       <c r="I249" t="n">
         <v>38.86</v>
@@ -11805,10 +11805,10 @@
         <v>23</v>
       </c>
       <c r="H253" t="n">
-        <v>0.5088</v>
+        <v>0.5087</v>
       </c>
       <c r="I253" t="n">
-        <v>36.66</v>
+        <v>36.67</v>
       </c>
       <c r="J253" t="n">
         <v>1362.2</v>
@@ -11850,10 +11850,10 @@
         <v>19</v>
       </c>
       <c r="H254" t="n">
-        <v>0.5037</v>
+        <v>0.5038</v>
       </c>
       <c r="I254" t="n">
-        <v>37.03</v>
+        <v>37.04</v>
       </c>
       <c r="J254" t="n">
         <v>1405.2</v>
@@ -11873,7 +11873,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C255" t="n">
         <v>1176</v>
@@ -11943,7 +11943,7 @@
         <v>0.4999</v>
       </c>
       <c r="I256" t="n">
-        <v>37.37</v>
+        <v>37.38</v>
       </c>
       <c r="J256" t="n">
         <v>1373.2</v>
@@ -12030,10 +12030,10 @@
         <v>22</v>
       </c>
       <c r="H258" t="n">
-        <v>0.4926</v>
+        <v>0.4925</v>
       </c>
       <c r="I258" t="n">
-        <v>36.29</v>
+        <v>36.28</v>
       </c>
       <c r="J258" t="n">
         <v>1421.8</v>
@@ -12168,7 +12168,7 @@
         <v>0.4741</v>
       </c>
       <c r="I261" t="n">
-        <v>36.31</v>
+        <v>36.32</v>
       </c>
       <c r="J261" t="n">
         <v>1375.4</v>
@@ -12210,7 +12210,7 @@
         <v>23</v>
       </c>
       <c r="H262" t="n">
-        <v>0.4695</v>
+        <v>0.4694</v>
       </c>
       <c r="I262" t="n">
         <v>34.53</v>
@@ -12255,10 +12255,10 @@
         <v>23</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4653</v>
+        <v>0.4652</v>
       </c>
       <c r="I263" t="n">
-        <v>34.23</v>
+        <v>34.24</v>
       </c>
       <c r="J263" t="n">
         <v>1348.7</v>
@@ -12300,10 +12300,10 @@
         <v>23</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4652</v>
+        <v>0.4651</v>
       </c>
       <c r="I264" t="n">
-        <v>32.75</v>
+        <v>32.74</v>
       </c>
       <c r="J264" t="n">
         <v>1374.1</v>
@@ -12345,10 +12345,10 @@
         <v>23</v>
       </c>
       <c r="H265" t="n">
-        <v>0.4607</v>
+        <v>0.4608</v>
       </c>
       <c r="I265" t="n">
-        <v>33.45</v>
+        <v>33.46</v>
       </c>
       <c r="J265" t="n">
         <v>1388.7</v>
@@ -12368,7 +12368,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C266" t="n">
         <v>1230</v>
@@ -12390,10 +12390,10 @@
         <v>23</v>
       </c>
       <c r="H266" t="n">
-        <v>0.4554</v>
+        <v>0.4552</v>
       </c>
       <c r="I266" t="n">
-        <v>33.96</v>
+        <v>33.95</v>
       </c>
       <c r="J266" t="n">
         <v>1320.9</v>
@@ -12483,7 +12483,7 @@
         <v>0.4538</v>
       </c>
       <c r="I268" t="n">
-        <v>33.55</v>
+        <v>33.54</v>
       </c>
       <c r="J268" t="n">
         <v>1322.9</v>
@@ -12525,7 +12525,7 @@
         <v>22</v>
       </c>
       <c r="H269" t="n">
-        <v>0.4531</v>
+        <v>0.453</v>
       </c>
       <c r="I269" t="n">
         <v>29.2</v>
@@ -12570,7 +12570,7 @@
         <v>23</v>
       </c>
       <c r="H270" t="n">
-        <v>0.4475</v>
+        <v>0.4474</v>
       </c>
       <c r="I270" t="n">
         <v>32.81</v>
@@ -12615,10 +12615,10 @@
         <v>23</v>
       </c>
       <c r="H271" t="n">
-        <v>0.447</v>
+        <v>0.4469</v>
       </c>
       <c r="I271" t="n">
-        <v>33.06</v>
+        <v>33.05</v>
       </c>
       <c r="J271" t="n">
         <v>1388</v>
@@ -12705,10 +12705,10 @@
         <v>22</v>
       </c>
       <c r="H273" t="n">
-        <v>0.4348</v>
+        <v>0.4346</v>
       </c>
       <c r="I273" t="n">
-        <v>31.18</v>
+        <v>31.17</v>
       </c>
       <c r="J273" t="n">
         <v>1331.3</v>
@@ -12753,7 +12753,7 @@
         <v>0.4311</v>
       </c>
       <c r="I274" t="n">
-        <v>31.43</v>
+        <v>31.44</v>
       </c>
       <c r="J274" t="n">
         <v>1336.5</v>
@@ -12795,10 +12795,10 @@
         <v>24</v>
       </c>
       <c r="H275" t="n">
-        <v>0.4299</v>
+        <v>0.4296</v>
       </c>
       <c r="I275" t="n">
-        <v>31.55</v>
+        <v>31.53</v>
       </c>
       <c r="J275" t="n">
         <v>1284</v>
@@ -12885,10 +12885,10 @@
         <v>23</v>
       </c>
       <c r="H277" t="n">
-        <v>0.4274</v>
+        <v>0.4262</v>
       </c>
       <c r="I277" t="n">
-        <v>29.61</v>
+        <v>29.59</v>
       </c>
       <c r="J277" t="n">
         <v>1340.3</v>
@@ -12908,7 +12908,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C278" t="n">
         <v>1447</v>
@@ -12975,10 +12975,10 @@
         <v>22</v>
       </c>
       <c r="H279" t="n">
-        <v>0.4224</v>
+        <v>0.4223</v>
       </c>
       <c r="I279" t="n">
-        <v>30.74</v>
+        <v>30.72</v>
       </c>
       <c r="J279" t="n">
         <v>1364.3</v>
@@ -13065,10 +13065,10 @@
         <v>23</v>
       </c>
       <c r="H281" t="n">
-        <v>0.4193</v>
+        <v>0.4191</v>
       </c>
       <c r="I281" t="n">
-        <v>30.96</v>
+        <v>30.95</v>
       </c>
       <c r="J281" t="n">
         <v>1369.2</v>
@@ -13155,7 +13155,7 @@
         <v>24</v>
       </c>
       <c r="H283" t="n">
-        <v>0.4174</v>
+        <v>0.4173</v>
       </c>
       <c r="I283" t="n">
         <v>30.48</v>
@@ -13203,7 +13203,7 @@
         <v>0.4157</v>
       </c>
       <c r="I284" t="n">
-        <v>32.03</v>
+        <v>32.04</v>
       </c>
       <c r="J284" t="n">
         <v>1313.8</v>
@@ -13245,10 +13245,10 @@
         <v>21</v>
       </c>
       <c r="H285" t="n">
-        <v>0.4098</v>
+        <v>0.4099</v>
       </c>
       <c r="I285" t="n">
-        <v>28.36</v>
+        <v>28.37</v>
       </c>
       <c r="J285" t="n">
         <v>1364.5</v>
@@ -13338,7 +13338,7 @@
         <v>0.4043</v>
       </c>
       <c r="I287" t="n">
-        <v>32.31</v>
+        <v>32.32</v>
       </c>
       <c r="J287" t="n">
         <v>1362.7</v>
@@ -13380,7 +13380,7 @@
         <v>21</v>
       </c>
       <c r="H288" t="n">
-        <v>0.4031</v>
+        <v>0.403</v>
       </c>
       <c r="I288" t="n">
         <v>31.13</v>
@@ -13425,10 +13425,10 @@
         <v>22</v>
       </c>
       <c r="H289" t="n">
-        <v>0.4028</v>
+        <v>0.4024</v>
       </c>
       <c r="I289" t="n">
-        <v>29.6</v>
+        <v>29.57</v>
       </c>
       <c r="J289" t="n">
         <v>1376.6</v>
@@ -13473,7 +13473,7 @@
         <v>0.4003</v>
       </c>
       <c r="I290" t="n">
-        <v>29.79</v>
+        <v>29.8</v>
       </c>
       <c r="J290" t="n">
         <v>1349.4</v>
@@ -13493,44 +13493,44 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C291" t="n">
-        <v>1337</v>
+        <v>1239</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Pepperdine</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G291" t="n">
         <v>23</v>
       </c>
       <c r="H291" t="n">
-        <v>0.3907</v>
+        <v>0.3903</v>
       </c>
       <c r="I291" t="n">
-        <v>30.95</v>
+        <v>29.64</v>
       </c>
       <c r="J291" t="n">
-        <v>1308.8</v>
+        <v>1361</v>
       </c>
       <c r="K291" t="n">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="L291" t="n">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="M291" t="n">
-        <v>259</v>
+        <v>294</v>
       </c>
     </row>
     <row r="292">
@@ -13538,44 +13538,44 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C292" t="n">
-        <v>1239</v>
+        <v>1337</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Pepperdine</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G292" t="n">
         <v>23</v>
       </c>
       <c r="H292" t="n">
-        <v>0.3904</v>
+        <v>0.3902</v>
       </c>
       <c r="I292" t="n">
-        <v>29.64</v>
+        <v>30.94</v>
       </c>
       <c r="J292" t="n">
-        <v>1361</v>
+        <v>1308.8</v>
       </c>
       <c r="K292" t="n">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="L292" t="n">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="M292" t="n">
-        <v>294</v>
+        <v>259</v>
       </c>
     </row>
     <row r="293">
@@ -13785,10 +13785,10 @@
         <v>22</v>
       </c>
       <c r="H297" t="n">
-        <v>0.3788</v>
+        <v>0.3786</v>
       </c>
       <c r="I297" t="n">
-        <v>27.78</v>
+        <v>27.76</v>
       </c>
       <c r="J297" t="n">
         <v>1285.4</v>
@@ -13808,7 +13808,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C298" t="n">
         <v>1411</v>
@@ -13830,10 +13830,10 @@
         <v>22</v>
       </c>
       <c r="H298" t="n">
-        <v>0.3734</v>
+        <v>0.3733</v>
       </c>
       <c r="I298" t="n">
-        <v>26.72</v>
+        <v>26.7</v>
       </c>
       <c r="J298" t="n">
         <v>1289.8</v>
@@ -13875,10 +13875,10 @@
         <v>21</v>
       </c>
       <c r="H299" t="n">
-        <v>0.3729</v>
+        <v>0.3726</v>
       </c>
       <c r="I299" t="n">
-        <v>26.02</v>
+        <v>26.01</v>
       </c>
       <c r="J299" t="n">
         <v>1254.2</v>
@@ -13898,7 +13898,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C300" t="n">
         <v>1476</v>
@@ -13968,7 +13968,7 @@
         <v>0.37</v>
       </c>
       <c r="I301" t="n">
-        <v>26.68</v>
+        <v>26.67</v>
       </c>
       <c r="J301" t="n">
         <v>1314.9</v>
@@ -14055,7 +14055,7 @@
         <v>25</v>
       </c>
       <c r="H303" t="n">
-        <v>0.368</v>
+        <v>0.3679</v>
       </c>
       <c r="I303" t="n">
         <v>27.32</v>
@@ -14100,10 +14100,10 @@
         <v>21</v>
       </c>
       <c r="H304" t="n">
-        <v>0.3668</v>
+        <v>0.3665</v>
       </c>
       <c r="I304" t="n">
-        <v>27.72</v>
+        <v>27.7</v>
       </c>
       <c r="J304" t="n">
         <v>1320.1</v>
@@ -14145,7 +14145,7 @@
         <v>24</v>
       </c>
       <c r="H305" t="n">
-        <v>0.3649</v>
+        <v>0.3648</v>
       </c>
       <c r="I305" t="n">
         <v>27.52</v>
@@ -14190,10 +14190,10 @@
         <v>22</v>
       </c>
       <c r="H306" t="n">
-        <v>0.3631</v>
+        <v>0.3632</v>
       </c>
       <c r="I306" t="n">
-        <v>26.72</v>
+        <v>26.73</v>
       </c>
       <c r="J306" t="n">
         <v>1350.1</v>
@@ -14258,44 +14258,44 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C308" t="n">
-        <v>1212</v>
+        <v>1481</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Grambling</t>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>swac</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F308" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G308" t="n">
         <v>22</v>
       </c>
       <c r="H308" t="n">
-        <v>0.3608</v>
+        <v>0.3604</v>
       </c>
       <c r="I308" t="n">
-        <v>26.99</v>
+        <v>25.09</v>
       </c>
       <c r="J308" t="n">
-        <v>1310.9</v>
+        <v>1379.4</v>
       </c>
       <c r="K308" t="n">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="L308" t="n">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="M308" t="n">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="309">
@@ -14303,44 +14303,44 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C309" t="n">
-        <v>1481</v>
+        <v>1212</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>New Haven</t>
+          <t>Grambling</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>swac</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G309" t="n">
         <v>22</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3605</v>
+        <v>0.3603</v>
       </c>
       <c r="I309" t="n">
-        <v>25.09</v>
+        <v>26.98</v>
       </c>
       <c r="J309" t="n">
-        <v>1379.4</v>
+        <v>1310.9</v>
       </c>
       <c r="K309" t="n">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="L309" t="n">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="M309" t="n">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="310">
@@ -14373,7 +14373,7 @@
         <v>0.359</v>
       </c>
       <c r="I310" t="n">
-        <v>28.17</v>
+        <v>28.18</v>
       </c>
       <c r="J310" t="n">
         <v>1288.1</v>
@@ -14415,7 +14415,7 @@
         <v>22</v>
       </c>
       <c r="H311" t="n">
-        <v>0.3568</v>
+        <v>0.3569</v>
       </c>
       <c r="I311" t="n">
         <v>27.35</v>
@@ -14685,10 +14685,10 @@
         <v>25</v>
       </c>
       <c r="H317" t="n">
-        <v>0.3322</v>
+        <v>0.3316</v>
       </c>
       <c r="I317" t="n">
-        <v>25.48</v>
+        <v>25.47</v>
       </c>
       <c r="J317" t="n">
         <v>1285.5</v>
@@ -14730,10 +14730,10 @@
         <v>23</v>
       </c>
       <c r="H318" t="n">
-        <v>0.3317</v>
+        <v>0.3309</v>
       </c>
       <c r="I318" t="n">
-        <v>25.24</v>
+        <v>25.23</v>
       </c>
       <c r="J318" t="n">
         <v>1260.5</v>
@@ -14910,10 +14910,10 @@
         <v>22</v>
       </c>
       <c r="H322" t="n">
-        <v>0.3228</v>
+        <v>0.3227</v>
       </c>
       <c r="I322" t="n">
-        <v>21.54</v>
+        <v>21.53</v>
       </c>
       <c r="J322" t="n">
         <v>1244.7</v>
@@ -14958,7 +14958,7 @@
         <v>0.3125</v>
       </c>
       <c r="I323" t="n">
-        <v>23.72</v>
+        <v>23.73</v>
       </c>
       <c r="J323" t="n">
         <v>1294.9</v>
@@ -15048,7 +15048,7 @@
         <v>0.3085</v>
       </c>
       <c r="I325" t="n">
-        <v>23.51</v>
+        <v>23.5</v>
       </c>
       <c r="J325" t="n">
         <v>1300.9</v>
@@ -15135,10 +15135,10 @@
         <v>22</v>
       </c>
       <c r="H327" t="n">
-        <v>0.3055</v>
+        <v>0.3054</v>
       </c>
       <c r="I327" t="n">
-        <v>22.76</v>
+        <v>22.75</v>
       </c>
       <c r="J327" t="n">
         <v>1213.4</v>
@@ -15270,7 +15270,7 @@
         <v>22</v>
       </c>
       <c r="H330" t="n">
-        <v>0.2894</v>
+        <v>0.2895</v>
       </c>
       <c r="I330" t="n">
         <v>21.1</v>
@@ -15360,7 +15360,7 @@
         <v>24</v>
       </c>
       <c r="H332" t="n">
-        <v>0.2842</v>
+        <v>0.2843</v>
       </c>
       <c r="I332" t="n">
         <v>24.39</v>
@@ -15408,7 +15408,7 @@
         <v>0.2842</v>
       </c>
       <c r="I333" t="n">
-        <v>21.87</v>
+        <v>21.86</v>
       </c>
       <c r="J333" t="n">
         <v>1310</v>
@@ -15540,10 +15540,10 @@
         <v>24</v>
       </c>
       <c r="H336" t="n">
-        <v>0.2752</v>
+        <v>0.2751</v>
       </c>
       <c r="I336" t="n">
-        <v>20.66</v>
+        <v>20.65</v>
       </c>
       <c r="J336" t="n">
         <v>1290.1</v>
@@ -15563,7 +15563,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C337" t="n">
         <v>1316</v>
@@ -15653,44 +15653,44 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C339" t="n">
-        <v>1310</v>
+        <v>1137</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Niagara</t>
+          <t>Bucknell</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>patriot</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G339" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H339" t="n">
         <v>0.2679</v>
       </c>
       <c r="I339" t="n">
-        <v>20.53</v>
+        <v>21.26</v>
       </c>
       <c r="J339" t="n">
-        <v>1293.8</v>
+        <v>1306</v>
       </c>
       <c r="K339" t="n">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="L339" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M339" t="n">
-        <v>345</v>
+        <v>328</v>
       </c>
     </row>
     <row r="340">
@@ -15698,44 +15698,44 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C340" t="n">
-        <v>1137</v>
+        <v>1310</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Bucknell</t>
+          <t>Niagara</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>patriot</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G340" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H340" t="n">
-        <v>0.2679</v>
+        <v>0.2677</v>
       </c>
       <c r="I340" t="n">
-        <v>21.25</v>
+        <v>20.52</v>
       </c>
       <c r="J340" t="n">
-        <v>1306</v>
+        <v>1293.8</v>
       </c>
       <c r="K340" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L340" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M340" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="341">
@@ -15813,7 +15813,7 @@
         <v>0.2661</v>
       </c>
       <c r="I342" t="n">
-        <v>18.92</v>
+        <v>18.91</v>
       </c>
       <c r="J342" t="n">
         <v>1276.6</v>
@@ -15855,10 +15855,10 @@
         <v>21</v>
       </c>
       <c r="H343" t="n">
-        <v>0.2637</v>
+        <v>0.2633</v>
       </c>
       <c r="I343" t="n">
-        <v>20.78</v>
+        <v>20.77</v>
       </c>
       <c r="J343" t="n">
         <v>1293.9</v>
@@ -15945,10 +15945,10 @@
         <v>22</v>
       </c>
       <c r="H345" t="n">
-        <v>0.2541</v>
+        <v>0.254</v>
       </c>
       <c r="I345" t="n">
-        <v>19.12</v>
+        <v>19.11</v>
       </c>
       <c r="J345" t="n">
         <v>1278.5</v>
@@ -15990,7 +15990,7 @@
         <v>20</v>
       </c>
       <c r="H346" t="n">
-        <v>0.2423</v>
+        <v>0.2422</v>
       </c>
       <c r="I346" t="n">
         <v>18.2</v>
@@ -16170,10 +16170,10 @@
         <v>23</v>
       </c>
       <c r="H350" t="n">
-        <v>0.2353</v>
+        <v>0.2354</v>
       </c>
       <c r="I350" t="n">
-        <v>17.64</v>
+        <v>17.65</v>
       </c>
       <c r="J350" t="n">
         <v>1216.3</v>
@@ -16260,7 +16260,7 @@
         <v>23</v>
       </c>
       <c r="H352" t="n">
-        <v>0.2309</v>
+        <v>0.2307</v>
       </c>
       <c r="I352" t="n">
         <v>18.18</v>
@@ -16283,7 +16283,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C353" t="n">
         <v>1354</v>
@@ -16305,10 +16305,10 @@
         <v>20</v>
       </c>
       <c r="H353" t="n">
-        <v>0.2278</v>
+        <v>0.2276</v>
       </c>
       <c r="I353" t="n">
-        <v>16.68</v>
+        <v>16.67</v>
       </c>
       <c r="J353" t="n">
         <v>1259.4</v>
@@ -16395,7 +16395,7 @@
         <v>21</v>
       </c>
       <c r="H355" t="n">
-        <v>0.2192</v>
+        <v>0.2191</v>
       </c>
       <c r="I355" t="n">
         <v>16.62</v>
@@ -16893,7 +16893,7 @@
         <v>0.1213</v>
       </c>
       <c r="I366" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J366" t="n">
         <v>1094.9</v>

--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -510,7 +510,7 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3275</v>
+        <v>3.3276</v>
       </c>
       <c r="I2" t="n">
         <v>95.09</v>
@@ -555,10 +555,10 @@
         <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2135</v>
+        <v>3.2153</v>
       </c>
       <c r="I3" t="n">
-        <v>92.55</v>
+        <v>92.56</v>
       </c>
       <c r="J3" t="n">
         <v>2253.6</v>
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1421</v>
+        <v>3.1422</v>
       </c>
       <c r="I4" t="n">
         <v>91.72</v>
@@ -645,7 +645,7 @@
         <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0872</v>
+        <v>3.0873</v>
       </c>
       <c r="I5" t="n">
         <v>92.79000000000001</v>
@@ -690,7 +690,7 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>3.025</v>
+        <v>3.0251</v>
       </c>
       <c r="I6" t="n">
         <v>91.59</v>
@@ -735,10 +735,10 @@
         <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9337</v>
+        <v>2.9341</v>
       </c>
       <c r="I7" t="n">
-        <v>90.40000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="J7" t="n">
         <v>2003.3</v>
@@ -780,7 +780,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>2.878</v>
+        <v>2.8781</v>
       </c>
       <c r="I8" t="n">
         <v>90.15000000000001</v>
@@ -825,10 +825,10 @@
         <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8543</v>
+        <v>2.8559</v>
       </c>
       <c r="I9" t="n">
-        <v>90.63</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>2061.6</v>
@@ -870,10 +870,10 @@
         <v>23</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8369</v>
+        <v>2.8355</v>
       </c>
       <c r="I10" t="n">
-        <v>88.56</v>
+        <v>88.55</v>
       </c>
       <c r="J10" t="n">
         <v>1955.6</v>
@@ -915,7 +915,7 @@
         <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8071</v>
+        <v>2.8072</v>
       </c>
       <c r="I11" t="n">
         <v>88.2</v>
@@ -960,7 +960,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>2.719</v>
+        <v>2.7191</v>
       </c>
       <c r="I12" t="n">
         <v>85.05</v>
@@ -1005,10 +1005,10 @@
         <v>23</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6809</v>
+        <v>2.6822</v>
       </c>
       <c r="I13" t="n">
-        <v>87.56</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>2064.2</v>
@@ -1050,7 +1050,7 @@
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6535</v>
+        <v>2.6533</v>
       </c>
       <c r="I14" t="n">
         <v>86.63</v>
@@ -1140,10 +1140,10 @@
         <v>23</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6173</v>
+        <v>2.617</v>
       </c>
       <c r="I16" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>1935.7</v>
@@ -1185,10 +1185,10 @@
         <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5844</v>
+        <v>2.583</v>
       </c>
       <c r="I17" t="n">
-        <v>86.72</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>1845.2</v>
@@ -1230,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5532</v>
+        <v>2.5533</v>
       </c>
       <c r="I18" t="n">
         <v>83.91</v>
@@ -1410,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5066</v>
+        <v>2.5067</v>
       </c>
       <c r="I22" t="n">
         <v>86.69</v>
@@ -1500,10 +1500,10 @@
         <v>24</v>
       </c>
       <c r="H24" t="n">
-        <v>2.434</v>
+        <v>2.4323</v>
       </c>
       <c r="I24" t="n">
-        <v>84.93000000000001</v>
+        <v>84.92</v>
       </c>
       <c r="J24" t="n">
         <v>1859.5</v>
@@ -1545,7 +1545,7 @@
         <v>22</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3755</v>
+        <v>2.3754</v>
       </c>
       <c r="I25" t="n">
         <v>82.27</v>
@@ -1635,7 +1635,7 @@
         <v>24</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3208</v>
+        <v>2.3209</v>
       </c>
       <c r="I27" t="n">
         <v>83.93000000000001</v>
@@ -1680,7 +1680,7 @@
         <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3191</v>
+        <v>2.3194</v>
       </c>
       <c r="I28" t="n">
         <v>83.26000000000001</v>
@@ -1773,7 +1773,7 @@
         <v>2.2923</v>
       </c>
       <c r="I30" t="n">
-        <v>82.44</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>1917.6</v>
@@ -1815,7 +1815,7 @@
         <v>24</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2393</v>
+        <v>2.2392</v>
       </c>
       <c r="I31" t="n">
         <v>83.63</v>
@@ -1860,10 +1860,10 @@
         <v>24</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2257</v>
+        <v>2.2215</v>
       </c>
       <c r="I32" t="n">
-        <v>81.27</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>1799.9</v>
@@ -1973,7 +1973,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" t="n">
         <v>1365</v>
@@ -1995,10 +1995,10 @@
         <v>24</v>
       </c>
       <c r="H35" t="n">
-        <v>2.1617</v>
+        <v>2.1567</v>
       </c>
       <c r="I35" t="n">
-        <v>82.27</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>1768.3</v>
@@ -2085,10 +2085,10 @@
         <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1347</v>
+        <v>2.1364</v>
       </c>
       <c r="I37" t="n">
-        <v>81.59</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>1761</v>
@@ -2130,7 +2130,7 @@
         <v>23</v>
       </c>
       <c r="H38" t="n">
-        <v>2.1021</v>
+        <v>2.102</v>
       </c>
       <c r="I38" t="n">
         <v>80.90000000000001</v>
@@ -2175,7 +2175,7 @@
         <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>2.0954</v>
+        <v>2.0955</v>
       </c>
       <c r="I39" t="n">
         <v>81.13</v>
@@ -2220,7 +2220,7 @@
         <v>22</v>
       </c>
       <c r="H40" t="n">
-        <v>2.0713</v>
+        <v>2.0714</v>
       </c>
       <c r="I40" t="n">
         <v>81.18000000000001</v>
@@ -2265,7 +2265,7 @@
         <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0307</v>
+        <v>2.0308</v>
       </c>
       <c r="I41" t="n">
         <v>79.06</v>
@@ -2313,7 +2313,7 @@
         <v>1.9944</v>
       </c>
       <c r="I42" t="n">
-        <v>78.86</v>
+        <v>78.87</v>
       </c>
       <c r="J42" t="n">
         <v>1703.7</v>
@@ -2358,7 +2358,7 @@
         <v>1.9865</v>
       </c>
       <c r="I43" t="n">
-        <v>80.09999999999999</v>
+        <v>80.11</v>
       </c>
       <c r="J43" t="n">
         <v>1694.4</v>
@@ -2490,7 +2490,7 @@
         <v>24</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9672</v>
+        <v>1.9673</v>
       </c>
       <c r="I46" t="n">
         <v>78.3</v>
@@ -2583,7 +2583,7 @@
         <v>1.9529</v>
       </c>
       <c r="I48" t="n">
-        <v>78.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="J48" t="n">
         <v>1738.3</v>
@@ -2625,10 +2625,10 @@
         <v>22</v>
       </c>
       <c r="H49" t="n">
-        <v>1.9451</v>
+        <v>1.9448</v>
       </c>
       <c r="I49" t="n">
-        <v>79.98999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="J49" t="n">
         <v>1711.8</v>
@@ -2670,7 +2670,7 @@
         <v>23</v>
       </c>
       <c r="H50" t="n">
-        <v>1.9169</v>
+        <v>1.917</v>
       </c>
       <c r="I50" t="n">
         <v>78.02</v>
@@ -2760,10 +2760,10 @@
         <v>22</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8869</v>
+        <v>1.8879</v>
       </c>
       <c r="I52" t="n">
-        <v>76.48</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>1757.5</v>
@@ -2805,10 +2805,10 @@
         <v>22</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8854</v>
+        <v>1.8851</v>
       </c>
       <c r="I53" t="n">
-        <v>77.62</v>
+        <v>77.61</v>
       </c>
       <c r="J53" t="n">
         <v>1820.5</v>
@@ -2985,7 +2985,7 @@
         <v>23</v>
       </c>
       <c r="H57" t="n">
-        <v>1.7899</v>
+        <v>1.79</v>
       </c>
       <c r="I57" t="n">
         <v>75.69</v>
@@ -3030,10 +3030,10 @@
         <v>23</v>
       </c>
       <c r="H58" t="n">
-        <v>1.7889</v>
+        <v>1.7896</v>
       </c>
       <c r="I58" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="J58" t="n">
         <v>1737.5</v>
@@ -3120,10 +3120,10 @@
         <v>23</v>
       </c>
       <c r="H60" t="n">
-        <v>1.773</v>
+        <v>1.7743</v>
       </c>
       <c r="I60" t="n">
-        <v>75.25</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>1718.7</v>
@@ -3165,10 +3165,10 @@
         <v>23</v>
       </c>
       <c r="H61" t="n">
-        <v>1.7642</v>
+        <v>1.7641</v>
       </c>
       <c r="I61" t="n">
-        <v>75.14</v>
+        <v>75.13</v>
       </c>
       <c r="J61" t="n">
         <v>1662</v>
@@ -3210,10 +3210,10 @@
         <v>24</v>
       </c>
       <c r="H62" t="n">
-        <v>1.73</v>
+        <v>1.7293</v>
       </c>
       <c r="I62" t="n">
-        <v>74.14</v>
+        <v>74.12</v>
       </c>
       <c r="J62" t="n">
         <v>1645.7</v>
@@ -3300,7 +3300,7 @@
         <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>1.6505</v>
+        <v>1.6514</v>
       </c>
       <c r="I64" t="n">
         <v>72.20999999999999</v>
@@ -3345,10 +3345,10 @@
         <v>23</v>
       </c>
       <c r="H65" t="n">
-        <v>1.6445</v>
+        <v>1.6459</v>
       </c>
       <c r="I65" t="n">
-        <v>73.79000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="J65" t="n">
         <v>1720.3</v>
@@ -3435,7 +3435,7 @@
         <v>24</v>
       </c>
       <c r="H67" t="n">
-        <v>1.6386</v>
+        <v>1.6387</v>
       </c>
       <c r="I67" t="n">
         <v>72.06999999999999</v>
@@ -3570,10 +3570,10 @@
         <v>23</v>
       </c>
       <c r="H70" t="n">
-        <v>1.6276</v>
+        <v>1.6277</v>
       </c>
       <c r="I70" t="n">
-        <v>71.91</v>
+        <v>71.92</v>
       </c>
       <c r="J70" t="n">
         <v>1775.2</v>
@@ -3615,7 +3615,7 @@
         <v>22</v>
       </c>
       <c r="H71" t="n">
-        <v>1.6267</v>
+        <v>1.6268</v>
       </c>
       <c r="I71" t="n">
         <v>72.68000000000001</v>
@@ -3660,7 +3660,7 @@
         <v>22</v>
       </c>
       <c r="H72" t="n">
-        <v>1.6238</v>
+        <v>1.6237</v>
       </c>
       <c r="I72" t="n">
         <v>72.34</v>
@@ -3750,7 +3750,7 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.5987</v>
+        <v>1.5988</v>
       </c>
       <c r="I74" t="n">
         <v>70.62</v>
@@ -3795,7 +3795,7 @@
         <v>23</v>
       </c>
       <c r="H75" t="n">
-        <v>1.5935</v>
+        <v>1.5936</v>
       </c>
       <c r="I75" t="n">
         <v>70.09999999999999</v>
@@ -3840,7 +3840,7 @@
         <v>27</v>
       </c>
       <c r="H76" t="n">
-        <v>1.5862</v>
+        <v>1.5863</v>
       </c>
       <c r="I76" t="n">
         <v>71.08</v>
@@ -3885,10 +3885,10 @@
         <v>22</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5609</v>
+        <v>1.5605</v>
       </c>
       <c r="I77" t="n">
-        <v>71.62</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>1736.5</v>
@@ -3930,10 +3930,10 @@
         <v>22</v>
       </c>
       <c r="H78" t="n">
-        <v>1.5125</v>
+        <v>1.5112</v>
       </c>
       <c r="I78" t="n">
-        <v>70.37</v>
+        <v>70.36</v>
       </c>
       <c r="J78" t="n">
         <v>1743</v>
@@ -3975,10 +3975,10 @@
         <v>22</v>
       </c>
       <c r="H79" t="n">
-        <v>1.4923</v>
+        <v>1.4939</v>
       </c>
       <c r="I79" t="n">
-        <v>70.22</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>1663.4</v>
@@ -4020,10 +4020,10 @@
         <v>23</v>
       </c>
       <c r="H80" t="n">
-        <v>1.4923</v>
+        <v>1.4933</v>
       </c>
       <c r="I80" t="n">
-        <v>68.65000000000001</v>
+        <v>68.66</v>
       </c>
       <c r="J80" t="n">
         <v>1675</v>
@@ -4065,10 +4065,10 @@
         <v>23</v>
       </c>
       <c r="H81" t="n">
-        <v>1.49</v>
+        <v>1.4897</v>
       </c>
       <c r="I81" t="n">
-        <v>68.59999999999999</v>
+        <v>68.59</v>
       </c>
       <c r="J81" t="n">
         <v>1624.1</v>
@@ -4110,10 +4110,10 @@
         <v>23</v>
       </c>
       <c r="H82" t="n">
-        <v>1.4879</v>
+        <v>1.4878</v>
       </c>
       <c r="I82" t="n">
-        <v>68.84999999999999</v>
+        <v>68.84</v>
       </c>
       <c r="J82" t="n">
         <v>1624.5</v>
@@ -4155,7 +4155,7 @@
         <v>23</v>
       </c>
       <c r="H83" t="n">
-        <v>1.48</v>
+        <v>1.4804</v>
       </c>
       <c r="I83" t="n">
         <v>70.39</v>
@@ -4200,10 +4200,10 @@
         <v>22</v>
       </c>
       <c r="H84" t="n">
-        <v>1.4666</v>
+        <v>1.4673</v>
       </c>
       <c r="I84" t="n">
-        <v>69.68000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="J84" t="n">
         <v>1724.1</v>
@@ -4290,10 +4290,10 @@
         <v>22</v>
       </c>
       <c r="H86" t="n">
-        <v>1.4586</v>
+        <v>1.4589</v>
       </c>
       <c r="I86" t="n">
-        <v>68.48999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="J86" t="n">
         <v>1717.3</v>
@@ -4470,7 +4470,7 @@
         <v>22</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4392</v>
+        <v>1.4389</v>
       </c>
       <c r="I90" t="n">
         <v>67.58</v>
@@ -4515,10 +4515,10 @@
         <v>21</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4368</v>
+        <v>1.4372</v>
       </c>
       <c r="I91" t="n">
-        <v>68.89</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J91" t="n">
         <v>1524.7</v>
@@ -4608,7 +4608,7 @@
         <v>1.4116</v>
       </c>
       <c r="I93" t="n">
-        <v>67.25</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="J93" t="n">
         <v>1583.1</v>
@@ -4650,7 +4650,7 @@
         <v>22</v>
       </c>
       <c r="H94" t="n">
-        <v>1.4021</v>
+        <v>1.402</v>
       </c>
       <c r="I94" t="n">
         <v>66.97</v>
@@ -4785,7 +4785,7 @@
         <v>24</v>
       </c>
       <c r="H97" t="n">
-        <v>1.365</v>
+        <v>1.3651</v>
       </c>
       <c r="I97" t="n">
         <v>66.56</v>
@@ -4830,10 +4830,10 @@
         <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>1.3647</v>
+        <v>1.3643</v>
       </c>
       <c r="I98" t="n">
-        <v>66.81</v>
+        <v>66.8</v>
       </c>
       <c r="J98" t="n">
         <v>1526.8</v>
@@ -4875,7 +4875,7 @@
         <v>22</v>
       </c>
       <c r="H99" t="n">
-        <v>1.332</v>
+        <v>1.3321</v>
       </c>
       <c r="I99" t="n">
         <v>65.25</v>
@@ -4920,7 +4920,7 @@
         <v>22</v>
       </c>
       <c r="H100" t="n">
-        <v>1.329</v>
+        <v>1.3292</v>
       </c>
       <c r="I100" t="n">
         <v>65.95999999999999</v>
@@ -5058,7 +5058,7 @@
         <v>1.3034</v>
       </c>
       <c r="I103" t="n">
-        <v>62.44</v>
+        <v>62.45</v>
       </c>
       <c r="J103" t="n">
         <v>1609.6</v>
@@ -5145,7 +5145,7 @@
         <v>23</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2939</v>
+        <v>1.2936</v>
       </c>
       <c r="I105" t="n">
         <v>64.05</v>
@@ -5190,7 +5190,7 @@
         <v>23</v>
       </c>
       <c r="H106" t="n">
-        <v>1.2671</v>
+        <v>1.267</v>
       </c>
       <c r="I106" t="n">
         <v>64.18000000000001</v>
@@ -5235,10 +5235,10 @@
         <v>23</v>
       </c>
       <c r="H107" t="n">
-        <v>1.2643</v>
+        <v>1.2647</v>
       </c>
       <c r="I107" t="n">
-        <v>64.48</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="J107" t="n">
         <v>1733.1</v>
@@ -5280,10 +5280,10 @@
         <v>24</v>
       </c>
       <c r="H108" t="n">
-        <v>1.2618</v>
+        <v>1.2617</v>
       </c>
       <c r="I108" t="n">
-        <v>63.49</v>
+        <v>63.48</v>
       </c>
       <c r="J108" t="n">
         <v>1621.6</v>
@@ -5325,10 +5325,10 @@
         <v>25</v>
       </c>
       <c r="H109" t="n">
-        <v>1.2537</v>
+        <v>1.2538</v>
       </c>
       <c r="I109" t="n">
-        <v>63.59</v>
+        <v>63.61</v>
       </c>
       <c r="J109" t="n">
         <v>1593.8</v>
@@ -5370,7 +5370,7 @@
         <v>22</v>
       </c>
       <c r="H110" t="n">
-        <v>1.2382</v>
+        <v>1.2383</v>
       </c>
       <c r="I110" t="n">
         <v>63.34</v>
@@ -5460,7 +5460,7 @@
         <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>1.2289</v>
+        <v>1.2293</v>
       </c>
       <c r="I112" t="n">
         <v>62.42</v>
@@ -5505,10 +5505,10 @@
         <v>23</v>
       </c>
       <c r="H113" t="n">
-        <v>1.2211</v>
+        <v>1.2214</v>
       </c>
       <c r="I113" t="n">
-        <v>62.8</v>
+        <v>62.81</v>
       </c>
       <c r="J113" t="n">
         <v>1577.8</v>
@@ -5550,10 +5550,10 @@
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>1.2207</v>
+        <v>1.2212</v>
       </c>
       <c r="I114" t="n">
-        <v>63.27</v>
+        <v>63.28</v>
       </c>
       <c r="J114" t="n">
         <v>1580.6</v>
@@ -5595,10 +5595,10 @@
         <v>23</v>
       </c>
       <c r="H115" t="n">
-        <v>1.181</v>
+        <v>1.1812</v>
       </c>
       <c r="I115" t="n">
-        <v>62.49</v>
+        <v>62.5</v>
       </c>
       <c r="J115" t="n">
         <v>1530.7</v>
@@ -5640,7 +5640,7 @@
         <v>26</v>
       </c>
       <c r="H116" t="n">
-        <v>1.1789</v>
+        <v>1.1794</v>
       </c>
       <c r="I116" t="n">
         <v>62.09</v>
@@ -5730,7 +5730,7 @@
         <v>22</v>
       </c>
       <c r="H118" t="n">
-        <v>1.1574</v>
+        <v>1.157</v>
       </c>
       <c r="I118" t="n">
         <v>61.03</v>
@@ -5798,44 +5798,44 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C120" t="n">
-        <v>1362</v>
+        <v>1268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>125</v>
       </c>
       <c r="G120" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H120" t="n">
-        <v>1.1457</v>
+        <v>1.1456</v>
       </c>
       <c r="I120" t="n">
-        <v>61.67</v>
+        <v>60.57</v>
       </c>
       <c r="J120" t="n">
-        <v>1559.9</v>
+        <v>1598.1</v>
       </c>
       <c r="K120" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="L120" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M120" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="121">
@@ -5843,44 +5843,44 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C121" t="n">
-        <v>1268</v>
+        <v>1362</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>125</v>
       </c>
       <c r="G121" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H121" t="n">
-        <v>1.1456</v>
+        <v>1.1455</v>
       </c>
       <c r="I121" t="n">
-        <v>60.57</v>
+        <v>61.67</v>
       </c>
       <c r="J121" t="n">
-        <v>1598.1</v>
+        <v>1559.9</v>
       </c>
       <c r="K121" t="n">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="L121" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="M121" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122">
@@ -6000,10 +6000,10 @@
         <v>24</v>
       </c>
       <c r="H124" t="n">
-        <v>1.1383</v>
+        <v>1.1381</v>
       </c>
       <c r="I124" t="n">
-        <v>59.19</v>
+        <v>59.18</v>
       </c>
       <c r="J124" t="n">
         <v>1473.5</v>
@@ -6045,7 +6045,7 @@
         <v>23</v>
       </c>
       <c r="H125" t="n">
-        <v>1.1314</v>
+        <v>1.1315</v>
       </c>
       <c r="I125" t="n">
         <v>61.48</v>
@@ -6135,10 +6135,10 @@
         <v>22</v>
       </c>
       <c r="H127" t="n">
-        <v>1.126</v>
+        <v>1.1265</v>
       </c>
       <c r="I127" t="n">
-        <v>61.16</v>
+        <v>61.17</v>
       </c>
       <c r="J127" t="n">
         <v>1570.6</v>
@@ -6270,10 +6270,10 @@
         <v>21</v>
       </c>
       <c r="H130" t="n">
-        <v>1.1031</v>
+        <v>1.1033</v>
       </c>
       <c r="I130" t="n">
-        <v>59.58</v>
+        <v>59.59</v>
       </c>
       <c r="J130" t="n">
         <v>1597</v>
@@ -6315,7 +6315,7 @@
         <v>21</v>
       </c>
       <c r="H131" t="n">
-        <v>1.0673</v>
+        <v>1.0674</v>
       </c>
       <c r="I131" t="n">
         <v>58.92</v>
@@ -6360,10 +6360,10 @@
         <v>22</v>
       </c>
       <c r="H132" t="n">
-        <v>1.0631</v>
+        <v>1.0629</v>
       </c>
       <c r="I132" t="n">
-        <v>59.12</v>
+        <v>59.1</v>
       </c>
       <c r="J132" t="n">
         <v>1454.8</v>
@@ -6630,7 +6630,7 @@
         <v>24</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0133</v>
+        <v>1.0134</v>
       </c>
       <c r="I138" t="n">
         <v>56.86</v>
@@ -6675,10 +6675,10 @@
         <v>23</v>
       </c>
       <c r="H139" t="n">
-        <v>1.0073</v>
+        <v>1.0076</v>
       </c>
       <c r="I139" t="n">
-        <v>55.97</v>
+        <v>55.98</v>
       </c>
       <c r="J139" t="n">
         <v>1483.2</v>
@@ -6765,10 +6765,10 @@
         <v>22</v>
       </c>
       <c r="H141" t="n">
-        <v>0.9933</v>
+        <v>0.9932</v>
       </c>
       <c r="I141" t="n">
-        <v>57.48</v>
+        <v>57.47</v>
       </c>
       <c r="J141" t="n">
         <v>1533.9</v>
@@ -6810,10 +6810,10 @@
         <v>22</v>
       </c>
       <c r="H142" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9857</v>
       </c>
       <c r="I142" t="n">
-        <v>57.16</v>
+        <v>57.17</v>
       </c>
       <c r="J142" t="n">
         <v>1481.5</v>
@@ -6900,10 +6900,10 @@
         <v>24</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9779</v>
+        <v>0.9778</v>
       </c>
       <c r="I144" t="n">
-        <v>53.17</v>
+        <v>53.16</v>
       </c>
       <c r="J144" t="n">
         <v>1395</v>
@@ -7038,7 +7038,7 @@
         <v>0.9575</v>
       </c>
       <c r="I147" t="n">
-        <v>54.49</v>
+        <v>54.5</v>
       </c>
       <c r="J147" t="n">
         <v>1456.8</v>
@@ -7080,7 +7080,7 @@
         <v>24</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9554</v>
+        <v>0.9555</v>
       </c>
       <c r="I148" t="n">
         <v>56.4</v>
@@ -7170,7 +7170,7 @@
         <v>21</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9479</v>
+        <v>0.9478</v>
       </c>
       <c r="I150" t="n">
         <v>55.22</v>
@@ -7260,7 +7260,7 @@
         <v>23</v>
       </c>
       <c r="H152" t="n">
-        <v>0.9328</v>
+        <v>0.9327</v>
       </c>
       <c r="I152" t="n">
         <v>54.44</v>
@@ -7350,10 +7350,10 @@
         <v>21</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9294</v>
+        <v>0.9293</v>
       </c>
       <c r="I154" t="n">
-        <v>52.05</v>
+        <v>52.04</v>
       </c>
       <c r="J154" t="n">
         <v>1458.1</v>
@@ -7395,10 +7395,10 @@
         <v>19</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9172</v>
       </c>
       <c r="I155" t="n">
-        <v>53.77</v>
+        <v>53.78</v>
       </c>
       <c r="J155" t="n">
         <v>1419.8</v>
@@ -7485,10 +7485,10 @@
         <v>23</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9045</v>
+        <v>0.9044</v>
       </c>
       <c r="I157" t="n">
-        <v>53.87</v>
+        <v>53.86</v>
       </c>
       <c r="J157" t="n">
         <v>1453.6</v>
@@ -7530,10 +7530,10 @@
         <v>22</v>
       </c>
       <c r="H158" t="n">
-        <v>0.903</v>
+        <v>0.9028</v>
       </c>
       <c r="I158" t="n">
-        <v>54.61</v>
+        <v>54.59</v>
       </c>
       <c r="J158" t="n">
         <v>1489.7</v>
@@ -7710,7 +7710,7 @@
         <v>21</v>
       </c>
       <c r="H162" t="n">
-        <v>0.8731</v>
+        <v>0.8732</v>
       </c>
       <c r="I162" t="n">
         <v>53.39</v>
@@ -7758,7 +7758,7 @@
         <v>0.8729</v>
       </c>
       <c r="I163" t="n">
-        <v>53.18</v>
+        <v>53.19</v>
       </c>
       <c r="J163" t="n">
         <v>1471.5</v>
@@ -7800,10 +7800,10 @@
         <v>22</v>
       </c>
       <c r="H164" t="n">
-        <v>0.8724</v>
+        <v>0.8726</v>
       </c>
       <c r="I164" t="n">
-        <v>52.56</v>
+        <v>52.57</v>
       </c>
       <c r="J164" t="n">
         <v>1420.6</v>
@@ -7845,10 +7845,10 @@
         <v>19</v>
       </c>
       <c r="H165" t="n">
-        <v>0.8709</v>
+        <v>0.8707</v>
       </c>
       <c r="I165" t="n">
-        <v>53.33</v>
+        <v>53.32</v>
       </c>
       <c r="J165" t="n">
         <v>1513.7</v>
@@ -7980,7 +7980,7 @@
         <v>23</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8527</v>
+        <v>0.8525</v>
       </c>
       <c r="I168" t="n">
         <v>52.61</v>
@@ -8025,7 +8025,7 @@
         <v>23</v>
       </c>
       <c r="H169" t="n">
-        <v>0.8438</v>
+        <v>0.8436</v>
       </c>
       <c r="I169" t="n">
         <v>52.17</v>
@@ -8073,7 +8073,7 @@
         <v>0.8378</v>
       </c>
       <c r="I170" t="n">
-        <v>51.86</v>
+        <v>51.85</v>
       </c>
       <c r="J170" t="n">
         <v>1464.9</v>
@@ -8295,7 +8295,7 @@
         <v>24</v>
       </c>
       <c r="H175" t="n">
-        <v>0.8177</v>
+        <v>0.8176</v>
       </c>
       <c r="I175" t="n">
         <v>51.49</v>
@@ -8475,10 +8475,10 @@
         <v>23</v>
       </c>
       <c r="H179" t="n">
-        <v>0.8004</v>
+        <v>0.8007</v>
       </c>
       <c r="I179" t="n">
-        <v>50.43</v>
+        <v>50.44</v>
       </c>
       <c r="J179" t="n">
         <v>1467</v>
@@ -8835,7 +8835,7 @@
         <v>25</v>
       </c>
       <c r="H187" t="n">
-        <v>0.7625</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="I187" t="n">
         <v>48.85</v>
@@ -8970,10 +8970,10 @@
         <v>19</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7478</v>
+        <v>0.7481</v>
       </c>
       <c r="I190" t="n">
-        <v>48.65</v>
+        <v>48.66</v>
       </c>
       <c r="J190" t="n">
         <v>1455.1</v>
@@ -9105,10 +9105,10 @@
         <v>22</v>
       </c>
       <c r="H193" t="n">
-        <v>0.7296</v>
+        <v>0.7297</v>
       </c>
       <c r="I193" t="n">
-        <v>44.82</v>
+        <v>44.83</v>
       </c>
       <c r="J193" t="n">
         <v>1376.2</v>
@@ -9150,10 +9150,10 @@
         <v>23</v>
       </c>
       <c r="H194" t="n">
-        <v>0.7236</v>
+        <v>0.7235</v>
       </c>
       <c r="I194" t="n">
-        <v>44.04</v>
+        <v>44.03</v>
       </c>
       <c r="J194" t="n">
         <v>1468.7</v>
@@ -9195,10 +9195,10 @@
         <v>24</v>
       </c>
       <c r="H195" t="n">
-        <v>0.7143</v>
+        <v>0.7146</v>
       </c>
       <c r="I195" t="n">
-        <v>46.7</v>
+        <v>46.72</v>
       </c>
       <c r="J195" t="n">
         <v>1505.9</v>
@@ -9240,10 +9240,10 @@
         <v>21</v>
       </c>
       <c r="H196" t="n">
-        <v>0.7137</v>
+        <v>0.7135</v>
       </c>
       <c r="I196" t="n">
-        <v>45.9</v>
+        <v>45.88</v>
       </c>
       <c r="J196" t="n">
         <v>1383.1</v>
@@ -9285,7 +9285,7 @@
         <v>22</v>
       </c>
       <c r="H197" t="n">
-        <v>0.7095</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="I197" t="n">
         <v>46.86</v>
@@ -9330,7 +9330,7 @@
         <v>20</v>
       </c>
       <c r="H198" t="n">
-        <v>0.7057</v>
+        <v>0.7055</v>
       </c>
       <c r="I198" t="n">
         <v>45.73</v>
@@ -9420,7 +9420,7 @@
         <v>24</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6957</v>
+        <v>0.6955</v>
       </c>
       <c r="I200" t="n">
         <v>46.21</v>
@@ -9443,7 +9443,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C201" t="n">
         <v>1150</v>
@@ -9468,7 +9468,7 @@
         <v>0.6947</v>
       </c>
       <c r="I201" t="n">
-        <v>46.21</v>
+        <v>46.2</v>
       </c>
       <c r="J201" t="n">
         <v>1437.1</v>
@@ -9513,7 +9513,7 @@
         <v>0.6936</v>
       </c>
       <c r="I202" t="n">
-        <v>46.03</v>
+        <v>46.04</v>
       </c>
       <c r="J202" t="n">
         <v>1478.9</v>
@@ -9555,7 +9555,7 @@
         <v>23</v>
       </c>
       <c r="H203" t="n">
-        <v>0.6901</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I203" t="n">
         <v>44.12</v>
@@ -9600,7 +9600,7 @@
         <v>23</v>
       </c>
       <c r="H204" t="n">
-        <v>0.6835</v>
+        <v>0.6833</v>
       </c>
       <c r="I204" t="n">
         <v>45.5</v>
@@ -9713,7 +9713,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C207" t="n">
         <v>1168</v>
@@ -9738,7 +9738,7 @@
         <v>0.6738</v>
       </c>
       <c r="I207" t="n">
-        <v>45.5</v>
+        <v>45.49</v>
       </c>
       <c r="J207" t="n">
         <v>1394</v>
@@ -9780,7 +9780,7 @@
         <v>21</v>
       </c>
       <c r="H208" t="n">
-        <v>0.671</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="I208" t="n">
         <v>44.73</v>
@@ -9915,7 +9915,7 @@
         <v>22</v>
       </c>
       <c r="H211" t="n">
-        <v>0.6624</v>
+        <v>0.6622</v>
       </c>
       <c r="I211" t="n">
         <v>45.12</v>
@@ -9960,7 +9960,7 @@
         <v>28</v>
       </c>
       <c r="H212" t="n">
-        <v>0.6549</v>
+        <v>0.6551</v>
       </c>
       <c r="I212" t="n">
         <v>43.46</v>
@@ -10005,10 +10005,10 @@
         <v>23</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6521</v>
+        <v>0.6519</v>
       </c>
       <c r="I213" t="n">
-        <v>43.01</v>
+        <v>42.99</v>
       </c>
       <c r="J213" t="n">
         <v>1378.7</v>
@@ -10095,10 +10095,10 @@
         <v>24</v>
       </c>
       <c r="H215" t="n">
-        <v>0.6333</v>
+        <v>0.6331</v>
       </c>
       <c r="I215" t="n">
-        <v>42.93</v>
+        <v>42.91</v>
       </c>
       <c r="J215" t="n">
         <v>1395</v>
@@ -10230,10 +10230,10 @@
         <v>23</v>
       </c>
       <c r="H218" t="n">
-        <v>0.6264</v>
+        <v>0.6262</v>
       </c>
       <c r="I218" t="n">
-        <v>43.54</v>
+        <v>43.53</v>
       </c>
       <c r="J218" t="n">
         <v>1427.8</v>
@@ -10275,10 +10275,10 @@
         <v>23</v>
       </c>
       <c r="H219" t="n">
-        <v>0.6218</v>
+        <v>0.6217</v>
       </c>
       <c r="I219" t="n">
-        <v>42.26</v>
+        <v>42.25</v>
       </c>
       <c r="J219" t="n">
         <v>1389</v>
@@ -10323,7 +10323,7 @@
         <v>0.6182</v>
       </c>
       <c r="I220" t="n">
-        <v>42.78</v>
+        <v>42.79</v>
       </c>
       <c r="J220" t="n">
         <v>1384.9</v>
@@ -10368,7 +10368,7 @@
         <v>0.6163</v>
       </c>
       <c r="I221" t="n">
-        <v>42.05</v>
+        <v>42.04</v>
       </c>
       <c r="J221" t="n">
         <v>1342</v>
@@ -10410,10 +10410,10 @@
         <v>25</v>
       </c>
       <c r="H222" t="n">
-        <v>0.612</v>
+        <v>0.6121</v>
       </c>
       <c r="I222" t="n">
-        <v>42.16</v>
+        <v>42.17</v>
       </c>
       <c r="J222" t="n">
         <v>1419.4</v>
@@ -10545,10 +10545,10 @@
         <v>22</v>
       </c>
       <c r="H225" t="n">
-        <v>0.6041</v>
+        <v>0.6038</v>
       </c>
       <c r="I225" t="n">
-        <v>42.37</v>
+        <v>42.33</v>
       </c>
       <c r="J225" t="n">
         <v>1462.5</v>
@@ -10590,10 +10590,10 @@
         <v>23</v>
       </c>
       <c r="H226" t="n">
-        <v>0.6029</v>
+        <v>0.603</v>
       </c>
       <c r="I226" t="n">
-        <v>39.15</v>
+        <v>39.16</v>
       </c>
       <c r="J226" t="n">
         <v>1383.2</v>
@@ -10680,10 +10680,10 @@
         <v>21</v>
       </c>
       <c r="H228" t="n">
-        <v>0.5945</v>
+        <v>0.5944</v>
       </c>
       <c r="I228" t="n">
-        <v>41.43</v>
+        <v>41.42</v>
       </c>
       <c r="J228" t="n">
         <v>1400.5</v>
@@ -10773,7 +10773,7 @@
         <v>0.589</v>
       </c>
       <c r="I230" t="n">
-        <v>41.03</v>
+        <v>41.02</v>
       </c>
       <c r="J230" t="n">
         <v>1458.8</v>
@@ -10860,10 +10860,10 @@
         <v>24</v>
       </c>
       <c r="H232" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5789</v>
       </c>
       <c r="I232" t="n">
-        <v>39.73</v>
+        <v>39.72</v>
       </c>
       <c r="J232" t="n">
         <v>1443</v>
@@ -10883,44 +10883,44 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C233" t="n">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Elon</t>
+          <t>Fairfield</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G233" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H233" t="n">
-        <v>0.5737</v>
+        <v>0.5738</v>
       </c>
       <c r="I233" t="n">
-        <v>40.55</v>
+        <v>38.93</v>
       </c>
       <c r="J233" t="n">
-        <v>1459.8</v>
+        <v>1438.6</v>
       </c>
       <c r="K233" t="n">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="L233" t="n">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="M233" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="234">
@@ -10928,44 +10928,44 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C234" t="n">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Fairfield</t>
+          <t>Elon</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G234" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H234" t="n">
         <v>0.5736</v>
       </c>
       <c r="I234" t="n">
-        <v>38.93</v>
+        <v>40.55</v>
       </c>
       <c r="J234" t="n">
-        <v>1438.6</v>
+        <v>1459.8</v>
       </c>
       <c r="K234" t="n">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="L234" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="M234" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235">
@@ -10995,7 +10995,7 @@
         <v>22</v>
       </c>
       <c r="H235" t="n">
-        <v>0.5648</v>
+        <v>0.5647</v>
       </c>
       <c r="I235" t="n">
         <v>40.58</v>
@@ -11223,7 +11223,7 @@
         <v>0.5508</v>
       </c>
       <c r="I240" t="n">
-        <v>38.43</v>
+        <v>38.44</v>
       </c>
       <c r="J240" t="n">
         <v>1364.3</v>
@@ -11310,10 +11310,10 @@
         <v>25</v>
       </c>
       <c r="H242" t="n">
-        <v>0.5334</v>
+        <v>0.5339</v>
       </c>
       <c r="I242" t="n">
-        <v>38.68</v>
+        <v>38.71</v>
       </c>
       <c r="J242" t="n">
         <v>1397.2</v>
@@ -11445,10 +11445,10 @@
         <v>23</v>
       </c>
       <c r="H245" t="n">
-        <v>0.5263</v>
+        <v>0.5264</v>
       </c>
       <c r="I245" t="n">
-        <v>37.79</v>
+        <v>37.8</v>
       </c>
       <c r="J245" t="n">
         <v>1404.7</v>
@@ -11490,10 +11490,10 @@
         <v>23</v>
       </c>
       <c r="H246" t="n">
-        <v>0.523</v>
+        <v>0.5229</v>
       </c>
       <c r="I246" t="n">
-        <v>38.8</v>
+        <v>38.79</v>
       </c>
       <c r="J246" t="n">
         <v>1361.4</v>
@@ -11583,7 +11583,7 @@
         <v>0.5124</v>
       </c>
       <c r="I248" t="n">
-        <v>37.67</v>
+        <v>37.66</v>
       </c>
       <c r="J248" t="n">
         <v>1381.3</v>
@@ -11628,7 +11628,7 @@
         <v>0.511</v>
       </c>
       <c r="I249" t="n">
-        <v>36.63</v>
+        <v>36.62</v>
       </c>
       <c r="J249" t="n">
         <v>1355.7</v>
@@ -11760,10 +11760,10 @@
         <v>21</v>
       </c>
       <c r="H252" t="n">
-        <v>0.5064</v>
+        <v>0.5065</v>
       </c>
       <c r="I252" t="n">
-        <v>34.97</v>
+        <v>34.98</v>
       </c>
       <c r="J252" t="n">
         <v>1393.4</v>
@@ -11898,7 +11898,7 @@
         <v>0.496</v>
       </c>
       <c r="I255" t="n">
-        <v>36.92</v>
+        <v>36.91</v>
       </c>
       <c r="J255" t="n">
         <v>1373.2</v>
@@ -12030,10 +12030,10 @@
         <v>23</v>
       </c>
       <c r="H258" t="n">
-        <v>0.4878</v>
+        <v>0.488</v>
       </c>
       <c r="I258" t="n">
-        <v>36.23</v>
+        <v>36.24</v>
       </c>
       <c r="J258" t="n">
         <v>1418.8</v>
@@ -12303,7 +12303,7 @@
         <v>0.4575</v>
       </c>
       <c r="I264" t="n">
-        <v>34.34</v>
+        <v>34.35</v>
       </c>
       <c r="J264" t="n">
         <v>1346.8</v>
@@ -12348,7 +12348,7 @@
         <v>0.4573</v>
       </c>
       <c r="I265" t="n">
-        <v>33.17</v>
+        <v>33.16</v>
       </c>
       <c r="J265" t="n">
         <v>1388.7</v>
@@ -12435,10 +12435,10 @@
         <v>21</v>
       </c>
       <c r="H267" t="n">
-        <v>0.4526</v>
+        <v>0.4527</v>
       </c>
       <c r="I267" t="n">
-        <v>33.64</v>
+        <v>33.65</v>
       </c>
       <c r="J267" t="n">
         <v>1322.9</v>
@@ -12660,7 +12660,7 @@
         <v>23</v>
       </c>
       <c r="H272" t="n">
-        <v>0.4465</v>
+        <v>0.4464</v>
       </c>
       <c r="I272" t="n">
         <v>32.58</v>
@@ -12705,7 +12705,7 @@
         <v>23</v>
       </c>
       <c r="H273" t="n">
-        <v>0.4458</v>
+        <v>0.4457</v>
       </c>
       <c r="I273" t="n">
         <v>32.97</v>
@@ -12798,7 +12798,7 @@
         <v>0.4318</v>
       </c>
       <c r="I275" t="n">
-        <v>32.21</v>
+        <v>32.2</v>
       </c>
       <c r="J275" t="n">
         <v>1366.9</v>
@@ -12978,7 +12978,7 @@
         <v>0.4225</v>
       </c>
       <c r="I279" t="n">
-        <v>31.12</v>
+        <v>31.11</v>
       </c>
       <c r="J279" t="n">
         <v>1284</v>
@@ -12998,7 +12998,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C280" t="n">
         <v>1377</v>
@@ -13043,7 +13043,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C281" t="n">
         <v>1148</v>
@@ -13065,10 +13065,10 @@
         <v>23</v>
       </c>
       <c r="H281" t="n">
-        <v>0.4196</v>
+        <v>0.4199</v>
       </c>
       <c r="I281" t="n">
-        <v>30.48</v>
+        <v>30.52</v>
       </c>
       <c r="J281" t="n">
         <v>1451.5</v>
@@ -13110,10 +13110,10 @@
         <v>22</v>
       </c>
       <c r="H282" t="n">
-        <v>0.4192</v>
+        <v>0.4193</v>
       </c>
       <c r="I282" t="n">
-        <v>31.77</v>
+        <v>31.78</v>
       </c>
       <c r="J282" t="n">
         <v>1371.5</v>
@@ -13158,7 +13158,7 @@
         <v>0.4112</v>
       </c>
       <c r="I283" t="n">
-        <v>31.86</v>
+        <v>31.87</v>
       </c>
       <c r="J283" t="n">
         <v>1338.4</v>
@@ -13200,10 +13200,10 @@
         <v>24</v>
       </c>
       <c r="H284" t="n">
-        <v>0.4111</v>
+        <v>0.411</v>
       </c>
       <c r="I284" t="n">
-        <v>31.35</v>
+        <v>31.34</v>
       </c>
       <c r="J284" t="n">
         <v>1360</v>
@@ -13248,7 +13248,7 @@
         <v>0.408</v>
       </c>
       <c r="I285" t="n">
-        <v>31.45</v>
+        <v>31.46</v>
       </c>
       <c r="J285" t="n">
         <v>1327.5</v>
@@ -13383,7 +13383,7 @@
         <v>0.4021</v>
       </c>
       <c r="I288" t="n">
-        <v>29.22</v>
+        <v>29.23</v>
       </c>
       <c r="J288" t="n">
         <v>1322.2</v>
@@ -13608,7 +13608,7 @@
         <v>0.3892</v>
       </c>
       <c r="I293" t="n">
-        <v>29.54</v>
+        <v>29.55</v>
       </c>
       <c r="J293" t="n">
         <v>1361</v>
@@ -13653,7 +13653,7 @@
         <v>0.3882</v>
       </c>
       <c r="I294" t="n">
-        <v>30.67</v>
+        <v>30.66</v>
       </c>
       <c r="J294" t="n">
         <v>1308.8</v>
@@ -13698,7 +13698,7 @@
         <v>0.3845</v>
       </c>
       <c r="I295" t="n">
-        <v>29.14</v>
+        <v>29.15</v>
       </c>
       <c r="J295" t="n">
         <v>1323.1</v>
@@ -13740,10 +13740,10 @@
         <v>21</v>
       </c>
       <c r="H296" t="n">
-        <v>0.3813</v>
+        <v>0.3812</v>
       </c>
       <c r="I296" t="n">
-        <v>26.74</v>
+        <v>26.73</v>
       </c>
       <c r="J296" t="n">
         <v>1254.2</v>
@@ -13785,7 +13785,7 @@
         <v>16</v>
       </c>
       <c r="H297" t="n">
-        <v>0.379</v>
+        <v>0.3789</v>
       </c>
       <c r="I297" t="n">
         <v>29.59</v>
@@ -13965,10 +13965,10 @@
         <v>23</v>
       </c>
       <c r="H301" t="n">
-        <v>0.373</v>
+        <v>0.3729</v>
       </c>
       <c r="I301" t="n">
-        <v>29.2</v>
+        <v>29.19</v>
       </c>
       <c r="J301" t="n">
         <v>1388.3</v>
@@ -14013,7 +14013,7 @@
         <v>0.369</v>
       </c>
       <c r="I302" t="n">
-        <v>27.42</v>
+        <v>27.43</v>
       </c>
       <c r="J302" t="n">
         <v>1350.1</v>
@@ -14058,7 +14058,7 @@
         <v>0.3681</v>
       </c>
       <c r="I303" t="n">
-        <v>27.35</v>
+        <v>27.34</v>
       </c>
       <c r="J303" t="n">
         <v>1319.7</v>
@@ -14103,7 +14103,7 @@
         <v>0.368</v>
       </c>
       <c r="I304" t="n">
-        <v>28.41</v>
+        <v>28.4</v>
       </c>
       <c r="J304" t="n">
         <v>1326</v>
@@ -14193,7 +14193,7 @@
         <v>0.3614</v>
       </c>
       <c r="I306" t="n">
-        <v>25.14</v>
+        <v>25.13</v>
       </c>
       <c r="J306" t="n">
         <v>1379.4</v>
@@ -14238,7 +14238,7 @@
         <v>0.3608</v>
       </c>
       <c r="I307" t="n">
-        <v>27.02</v>
+        <v>27.03</v>
       </c>
       <c r="J307" t="n">
         <v>1333</v>
@@ -14283,7 +14283,7 @@
         <v>0.3583</v>
       </c>
       <c r="I308" t="n">
-        <v>25.59</v>
+        <v>25.6</v>
       </c>
       <c r="J308" t="n">
         <v>1289.8</v>
@@ -14325,10 +14325,10 @@
         <v>22</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3575</v>
+        <v>0.3576</v>
       </c>
       <c r="I309" t="n">
-        <v>26.77</v>
+        <v>26.78</v>
       </c>
       <c r="J309" t="n">
         <v>1310.9</v>
@@ -14438,23 +14438,23 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C312" t="n">
-        <v>1322</v>
+        <v>1174</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Northwestern LA</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>southland</t>
+          <t>cusa</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G312" t="n">
         <v>24</v>
@@ -14463,19 +14463,19 @@
         <v>0.3461</v>
       </c>
       <c r="I312" t="n">
-        <v>27.29</v>
+        <v>27.99</v>
       </c>
       <c r="J312" t="n">
-        <v>1286</v>
+        <v>1376.3</v>
       </c>
       <c r="K312" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="L312" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="M312" t="n">
-        <v>297</v>
+        <v>266</v>
       </c>
     </row>
     <row r="313">
@@ -14483,44 +14483,44 @@
         <v>312</v>
       </c>
       <c r="B313" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C313" t="n">
-        <v>1174</v>
+        <v>1322</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Northwestern LA</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>cusa</t>
+          <t>southland</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G313" t="n">
         <v>24</v>
       </c>
       <c r="H313" t="n">
-        <v>0.3461</v>
+        <v>0.3459</v>
       </c>
       <c r="I313" t="n">
-        <v>27.99</v>
+        <v>27.29</v>
       </c>
       <c r="J313" t="n">
-        <v>1376.3</v>
+        <v>1286</v>
       </c>
       <c r="K313" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="L313" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="M313" t="n">
-        <v>266</v>
+        <v>297</v>
       </c>
     </row>
     <row r="314">
@@ -14573,7 +14573,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C315" t="n">
         <v>1331</v>
@@ -14820,10 +14820,10 @@
         <v>23</v>
       </c>
       <c r="H320" t="n">
-        <v>0.33</v>
+        <v>0.3301</v>
       </c>
       <c r="I320" t="n">
-        <v>25.24</v>
+        <v>25.25</v>
       </c>
       <c r="J320" t="n">
         <v>1288.5</v>
@@ -14868,7 +14868,7 @@
         <v>0.3268</v>
       </c>
       <c r="I321" t="n">
-        <v>23.79</v>
+        <v>23.8</v>
       </c>
       <c r="J321" t="n">
         <v>1268.3</v>
@@ -15045,7 +15045,7 @@
         <v>23</v>
       </c>
       <c r="H325" t="n">
-        <v>0.3105</v>
+        <v>0.3101</v>
       </c>
       <c r="I325" t="n">
         <v>24.4</v>
@@ -15090,10 +15090,10 @@
         <v>23</v>
       </c>
       <c r="H326" t="n">
-        <v>0.3058</v>
+        <v>0.3057</v>
       </c>
       <c r="I326" t="n">
-        <v>22.62</v>
+        <v>22.61</v>
       </c>
       <c r="J326" t="n">
         <v>1265.1</v>
@@ -15135,10 +15135,10 @@
         <v>22</v>
       </c>
       <c r="H327" t="n">
-        <v>0.3027</v>
+        <v>0.3028</v>
       </c>
       <c r="I327" t="n">
-        <v>22.38</v>
+        <v>22.39</v>
       </c>
       <c r="J327" t="n">
         <v>1213.4</v>
@@ -15180,7 +15180,7 @@
         <v>24</v>
       </c>
       <c r="H328" t="n">
-        <v>0.2999</v>
+        <v>0.2998</v>
       </c>
       <c r="I328" t="n">
         <v>23.48</v>
@@ -15228,7 +15228,7 @@
         <v>0.2953</v>
       </c>
       <c r="I329" t="n">
-        <v>21.28</v>
+        <v>21.29</v>
       </c>
       <c r="J329" t="n">
         <v>1309</v>
@@ -15270,7 +15270,7 @@
         <v>22</v>
       </c>
       <c r="H330" t="n">
-        <v>0.2879</v>
+        <v>0.2878</v>
       </c>
       <c r="I330" t="n">
         <v>20.93</v>
@@ -15315,10 +15315,10 @@
         <v>23</v>
       </c>
       <c r="H331" t="n">
-        <v>0.287</v>
+        <v>0.2869</v>
       </c>
       <c r="I331" t="n">
-        <v>22.42</v>
+        <v>22.41</v>
       </c>
       <c r="J331" t="n">
         <v>1308.6</v>
@@ -15495,7 +15495,7 @@
         <v>22</v>
       </c>
       <c r="H335" t="n">
-        <v>0.281</v>
+        <v>0.2811</v>
       </c>
       <c r="I335" t="n">
         <v>21.33</v>
@@ -15543,7 +15543,7 @@
         <v>0.2755</v>
       </c>
       <c r="I336" t="n">
-        <v>21.62</v>
+        <v>21.63</v>
       </c>
       <c r="J336" t="n">
         <v>1256.8</v>
@@ -15630,7 +15630,7 @@
         <v>24</v>
       </c>
       <c r="H338" t="n">
-        <v>0.2722</v>
+        <v>0.2721</v>
       </c>
       <c r="I338" t="n">
         <v>21.65</v>
@@ -15855,10 +15855,10 @@
         <v>22</v>
       </c>
       <c r="H343" t="n">
-        <v>0.2616</v>
+        <v>0.2614</v>
       </c>
       <c r="I343" t="n">
-        <v>20.57</v>
+        <v>20.56</v>
       </c>
       <c r="J343" t="n">
         <v>1292.3</v>
@@ -15945,7 +15945,7 @@
         <v>22</v>
       </c>
       <c r="H345" t="n">
-        <v>0.2554</v>
+        <v>0.2553</v>
       </c>
       <c r="I345" t="n">
         <v>19.27</v>
@@ -15993,7 +15993,7 @@
         <v>0.2411</v>
       </c>
       <c r="I346" t="n">
-        <v>18.3</v>
+        <v>18.29</v>
       </c>
       <c r="J346" t="n">
         <v>1283.6</v>
@@ -16038,7 +16038,7 @@
         <v>0.2411</v>
       </c>
       <c r="I347" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="J347" t="n">
         <v>1234.7</v>
@@ -16215,10 +16215,10 @@
         <v>23</v>
       </c>
       <c r="H351" t="n">
-        <v>0.2342</v>
+        <v>0.2341</v>
       </c>
       <c r="I351" t="n">
-        <v>18.34</v>
+        <v>18.35</v>
       </c>
       <c r="J351" t="n">
         <v>1300.9</v>
@@ -16260,10 +16260,10 @@
         <v>21</v>
       </c>
       <c r="H352" t="n">
-        <v>0.2315</v>
+        <v>0.2316</v>
       </c>
       <c r="I352" t="n">
-        <v>18</v>
+        <v>18.01</v>
       </c>
       <c r="J352" t="n">
         <v>1323.3</v>
@@ -16485,10 +16485,10 @@
         <v>21</v>
       </c>
       <c r="H357" t="n">
-        <v>0.21</v>
+        <v>0.2099</v>
       </c>
       <c r="I357" t="n">
-        <v>18.38</v>
+        <v>18.37</v>
       </c>
       <c r="J357" t="n">
         <v>1280.3</v>
@@ -16665,7 +16665,7 @@
         <v>21</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1796</v>
+        <v>0.1797</v>
       </c>
       <c r="I361" t="n">
         <v>12.75</v>
@@ -16848,7 +16848,7 @@
         <v>0.1463</v>
       </c>
       <c r="I365" t="n">
-        <v>12.24</v>
+        <v>12.23</v>
       </c>
       <c r="J365" t="n">
         <v>1245.7</v>

--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MR_Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>EWP_Rank</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Conf</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N_games</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MR_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Exp_Wins_pct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Elo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>POM</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MAS</t>
         </is>

--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2084</v>
+        <v>3.2126</v>
       </c>
       <c r="I2" t="n">
-        <v>92.63</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2278.5</v>
+        <v>2286.8</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -555,10 +555,10 @@
         <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1349</v>
+        <v>3.1226</v>
       </c>
       <c r="I3" t="n">
-        <v>92.48999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="J3" t="n">
         <v>2203.3</v>
@@ -600,7 +600,7 @@
         <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1114</v>
+        <v>3.1088</v>
       </c>
       <c r="I4" t="n">
         <v>92.76000000000001</v>
@@ -645,10 +645,10 @@
         <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0867</v>
+        <v>3.0858</v>
       </c>
       <c r="I5" t="n">
-        <v>93.29000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="J5" t="n">
         <v>2057.2</v>
@@ -690,7 +690,7 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0689</v>
+        <v>3.065</v>
       </c>
       <c r="I6" t="n">
         <v>91.04000000000001</v>
@@ -713,44 +713,44 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1345</v>
+        <v>1196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0048</v>
+        <v>3.0002</v>
       </c>
       <c r="I7" t="n">
-        <v>90.76000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2023.2</v>
+        <v>2007.2</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -758,44 +758,44 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0024</v>
+        <v>2.9807</v>
       </c>
       <c r="I8" t="n">
-        <v>91.76000000000001</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2007.2</v>
+        <v>2037.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9318</v>
+        <v>2.9411</v>
       </c>
       <c r="I9" t="n">
-        <v>90.81999999999999</v>
+        <v>90.77</v>
       </c>
       <c r="J9" t="n">
-        <v>1997.8</v>
+        <v>2033.1</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
@@ -870,7 +870,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8108</v>
+        <v>2.8088</v>
       </c>
       <c r="I10" t="n">
         <v>90.14</v>
@@ -915,7 +915,7 @@
         <v>27</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7439</v>
+        <v>2.7417</v>
       </c>
       <c r="I11" t="n">
         <v>87.69</v>
@@ -1005,10 +1005,10 @@
         <v>28</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6629</v>
+        <v>2.6625</v>
       </c>
       <c r="I13" t="n">
-        <v>84.93000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="J13" t="n">
         <v>1985.7</v>
@@ -1050,10 +1050,10 @@
         <v>29</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6591</v>
+        <v>2.6567</v>
       </c>
       <c r="I14" t="n">
-        <v>87.70999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="J14" t="n">
         <v>2068.6</v>
@@ -1095,10 +1095,10 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6385</v>
+        <v>2.6424</v>
       </c>
       <c r="I15" t="n">
-        <v>88.13</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>2014.7</v>
@@ -1140,10 +1140,10 @@
         <v>27</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6326</v>
+        <v>2.6379</v>
       </c>
       <c r="I16" t="n">
-        <v>87.8</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>1945</v>
@@ -1185,7 +1185,7 @@
         <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5742</v>
+        <v>2.5726</v>
       </c>
       <c r="I17" t="n">
         <v>87.93000000000001</v>
@@ -1230,10 +1230,10 @@
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5625</v>
+        <v>2.5562</v>
       </c>
       <c r="I18" t="n">
-        <v>83.95</v>
+        <v>83.94</v>
       </c>
       <c r="J18" t="n">
         <v>1988.1</v>
@@ -1275,10 +1275,10 @@
         <v>26</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5016</v>
+        <v>2.4988</v>
       </c>
       <c r="I19" t="n">
-        <v>85.45999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="J19" t="n">
         <v>2018.6</v>
@@ -1320,10 +1320,10 @@
         <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>2.491</v>
+        <v>2.4856</v>
       </c>
       <c r="I20" t="n">
-        <v>85.47</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>1854.1</v>
@@ -1365,10 +1365,10 @@
         <v>27</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4259</v>
+        <v>2.4215</v>
       </c>
       <c r="I21" t="n">
-        <v>84.83</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>2012.5</v>
@@ -1410,7 +1410,7 @@
         <v>28</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4145</v>
+        <v>2.4131</v>
       </c>
       <c r="I22" t="n">
         <v>82.73</v>
@@ -1433,44 +1433,44 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>1388</v>
+        <v>1458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>136</v>
       </c>
       <c r="G23" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4092</v>
+        <v>2.4079</v>
       </c>
       <c r="I23" t="n">
-        <v>85.48999999999999</v>
+        <v>84.67</v>
       </c>
       <c r="J23" t="n">
-        <v>1857.8</v>
+        <v>1882.4</v>
       </c>
       <c r="K23" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" t="n">
         <v>22</v>
       </c>
-      <c r="L23" t="n">
-        <v>24</v>
-      </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1478,44 +1478,44 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>1458</v>
+        <v>1388</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>136</v>
       </c>
       <c r="G24" t="n">
+        <v>24</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.4045</v>
+      </c>
+      <c r="I24" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1857.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>22</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24</v>
+      </c>
+      <c r="M24" t="n">
         <v>28</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.4087</v>
-      </c>
-      <c r="I24" t="n">
-        <v>84.67</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1882.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22</v>
-      </c>
-      <c r="M24" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1545,7 +1545,7 @@
         <v>29</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4052</v>
+        <v>2.4039</v>
       </c>
       <c r="I25" t="n">
         <v>85.77</v>
@@ -1584,19 +1584,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3511</v>
+        <v>2.36</v>
       </c>
       <c r="I26" t="n">
-        <v>82.94</v>
+        <v>83.09</v>
       </c>
       <c r="J26" t="n">
-        <v>1896.9</v>
+        <v>1916.7</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
@@ -1635,7 +1635,7 @@
         <v>29</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3159</v>
+        <v>2.3157</v>
       </c>
       <c r="I27" t="n">
         <v>83.89</v>
@@ -1680,10 +1680,10 @@
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2949</v>
+        <v>2.2954</v>
       </c>
       <c r="I28" t="n">
-        <v>81.29000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="J28" t="n">
         <v>1979.2</v>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2606</v>
+        <v>2.2582</v>
       </c>
       <c r="I29" t="n">
         <v>81.51000000000001</v>
@@ -1815,7 +1815,7 @@
         <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2212</v>
+        <v>2.2189</v>
       </c>
       <c r="I31" t="n">
         <v>81.56</v>
@@ -1860,7 +1860,7 @@
         <v>24</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2124</v>
+        <v>2.2115</v>
       </c>
       <c r="I32" t="n">
         <v>81.67</v>
@@ -1905,7 +1905,7 @@
         <v>28</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1718</v>
+        <v>2.1674</v>
       </c>
       <c r="I33" t="n">
         <v>78.73999999999999</v>
@@ -1950,7 +1950,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1268</v>
+        <v>2.1267</v>
       </c>
       <c r="I34" t="n">
         <v>81.79000000000001</v>
@@ -1995,7 +1995,7 @@
         <v>28</v>
       </c>
       <c r="H35" t="n">
-        <v>2.1149</v>
+        <v>2.1144</v>
       </c>
       <c r="I35" t="n">
         <v>81.09</v>
@@ -2040,10 +2040,10 @@
         <v>25</v>
       </c>
       <c r="H36" t="n">
-        <v>2.0958</v>
+        <v>2.0939</v>
       </c>
       <c r="I36" t="n">
-        <v>81.36</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>1852.8</v>
@@ -2063,44 +2063,44 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C37" t="n">
-        <v>1274</v>
+        <v>1328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G37" t="n">
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>2.0829</v>
+        <v>2.0801</v>
       </c>
       <c r="I37" t="n">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>1794.7</v>
+        <v>1729</v>
       </c>
       <c r="K37" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -2108,44 +2108,44 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>1328</v>
+        <v>1274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G38" t="n">
         <v>26</v>
       </c>
       <c r="H38" t="n">
-        <v>2.0809</v>
+        <v>2.0792</v>
       </c>
       <c r="I38" t="n">
-        <v>80.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>1729</v>
+        <v>1794.7</v>
       </c>
       <c r="K38" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -2175,7 +2175,7 @@
         <v>26</v>
       </c>
       <c r="H39" t="n">
-        <v>2.0635</v>
+        <v>2.0625</v>
       </c>
       <c r="I39" t="n">
         <v>81.39</v>
@@ -2220,10 +2220,10 @@
         <v>26</v>
       </c>
       <c r="H40" t="n">
-        <v>2.0559</v>
+        <v>2.0579</v>
       </c>
       <c r="I40" t="n">
-        <v>80.98</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>1806.3</v>
@@ -2265,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0549</v>
+        <v>2.0539</v>
       </c>
       <c r="I41" t="n">
         <v>80.66</v>
@@ -2310,7 +2310,7 @@
         <v>27</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0487</v>
+        <v>2.0479</v>
       </c>
       <c r="I42" t="n">
         <v>78.67</v>
@@ -2355,7 +2355,7 @@
         <v>28</v>
       </c>
       <c r="H43" t="n">
-        <v>2.0186</v>
+        <v>2.0176</v>
       </c>
       <c r="I43" t="n">
         <v>80.53</v>
@@ -2400,7 +2400,7 @@
         <v>28</v>
       </c>
       <c r="H44" t="n">
-        <v>1.988</v>
+        <v>1.9872</v>
       </c>
       <c r="I44" t="n">
         <v>79.66</v>
@@ -2423,44 +2423,44 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G45" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9735</v>
+        <v>1.9719</v>
       </c>
       <c r="I45" t="n">
-        <v>80.48999999999999</v>
+        <v>79.09</v>
       </c>
       <c r="J45" t="n">
-        <v>1723.5</v>
+        <v>1733.9</v>
       </c>
       <c r="K45" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L45" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M45" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -2468,44 +2468,44 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C46" t="n">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H46" t="n">
-        <v>1.973</v>
+        <v>1.9694</v>
       </c>
       <c r="I46" t="n">
-        <v>79.09999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="J46" t="n">
-        <v>1733.9</v>
+        <v>1723.5</v>
       </c>
       <c r="K46" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M46" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47">
@@ -2535,10 +2535,10 @@
         <v>27</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9432</v>
+        <v>1.9376</v>
       </c>
       <c r="I47" t="n">
-        <v>77.95999999999999</v>
+        <v>77.94</v>
       </c>
       <c r="J47" t="n">
         <v>1734</v>
@@ -2580,7 +2580,7 @@
         <v>25</v>
       </c>
       <c r="H48" t="n">
-        <v>1.9122</v>
+        <v>1.9105</v>
       </c>
       <c r="I48" t="n">
         <v>76.58</v>
@@ -2625,7 +2625,7 @@
         <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8948</v>
+        <v>1.894</v>
       </c>
       <c r="I49" t="n">
         <v>75.05</v>
@@ -2670,7 +2670,7 @@
         <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>1.8548</v>
+        <v>1.8565</v>
       </c>
       <c r="I50" t="n">
         <v>77.37</v>
@@ -2715,7 +2715,7 @@
         <v>26</v>
       </c>
       <c r="H51" t="n">
-        <v>1.8475</v>
+        <v>1.8466</v>
       </c>
       <c r="I51" t="n">
         <v>76.81999999999999</v>
@@ -2760,7 +2760,7 @@
         <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8377</v>
+        <v>1.837</v>
       </c>
       <c r="I52" t="n">
         <v>75.67</v>
@@ -2783,44 +2783,44 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C53" t="n">
-        <v>1153</v>
+        <v>1103</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>big_twelve</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8307</v>
+        <v>1.8309</v>
       </c>
       <c r="I53" t="n">
-        <v>75.72</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>1728.9</v>
+        <v>1707.9</v>
       </c>
       <c r="K53" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L53" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="M53" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
@@ -2828,44 +2828,44 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C54" t="n">
-        <v>1103</v>
+        <v>1153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>mac</t>
+          <t>big_twelve</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>1.8295</v>
+        <v>1.8297</v>
       </c>
       <c r="I54" t="n">
-        <v>77.14</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>1707.9</v>
+        <v>1728.9</v>
       </c>
       <c r="K54" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L54" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -2873,7 +2873,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" t="n">
         <v>1452</v>
@@ -2895,10 +2895,10 @@
         <v>24</v>
       </c>
       <c r="H55" t="n">
-        <v>1.7882</v>
+        <v>1.7913</v>
       </c>
       <c r="I55" t="n">
-        <v>75.54000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="J55" t="n">
         <v>1710.3</v>
@@ -2940,7 +2940,7 @@
         <v>26</v>
       </c>
       <c r="H56" t="n">
-        <v>1.7644</v>
+        <v>1.7657</v>
       </c>
       <c r="I56" t="n">
         <v>75.09</v>
@@ -2985,7 +2985,7 @@
         <v>25</v>
       </c>
       <c r="H57" t="n">
-        <v>1.7631</v>
+        <v>1.764</v>
       </c>
       <c r="I57" t="n">
         <v>75.56</v>
@@ -3030,7 +3030,7 @@
         <v>26</v>
       </c>
       <c r="H58" t="n">
-        <v>1.7621</v>
+        <v>1.7614</v>
       </c>
       <c r="I58" t="n">
         <v>74.90000000000001</v>
@@ -3075,7 +3075,7 @@
         <v>23</v>
       </c>
       <c r="H59" t="n">
-        <v>1.7572</v>
+        <v>1.7583</v>
       </c>
       <c r="I59" t="n">
         <v>75.47</v>
@@ -3120,10 +3120,10 @@
         <v>24</v>
       </c>
       <c r="H60" t="n">
-        <v>1.7515</v>
+        <v>1.7507</v>
       </c>
       <c r="I60" t="n">
-        <v>75.27</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>1750</v>
@@ -3165,10 +3165,10 @@
         <v>24</v>
       </c>
       <c r="H61" t="n">
-        <v>1.684</v>
+        <v>1.6854</v>
       </c>
       <c r="I61" t="n">
-        <v>73.53</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>1737.5</v>
@@ -3210,7 +3210,7 @@
         <v>27</v>
       </c>
       <c r="H62" t="n">
-        <v>1.6766</v>
+        <v>1.6762</v>
       </c>
       <c r="I62" t="n">
         <v>72.88</v>
@@ -3255,7 +3255,7 @@
         <v>28</v>
       </c>
       <c r="H63" t="n">
-        <v>1.6649</v>
+        <v>1.6642</v>
       </c>
       <c r="I63" t="n">
         <v>74.91</v>
@@ -3278,44 +3278,44 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>1455</v>
+        <v>1321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G64" t="n">
         <v>27</v>
       </c>
       <c r="H64" t="n">
-        <v>1.6593</v>
+        <v>1.6611</v>
       </c>
       <c r="I64" t="n">
-        <v>73.56999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="J64" t="n">
-        <v>1659</v>
+        <v>1607</v>
       </c>
       <c r="K64" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="L64" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="M64" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -3323,44 +3323,44 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C65" t="n">
-        <v>1321</v>
+        <v>1455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G65" t="n">
         <v>27</v>
       </c>
       <c r="H65" t="n">
-        <v>1.659</v>
+        <v>1.6586</v>
       </c>
       <c r="I65" t="n">
-        <v>72.18000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="J65" t="n">
-        <v>1607</v>
+        <v>1659</v>
       </c>
       <c r="K65" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L65" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="M65" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66">
@@ -3390,7 +3390,7 @@
         <v>26</v>
       </c>
       <c r="H66" t="n">
-        <v>1.6567</v>
+        <v>1.658</v>
       </c>
       <c r="I66" t="n">
         <v>73.14</v>
@@ -3435,7 +3435,7 @@
         <v>24</v>
       </c>
       <c r="H67" t="n">
-        <v>1.6566</v>
+        <v>1.6561</v>
       </c>
       <c r="I67" t="n">
         <v>73.43000000000001</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="H68" t="n">
-        <v>1.6474</v>
+        <v>1.6483</v>
       </c>
       <c r="I68" t="n">
         <v>72.03</v>
@@ -3525,7 +3525,7 @@
         <v>28</v>
       </c>
       <c r="H69" t="n">
-        <v>1.6418</v>
+        <v>1.6415</v>
       </c>
       <c r="I69" t="n">
         <v>73.34</v>
@@ -3570,10 +3570,10 @@
         <v>26</v>
       </c>
       <c r="H70" t="n">
-        <v>1.6359</v>
+        <v>1.6318</v>
       </c>
       <c r="I70" t="n">
-        <v>72.90000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="J70" t="n">
         <v>1664.3</v>
@@ -3615,7 +3615,7 @@
         <v>25</v>
       </c>
       <c r="H71" t="n">
-        <v>1.6204</v>
+        <v>1.6194</v>
       </c>
       <c r="I71" t="n">
         <v>71.73999999999999</v>
@@ -3660,10 +3660,10 @@
         <v>21</v>
       </c>
       <c r="H72" t="n">
-        <v>1.6077</v>
+        <v>1.6086</v>
       </c>
       <c r="I72" t="n">
-        <v>72.65000000000001</v>
+        <v>72.66</v>
       </c>
       <c r="J72" t="n">
         <v>1707.2</v>
@@ -3705,7 +3705,7 @@
         <v>25</v>
       </c>
       <c r="H73" t="n">
-        <v>1.6054</v>
+        <v>1.6052</v>
       </c>
       <c r="I73" t="n">
         <v>71.75</v>
@@ -3750,10 +3750,10 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.5825</v>
+        <v>1.5806</v>
       </c>
       <c r="I74" t="n">
-        <v>72.76000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="J74" t="n">
         <v>1720.3</v>
@@ -3795,7 +3795,7 @@
         <v>28</v>
       </c>
       <c r="H75" t="n">
-        <v>1.572</v>
+        <v>1.5717</v>
       </c>
       <c r="I75" t="n">
         <v>70.87</v>
@@ -3840,7 +3840,7 @@
         <v>25</v>
       </c>
       <c r="H76" t="n">
-        <v>1.5706</v>
+        <v>1.5699</v>
       </c>
       <c r="I76" t="n">
         <v>69.26000000000001</v>
@@ -3885,7 +3885,7 @@
         <v>26</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5317</v>
+        <v>1.5312</v>
       </c>
       <c r="I77" t="n">
         <v>70.25</v>
@@ -3930,7 +3930,7 @@
         <v>28</v>
       </c>
       <c r="H78" t="n">
-        <v>1.5212</v>
+        <v>1.521</v>
       </c>
       <c r="I78" t="n">
         <v>70.89</v>
@@ -3975,7 +3975,7 @@
         <v>23</v>
       </c>
       <c r="H79" t="n">
-        <v>1.5076</v>
+        <v>1.5072</v>
       </c>
       <c r="I79" t="n">
         <v>70.41</v>
@@ -4020,7 +4020,7 @@
         <v>24</v>
       </c>
       <c r="H80" t="n">
-        <v>1.5076</v>
+        <v>1.5071</v>
       </c>
       <c r="I80" t="n">
         <v>68.78</v>
@@ -4065,7 +4065,7 @@
         <v>27</v>
       </c>
       <c r="H81" t="n">
-        <v>1.4536</v>
+        <v>1.4533</v>
       </c>
       <c r="I81" t="n">
         <v>68.17</v>
@@ -4110,10 +4110,10 @@
         <v>26</v>
       </c>
       <c r="H82" t="n">
-        <v>1.4494</v>
+        <v>1.451</v>
       </c>
       <c r="I82" t="n">
-        <v>66.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="J82" t="n">
         <v>1607.9</v>
@@ -4155,7 +4155,7 @@
         <v>24</v>
       </c>
       <c r="H83" t="n">
-        <v>1.447</v>
+        <v>1.4468</v>
       </c>
       <c r="I83" t="n">
         <v>67.5</v>
@@ -4200,7 +4200,7 @@
         <v>24</v>
       </c>
       <c r="H84" t="n">
-        <v>1.4464</v>
+        <v>1.4462</v>
       </c>
       <c r="I84" t="n">
         <v>67.70999999999999</v>
@@ -4245,7 +4245,7 @@
         <v>26</v>
       </c>
       <c r="H85" t="n">
-        <v>1.4434</v>
+        <v>1.4443</v>
       </c>
       <c r="I85" t="n">
         <v>67.40000000000001</v>
@@ -4290,7 +4290,7 @@
         <v>24</v>
       </c>
       <c r="H86" t="n">
-        <v>1.4335</v>
+        <v>1.4333</v>
       </c>
       <c r="I86" t="n">
         <v>67.77</v>
@@ -4335,7 +4335,7 @@
         <v>25</v>
       </c>
       <c r="H87" t="n">
-        <v>1.4258</v>
+        <v>1.4252</v>
       </c>
       <c r="I87" t="n">
         <v>67.94</v>
@@ -4380,7 +4380,7 @@
         <v>23</v>
       </c>
       <c r="H88" t="n">
-        <v>1.4144</v>
+        <v>1.4142</v>
       </c>
       <c r="I88" t="n">
         <v>66.95999999999999</v>
@@ -4425,10 +4425,10 @@
         <v>25</v>
       </c>
       <c r="H89" t="n">
-        <v>1.4116</v>
+        <v>1.4132</v>
       </c>
       <c r="I89" t="n">
-        <v>68.23</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>1546.5</v>
@@ -4448,44 +4448,44 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C90" t="n">
-        <v>1220</v>
+        <v>1143</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G90" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4109</v>
+        <v>1.4115</v>
       </c>
       <c r="I90" t="n">
-        <v>68.34</v>
+        <v>67.77</v>
       </c>
       <c r="J90" t="n">
-        <v>1586.2</v>
+        <v>1710.4</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="L90" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="M90" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91">
@@ -4493,44 +4493,44 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C91" t="n">
-        <v>1143</v>
+        <v>1220</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G91" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4098</v>
+        <v>1.4085</v>
       </c>
       <c r="I91" t="n">
-        <v>67.77</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>1710.4</v>
+        <v>1586.2</v>
       </c>
       <c r="K91" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L91" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="M91" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92">
@@ -4560,7 +4560,7 @@
         <v>24</v>
       </c>
       <c r="H92" t="n">
-        <v>1.4069</v>
+        <v>1.4067</v>
       </c>
       <c r="I92" t="n">
         <v>68.18000000000001</v>
@@ -4605,7 +4605,7 @@
         <v>24</v>
       </c>
       <c r="H93" t="n">
-        <v>1.4024</v>
+        <v>1.4021</v>
       </c>
       <c r="I93" t="n">
         <v>66.38</v>
@@ -4650,7 +4650,7 @@
         <v>24</v>
       </c>
       <c r="H94" t="n">
-        <v>1.3856</v>
+        <v>1.3854</v>
       </c>
       <c r="I94" t="n">
         <v>66.45</v>
@@ -4695,7 +4695,7 @@
         <v>24</v>
       </c>
       <c r="H95" t="n">
-        <v>1.3844</v>
+        <v>1.384</v>
       </c>
       <c r="I95" t="n">
         <v>66.89</v>
@@ -4740,10 +4740,10 @@
         <v>26</v>
       </c>
       <c r="H96" t="n">
-        <v>1.3748</v>
+        <v>1.3785</v>
       </c>
       <c r="I96" t="n">
-        <v>65.51000000000001</v>
+        <v>65.53</v>
       </c>
       <c r="J96" t="n">
         <v>1559.8</v>
@@ -4785,7 +4785,7 @@
         <v>25</v>
       </c>
       <c r="H97" t="n">
-        <v>1.3704</v>
+        <v>1.3703</v>
       </c>
       <c r="I97" t="n">
         <v>67.05</v>
@@ -4830,7 +4830,7 @@
         <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>1.3626</v>
+        <v>1.3623</v>
       </c>
       <c r="I98" t="n">
         <v>66.68000000000001</v>
@@ -4875,10 +4875,10 @@
         <v>24</v>
       </c>
       <c r="H99" t="n">
-        <v>1.3343</v>
+        <v>1.3326</v>
       </c>
       <c r="I99" t="n">
-        <v>65.45999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="J99" t="n">
         <v>1536.9</v>
@@ -4920,7 +4920,7 @@
         <v>26</v>
       </c>
       <c r="H100" t="n">
-        <v>1.3197</v>
+        <v>1.3206</v>
       </c>
       <c r="I100" t="n">
         <v>63.19</v>
@@ -4965,7 +4965,7 @@
         <v>24</v>
       </c>
       <c r="H101" t="n">
-        <v>1.3195</v>
+        <v>1.3191</v>
       </c>
       <c r="I101" t="n">
         <v>66.15000000000001</v>
@@ -4988,7 +4988,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" t="n">
         <v>1471</v>
@@ -5010,10 +5010,10 @@
         <v>25</v>
       </c>
       <c r="H102" t="n">
-        <v>1.3046</v>
+        <v>1.3055</v>
       </c>
       <c r="I102" t="n">
-        <v>61.89</v>
+        <v>61.9</v>
       </c>
       <c r="J102" t="n">
         <v>1612.4</v>
@@ -5055,10 +5055,10 @@
         <v>23</v>
       </c>
       <c r="H103" t="n">
-        <v>1.2925</v>
+        <v>1.2943</v>
       </c>
       <c r="I103" t="n">
-        <v>64.02</v>
+        <v>64.03</v>
       </c>
       <c r="J103" t="n">
         <v>1599.6</v>
@@ -5100,7 +5100,7 @@
         <v>26</v>
       </c>
       <c r="H104" t="n">
-        <v>1.2716</v>
+        <v>1.2712</v>
       </c>
       <c r="I104" t="n">
         <v>64.95999999999999</v>
@@ -5145,7 +5145,7 @@
         <v>27</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2606</v>
+        <v>1.2603</v>
       </c>
       <c r="I105" t="n">
         <v>64.42</v>
@@ -5190,7 +5190,7 @@
         <v>26</v>
       </c>
       <c r="H106" t="n">
-        <v>1.2574</v>
+        <v>1.2572</v>
       </c>
       <c r="I106" t="n">
         <v>63.45</v>
@@ -5235,7 +5235,7 @@
         <v>22</v>
       </c>
       <c r="H107" t="n">
-        <v>1.2565</v>
+        <v>1.2563</v>
       </c>
       <c r="I107" t="n">
         <v>63.92</v>
@@ -5280,10 +5280,10 @@
         <v>24</v>
       </c>
       <c r="H108" t="n">
-        <v>1.2518</v>
+        <v>1.2519</v>
       </c>
       <c r="I108" t="n">
-        <v>63.5</v>
+        <v>63.49</v>
       </c>
       <c r="J108" t="n">
         <v>1577.8</v>
@@ -5325,7 +5325,7 @@
         <v>24</v>
       </c>
       <c r="H109" t="n">
-        <v>1.2427</v>
+        <v>1.2423</v>
       </c>
       <c r="I109" t="n">
         <v>63.9</v>
@@ -5370,7 +5370,7 @@
         <v>28</v>
       </c>
       <c r="H110" t="n">
-        <v>1.2421</v>
+        <v>1.2417</v>
       </c>
       <c r="I110" t="n">
         <v>63.16</v>
@@ -5460,7 +5460,7 @@
         <v>26</v>
       </c>
       <c r="H112" t="n">
-        <v>1.2206</v>
+        <v>1.2204</v>
       </c>
       <c r="I112" t="n">
         <v>63.15</v>
@@ -5505,7 +5505,7 @@
         <v>24</v>
       </c>
       <c r="H113" t="n">
-        <v>1.1998</v>
+        <v>1.1993</v>
       </c>
       <c r="I113" t="n">
         <v>61.94</v>
@@ -5550,7 +5550,7 @@
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>1.1954</v>
+        <v>1.1953</v>
       </c>
       <c r="I114" t="n">
         <v>62.19</v>
@@ -5595,7 +5595,7 @@
         <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>1.1887</v>
+        <v>1.1884</v>
       </c>
       <c r="I115" t="n">
         <v>62.21</v>
@@ -5640,7 +5640,7 @@
         <v>24</v>
       </c>
       <c r="H116" t="n">
-        <v>1.1877</v>
+        <v>1.1875</v>
       </c>
       <c r="I116" t="n">
         <v>61.9</v>
@@ -5685,7 +5685,7 @@
         <v>23</v>
       </c>
       <c r="H117" t="n">
-        <v>1.183</v>
+        <v>1.1827</v>
       </c>
       <c r="I117" t="n">
         <v>61.09</v>
@@ -5730,7 +5730,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="n">
-        <v>1.1815</v>
+        <v>1.1813</v>
       </c>
       <c r="I118" t="n">
         <v>61.64</v>
@@ -5775,10 +5775,10 @@
         <v>23</v>
       </c>
       <c r="H119" t="n">
-        <v>1.1716</v>
+        <v>1.1729</v>
       </c>
       <c r="I119" t="n">
-        <v>60.15</v>
+        <v>60.16</v>
       </c>
       <c r="J119" t="n">
         <v>1562.6</v>
@@ -5820,7 +5820,7 @@
         <v>23</v>
       </c>
       <c r="H120" t="n">
-        <v>1.171</v>
+        <v>1.1708</v>
       </c>
       <c r="I120" t="n">
         <v>61.04</v>
@@ -5865,7 +5865,7 @@
         <v>25</v>
       </c>
       <c r="H121" t="n">
-        <v>1.1543</v>
+        <v>1.1539</v>
       </c>
       <c r="I121" t="n">
         <v>61.78</v>
@@ -5910,7 +5910,7 @@
         <v>24</v>
       </c>
       <c r="H122" t="n">
-        <v>1.1513</v>
+        <v>1.153</v>
       </c>
       <c r="I122" t="n">
         <v>59.38</v>
@@ -5955,7 +5955,7 @@
         <v>26</v>
       </c>
       <c r="H123" t="n">
-        <v>1.1469</v>
+        <v>1.149</v>
       </c>
       <c r="I123" t="n">
         <v>59.33</v>
@@ -6000,10 +6000,10 @@
         <v>25</v>
       </c>
       <c r="H124" t="n">
-        <v>1.1439</v>
+        <v>1.1469</v>
       </c>
       <c r="I124" t="n">
-        <v>59.62</v>
+        <v>59.63</v>
       </c>
       <c r="J124" t="n">
         <v>1556.9</v>
@@ -6023,44 +6023,44 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C125" t="n">
-        <v>1382</v>
+        <v>1218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>St Bonaventure</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>a_ten</t>
+          <t>big_west</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G125" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H125" t="n">
-        <v>1.1282</v>
+        <v>1.1285</v>
       </c>
       <c r="I125" t="n">
-        <v>61.04</v>
+        <v>60.8</v>
       </c>
       <c r="J125" t="n">
-        <v>1551.8</v>
+        <v>1549.1</v>
       </c>
       <c r="K125" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="L125" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="M125" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="126">
@@ -6068,44 +6068,44 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C126" t="n">
-        <v>1218</v>
+        <v>1382</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>St Bonaventure</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>big_west</t>
+          <t>a_ten</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G126" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H126" t="n">
-        <v>1.1276</v>
+        <v>1.1279</v>
       </c>
       <c r="I126" t="n">
-        <v>60.8</v>
+        <v>61.04</v>
       </c>
       <c r="J126" t="n">
-        <v>1549.1</v>
+        <v>1551.8</v>
       </c>
       <c r="K126" t="n">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="L126" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="M126" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="127">
@@ -6135,7 +6135,7 @@
         <v>27</v>
       </c>
       <c r="H127" t="n">
-        <v>1.1234</v>
+        <v>1.1233</v>
       </c>
       <c r="I127" t="n">
         <v>58.74</v>
@@ -6158,44 +6158,44 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C128" t="n">
-        <v>1133</v>
+        <v>1272</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>mvc</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F128" t="n">
+        <v>128</v>
+      </c>
+      <c r="G128" t="n">
+        <v>26</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="I128" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1567</v>
+      </c>
+      <c r="K128" t="n">
         <v>135</v>
       </c>
-      <c r="G128" t="n">
-        <v>24</v>
-      </c>
-      <c r="H128" t="n">
-        <v>1.1193</v>
-      </c>
-      <c r="I128" t="n">
-        <v>60.91</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1617.1</v>
-      </c>
-      <c r="K128" t="n">
-        <v>113</v>
-      </c>
       <c r="L128" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="M128" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129">
@@ -6203,44 +6203,44 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C129" t="n">
-        <v>1272</v>
+        <v>1133</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Bradley</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>mvc</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G129" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H129" t="n">
-        <v>1.1157</v>
+        <v>1.1168</v>
       </c>
       <c r="I129" t="n">
-        <v>60.48</v>
+        <v>60.9</v>
       </c>
       <c r="J129" t="n">
-        <v>1567</v>
+        <v>1617.1</v>
       </c>
       <c r="K129" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="L129" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="M129" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="130">
@@ -6360,7 +6360,7 @@
         <v>24</v>
       </c>
       <c r="H132" t="n">
-        <v>1.1016</v>
+        <v>1.1014</v>
       </c>
       <c r="I132" t="n">
         <v>60.44</v>
@@ -6405,7 +6405,7 @@
         <v>25</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0716</v>
+        <v>1.0712</v>
       </c>
       <c r="I133" t="n">
         <v>59.05</v>
@@ -6450,7 +6450,7 @@
         <v>24</v>
       </c>
       <c r="H134" t="n">
-        <v>1.0703</v>
+        <v>1.07</v>
       </c>
       <c r="I134" t="n">
         <v>58.9</v>
@@ -6585,7 +6585,7 @@
         <v>23</v>
       </c>
       <c r="H137" t="n">
-        <v>1.0571</v>
+        <v>1.0568</v>
       </c>
       <c r="I137" t="n">
         <v>57.86</v>
@@ -6630,10 +6630,10 @@
         <v>26</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0484</v>
+        <v>1.0505</v>
       </c>
       <c r="I138" t="n">
-        <v>54.81</v>
+        <v>54.82</v>
       </c>
       <c r="J138" t="n">
         <v>1397.4</v>
@@ -6675,7 +6675,7 @@
         <v>22</v>
       </c>
       <c r="H139" t="n">
-        <v>1.0279</v>
+        <v>1.0282</v>
       </c>
       <c r="I139" t="n">
         <v>55.74</v>
@@ -6720,7 +6720,7 @@
         <v>24</v>
       </c>
       <c r="H140" t="n">
-        <v>1.0111</v>
+        <v>1.011</v>
       </c>
       <c r="I140" t="n">
         <v>57.7</v>
@@ -6765,7 +6765,7 @@
         <v>24</v>
       </c>
       <c r="H141" t="n">
-        <v>1.0104</v>
+        <v>1.0102</v>
       </c>
       <c r="I141" t="n">
         <v>56.45</v>
@@ -6810,7 +6810,7 @@
         <v>24</v>
       </c>
       <c r="H142" t="n">
-        <v>1.0088</v>
+        <v>1.0085</v>
       </c>
       <c r="I142" t="n">
         <v>55.74</v>
@@ -6855,7 +6855,7 @@
         <v>23</v>
       </c>
       <c r="H143" t="n">
-        <v>1.0078</v>
+        <v>1.0077</v>
       </c>
       <c r="I143" t="n">
         <v>57.69</v>
@@ -6945,7 +6945,7 @@
         <v>24</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9937</v>
+        <v>0.9931</v>
       </c>
       <c r="I145" t="n">
         <v>55.37</v>
@@ -6990,7 +6990,7 @@
         <v>22</v>
       </c>
       <c r="H146" t="n">
-        <v>0.9867</v>
+        <v>0.9866</v>
       </c>
       <c r="I146" t="n">
         <v>55.71</v>
@@ -7035,7 +7035,7 @@
         <v>22</v>
       </c>
       <c r="H147" t="n">
-        <v>0.9853</v>
+        <v>0.985</v>
       </c>
       <c r="I147" t="n">
         <v>54.38</v>
@@ -7080,10 +7080,10 @@
         <v>22</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9695</v>
+        <v>0.9685</v>
       </c>
       <c r="I148" t="n">
-        <v>56.76</v>
+        <v>56.75</v>
       </c>
       <c r="J148" t="n">
         <v>1543.6</v>
@@ -7125,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="H149" t="n">
-        <v>0.9641</v>
+        <v>0.964</v>
       </c>
       <c r="I149" t="n">
         <v>55.93</v>
@@ -7148,7 +7148,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C150" t="n">
         <v>1426</v>
@@ -7170,7 +7170,7 @@
         <v>23</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9504</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="I150" t="n">
         <v>52.37</v>
@@ -7215,7 +7215,7 @@
         <v>22</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9479</v>
+        <v>0.9476</v>
       </c>
       <c r="I151" t="n">
         <v>54.85</v>
@@ -7260,10 +7260,10 @@
         <v>25</v>
       </c>
       <c r="H152" t="n">
-        <v>0.9356</v>
+        <v>0.9363</v>
       </c>
       <c r="I152" t="n">
-        <v>51.69</v>
+        <v>51.7</v>
       </c>
       <c r="J152" t="n">
         <v>1521.4</v>
@@ -7283,44 +7283,44 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C153" t="n">
-        <v>1398</v>
+        <v>1450</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Washington St</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F153" t="n">
+        <v>123</v>
+      </c>
+      <c r="G153" t="n">
+        <v>23</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.9111</v>
+      </c>
+      <c r="I153" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1458.2</v>
+      </c>
+      <c r="K153" t="n">
+        <v>146</v>
+      </c>
+      <c r="L153" t="n">
         <v>137</v>
       </c>
-      <c r="G153" t="n">
-        <v>25</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0.9105</v>
-      </c>
-      <c r="I153" t="n">
-        <v>52.37</v>
-      </c>
-      <c r="J153" t="n">
-        <v>1466.9</v>
-      </c>
-      <c r="K153" t="n">
-        <v>172</v>
-      </c>
-      <c r="L153" t="n">
-        <v>187</v>
-      </c>
       <c r="M153" t="n">
-        <v>185</v>
+        <v>143</v>
       </c>
     </row>
     <row r="154">
@@ -7328,44 +7328,44 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C154" t="n">
-        <v>1450</v>
+        <v>1398</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Washington St</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G154" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9104</v>
+        <v>0.9111</v>
       </c>
       <c r="I154" t="n">
-        <v>54.21</v>
+        <v>52.38</v>
       </c>
       <c r="J154" t="n">
-        <v>1458.2</v>
+        <v>1466.9</v>
       </c>
       <c r="K154" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="L154" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="M154" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155">
@@ -7395,7 +7395,7 @@
         <v>24</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9081</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="I155" t="n">
         <v>53.56</v>
@@ -7440,7 +7440,7 @@
         <v>25</v>
       </c>
       <c r="H156" t="n">
-        <v>0.9053</v>
+        <v>0.905</v>
       </c>
       <c r="I156" t="n">
         <v>53.63</v>
@@ -7485,7 +7485,7 @@
         <v>26</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9006</v>
+        <v>0.9002</v>
       </c>
       <c r="I157" t="n">
         <v>50.52</v>
@@ -7530,7 +7530,7 @@
         <v>24</v>
       </c>
       <c r="H158" t="n">
-        <v>0.894</v>
+        <v>0.8939</v>
       </c>
       <c r="I158" t="n">
         <v>51.07</v>
@@ -7575,7 +7575,7 @@
         <v>25</v>
       </c>
       <c r="H159" t="n">
-        <v>0.876</v>
+        <v>0.8759</v>
       </c>
       <c r="I159" t="n">
         <v>53.87</v>
@@ -7620,7 +7620,7 @@
         <v>24</v>
       </c>
       <c r="H160" t="n">
-        <v>0.8746</v>
+        <v>0.8747</v>
       </c>
       <c r="I160" t="n">
         <v>52.03</v>
@@ -7710,7 +7710,7 @@
         <v>22</v>
       </c>
       <c r="H162" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8671</v>
       </c>
       <c r="I162" t="n">
         <v>52.78</v>
@@ -7755,7 +7755,7 @@
         <v>23</v>
       </c>
       <c r="H163" t="n">
-        <v>0.8657</v>
+        <v>0.8656</v>
       </c>
       <c r="I163" t="n">
         <v>52.26</v>
@@ -7823,44 +7823,44 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C165" t="n">
-        <v>1158</v>
+        <v>1373</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Col Charleston</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G165" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H165" t="n">
-        <v>0.8559</v>
+        <v>0.8575</v>
       </c>
       <c r="I165" t="n">
-        <v>53.12</v>
+        <v>50.74</v>
       </c>
       <c r="J165" t="n">
-        <v>1578.3</v>
+        <v>1478</v>
       </c>
       <c r="K165" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="L165" t="n">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="M165" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="166">
@@ -7868,44 +7868,44 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C166" t="n">
-        <v>1373</v>
+        <v>1158</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Col Charleston</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G166" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H166" t="n">
-        <v>0.8527</v>
+        <v>0.8559</v>
       </c>
       <c r="I166" t="n">
-        <v>50.73</v>
+        <v>53.12</v>
       </c>
       <c r="J166" t="n">
-        <v>1478</v>
+        <v>1578.3</v>
       </c>
       <c r="K166" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="L166" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="M166" t="n">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="167">
@@ -7935,7 +7935,7 @@
         <v>23</v>
       </c>
       <c r="H167" t="n">
-        <v>0.8512</v>
+        <v>0.8535</v>
       </c>
       <c r="I167" t="n">
         <v>52.9</v>
@@ -7980,7 +7980,7 @@
         <v>22</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8444</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="I168" t="n">
         <v>52.4</v>
@@ -8048,44 +8048,44 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C170" t="n">
-        <v>1284</v>
+        <v>1413</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Monmouth NJ</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>big_west</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G170" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H170" t="n">
-        <v>0.8383</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>50.93</v>
+        <v>49.36</v>
       </c>
       <c r="J170" t="n">
-        <v>1450.7</v>
+        <v>1478.5</v>
       </c>
       <c r="K170" t="n">
+        <v>178</v>
+      </c>
+      <c r="L170" t="n">
+        <v>159</v>
+      </c>
+      <c r="M170" t="n">
         <v>168</v>
-      </c>
-      <c r="L170" t="n">
-        <v>180</v>
-      </c>
-      <c r="M170" t="n">
-        <v>188</v>
       </c>
     </row>
     <row r="171">
@@ -8093,44 +8093,44 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C171" t="n">
-        <v>1217</v>
+        <v>1284</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Harvard</t>
+          <t>Monmouth NJ</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ivy</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G171" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H171" t="n">
-        <v>0.8381</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>52</v>
+        <v>50.93</v>
       </c>
       <c r="J171" t="n">
-        <v>1506.7</v>
+        <v>1450.7</v>
       </c>
       <c r="K171" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="L171" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="M171" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172">
@@ -8138,14 +8138,14 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C172" t="n">
-        <v>1165</v>
+        <v>1217</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cornell</t>
+          <t>Harvard</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8157,25 +8157,25 @@
         <v>131</v>
       </c>
       <c r="G172" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H172" t="n">
-        <v>0.8343</v>
+        <v>0.838</v>
       </c>
       <c r="I172" t="n">
-        <v>52.56</v>
+        <v>52</v>
       </c>
       <c r="J172" t="n">
-        <v>1488.6</v>
+        <v>1506.7</v>
       </c>
       <c r="K172" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L172" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="M172" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="173">
@@ -8183,44 +8183,44 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C173" t="n">
-        <v>1413</v>
+        <v>1165</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Cornell</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>big_west</t>
+          <t>ivy</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G173" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H173" t="n">
-        <v>0.8331</v>
+        <v>0.8343</v>
       </c>
       <c r="I173" t="n">
-        <v>49.34</v>
+        <v>52.56</v>
       </c>
       <c r="J173" t="n">
-        <v>1478.5</v>
+        <v>1488.6</v>
       </c>
       <c r="K173" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="L173" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M173" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174">
@@ -8250,7 +8250,7 @@
         <v>27</v>
       </c>
       <c r="H174" t="n">
-        <v>0.8272</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="I174" t="n">
         <v>50.26</v>
@@ -8295,10 +8295,10 @@
         <v>26</v>
       </c>
       <c r="H175" t="n">
-        <v>0.824</v>
+        <v>0.8248</v>
       </c>
       <c r="I175" t="n">
-        <v>50.83</v>
+        <v>50.84</v>
       </c>
       <c r="J175" t="n">
         <v>1515.2</v>
@@ -8430,7 +8430,7 @@
         <v>23</v>
       </c>
       <c r="H178" t="n">
-        <v>0.8196</v>
+        <v>0.8203</v>
       </c>
       <c r="I178" t="n">
         <v>51.28</v>
@@ -8520,7 +8520,7 @@
         <v>25</v>
       </c>
       <c r="H180" t="n">
-        <v>0.8008</v>
+        <v>0.8015</v>
       </c>
       <c r="I180" t="n">
         <v>49.96</v>
@@ -8655,10 +8655,10 @@
         <v>24</v>
       </c>
       <c r="H183" t="n">
-        <v>0.7843</v>
+        <v>0.7892</v>
       </c>
       <c r="I183" t="n">
-        <v>47.9</v>
+        <v>47.92</v>
       </c>
       <c r="J183" t="n">
         <v>1509.4</v>
@@ -8700,7 +8700,7 @@
         <v>25</v>
       </c>
       <c r="H184" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7815</v>
       </c>
       <c r="I184" t="n">
         <v>49.44</v>
@@ -8745,7 +8745,7 @@
         <v>23</v>
       </c>
       <c r="H185" t="n">
-        <v>0.7771</v>
+        <v>0.777</v>
       </c>
       <c r="I185" t="n">
         <v>48.37</v>
@@ -8790,7 +8790,7 @@
         <v>24</v>
       </c>
       <c r="H186" t="n">
-        <v>0.7754</v>
+        <v>0.775</v>
       </c>
       <c r="I186" t="n">
         <v>46.16</v>
@@ -8813,7 +8813,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C187" t="n">
         <v>1404</v>
@@ -8835,10 +8835,10 @@
         <v>24</v>
       </c>
       <c r="H187" t="n">
-        <v>0.7729</v>
+        <v>0.7715</v>
       </c>
       <c r="I187" t="n">
-        <v>43.87</v>
+        <v>43.86</v>
       </c>
       <c r="J187" t="n">
         <v>1455.9</v>
@@ -8903,44 +8903,44 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C189" t="n">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Marist</t>
+          <t>Mercer</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>southern</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G189" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H189" t="n">
-        <v>0.7598</v>
+        <v>0.7601</v>
       </c>
       <c r="I189" t="n">
-        <v>47.42</v>
+        <v>49.1</v>
       </c>
       <c r="J189" t="n">
-        <v>1497.5</v>
+        <v>1454.9</v>
       </c>
       <c r="K189" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L189" t="n">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="M189" t="n">
-        <v>227</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190">
@@ -8948,44 +8948,44 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C190" t="n">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Mercer</t>
+          <t>Marist</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>southern</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G190" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7593</v>
+        <v>0.7598</v>
       </c>
       <c r="I190" t="n">
-        <v>49.09</v>
+        <v>47.42</v>
       </c>
       <c r="J190" t="n">
-        <v>1454.9</v>
+        <v>1497.5</v>
       </c>
       <c r="K190" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L190" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="M190" t="n">
-        <v>189</v>
+        <v>227</v>
       </c>
     </row>
     <row r="191">
@@ -9015,7 +9015,7 @@
         <v>25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.7462</v>
+        <v>0.7461</v>
       </c>
       <c r="I191" t="n">
         <v>48.2</v>
@@ -9285,10 +9285,10 @@
         <v>25</v>
       </c>
       <c r="H197" t="n">
-        <v>0.7202</v>
+        <v>0.7225</v>
       </c>
       <c r="I197" t="n">
-        <v>43.61</v>
+        <v>43.62</v>
       </c>
       <c r="J197" t="n">
         <v>1470</v>
@@ -9330,7 +9330,7 @@
         <v>23</v>
       </c>
       <c r="H198" t="n">
-        <v>0.7158</v>
+        <v>0.7159</v>
       </c>
       <c r="I198" t="n">
         <v>45.67</v>
@@ -9398,44 +9398,44 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C200" t="n">
-        <v>1111</v>
+        <v>1451</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Appalachian St</t>
+          <t>Weber St</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>sun_belt</t>
+          <t>big_sky</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G200" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6967</v>
+        <v>0.6984</v>
       </c>
       <c r="I200" t="n">
-        <v>46.47</v>
+        <v>43.89</v>
       </c>
       <c r="J200" t="n">
-        <v>1494.4</v>
+        <v>1362.9</v>
       </c>
       <c r="K200" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L200" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M200" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201">
@@ -9443,44 +9443,44 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C201" t="n">
-        <v>1451</v>
+        <v>1111</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Weber St</t>
+          <t>Appalachian St</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>big_sky</t>
+          <t>sun_belt</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G201" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.696</v>
+        <v>0.6967</v>
       </c>
       <c r="I201" t="n">
-        <v>43.89</v>
+        <v>46.47</v>
       </c>
       <c r="J201" t="n">
-        <v>1362.9</v>
+        <v>1494.4</v>
       </c>
       <c r="K201" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="L201" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M201" t="n">
-        <v>212</v>
+        <v>182</v>
       </c>
     </row>
     <row r="202">
@@ -9510,7 +9510,7 @@
         <v>24</v>
       </c>
       <c r="H202" t="n">
-        <v>0.6926</v>
+        <v>0.6927</v>
       </c>
       <c r="I202" t="n">
         <v>45.98</v>
@@ -9555,7 +9555,7 @@
         <v>27</v>
       </c>
       <c r="H203" t="n">
-        <v>0.6869</v>
+        <v>0.6876</v>
       </c>
       <c r="I203" t="n">
         <v>45.2</v>
@@ -9600,7 +9600,7 @@
         <v>21</v>
       </c>
       <c r="H204" t="n">
-        <v>0.6842</v>
+        <v>0.6849</v>
       </c>
       <c r="I204" t="n">
         <v>44.92</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="H205" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6811</v>
       </c>
       <c r="I205" t="n">
         <v>43.87</v>
@@ -9735,7 +9735,7 @@
         <v>22</v>
       </c>
       <c r="H207" t="n">
-        <v>0.68</v>
+        <v>0.6801</v>
       </c>
       <c r="I207" t="n">
         <v>42.81</v>
@@ -9780,7 +9780,7 @@
         <v>25</v>
       </c>
       <c r="H208" t="n">
-        <v>0.6793</v>
+        <v>0.6801</v>
       </c>
       <c r="I208" t="n">
         <v>45.17</v>
@@ -9870,7 +9870,7 @@
         <v>23</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6744</v>
+        <v>0.6751</v>
       </c>
       <c r="I210" t="n">
         <v>44.05</v>
@@ -9960,7 +9960,7 @@
         <v>28</v>
       </c>
       <c r="H212" t="n">
-        <v>0.6653</v>
+        <v>0.6661</v>
       </c>
       <c r="I212" t="n">
         <v>43.33</v>
@@ -10050,7 +10050,7 @@
         <v>24</v>
       </c>
       <c r="H214" t="n">
-        <v>0.659</v>
+        <v>0.6589</v>
       </c>
       <c r="I214" t="n">
         <v>43.15</v>
@@ -10095,7 +10095,7 @@
         <v>26</v>
       </c>
       <c r="H215" t="n">
-        <v>0.6577</v>
+        <v>0.6576</v>
       </c>
       <c r="I215" t="n">
         <v>44.77</v>
@@ -10140,7 +10140,7 @@
         <v>23</v>
       </c>
       <c r="H216" t="n">
-        <v>0.6455</v>
+        <v>0.6462</v>
       </c>
       <c r="I216" t="n">
         <v>42.9</v>
@@ -10230,7 +10230,7 @@
         <v>22</v>
       </c>
       <c r="H218" t="n">
-        <v>0.6371</v>
+        <v>0.6377</v>
       </c>
       <c r="I218" t="n">
         <v>40.3</v>
@@ -10275,7 +10275,7 @@
         <v>22</v>
       </c>
       <c r="H219" t="n">
-        <v>0.635</v>
+        <v>0.6351</v>
       </c>
       <c r="I219" t="n">
         <v>40.84</v>
@@ -10320,7 +10320,7 @@
         <v>24</v>
       </c>
       <c r="H220" t="n">
-        <v>0.6325</v>
+        <v>0.6324</v>
       </c>
       <c r="I220" t="n">
         <v>41.86</v>
@@ -10500,7 +10500,7 @@
         <v>23</v>
       </c>
       <c r="H224" t="n">
-        <v>0.6206</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="I224" t="n">
         <v>39.47</v>
@@ -10545,7 +10545,7 @@
         <v>23</v>
       </c>
       <c r="H225" t="n">
-        <v>0.614</v>
+        <v>0.6157</v>
       </c>
       <c r="I225" t="n">
         <v>40.26</v>
@@ -10590,7 +10590,7 @@
         <v>27</v>
       </c>
       <c r="H226" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6121</v>
       </c>
       <c r="I226" t="n">
         <v>41.74</v>
@@ -10725,7 +10725,7 @@
         <v>23</v>
       </c>
       <c r="H229" t="n">
-        <v>0.5988</v>
+        <v>0.5977</v>
       </c>
       <c r="I229" t="n">
         <v>41.79</v>
@@ -10905,10 +10905,10 @@
         <v>25</v>
       </c>
       <c r="H233" t="n">
-        <v>0.5874</v>
+        <v>0.5881</v>
       </c>
       <c r="I233" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="J233" t="n">
         <v>1442.9</v>
@@ -10950,7 +10950,7 @@
         <v>21</v>
       </c>
       <c r="H234" t="n">
-        <v>0.5853</v>
+        <v>0.5859</v>
       </c>
       <c r="I234" t="n">
         <v>40.86</v>
@@ -11130,7 +11130,7 @@
         <v>24</v>
       </c>
       <c r="H238" t="n">
-        <v>0.5692</v>
+        <v>0.5697</v>
       </c>
       <c r="I238" t="n">
         <v>40</v>
@@ -11175,7 +11175,7 @@
         <v>25</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5692</v>
+        <v>0.5693</v>
       </c>
       <c r="I239" t="n">
         <v>34.37</v>
@@ -11220,7 +11220,7 @@
         <v>23</v>
       </c>
       <c r="H240" t="n">
-        <v>0.5515</v>
+        <v>0.5512</v>
       </c>
       <c r="I240" t="n">
         <v>39.33</v>
@@ -11355,10 +11355,10 @@
         <v>22</v>
       </c>
       <c r="H243" t="n">
-        <v>0.5401</v>
+        <v>0.5417</v>
       </c>
       <c r="I243" t="n">
-        <v>36.29</v>
+        <v>36.3</v>
       </c>
       <c r="J243" t="n">
         <v>1383.4</v>
@@ -11445,7 +11445,7 @@
         <v>22</v>
       </c>
       <c r="H245" t="n">
-        <v>0.5374</v>
+        <v>0.5373</v>
       </c>
       <c r="I245" t="n">
         <v>36.26</v>
@@ -11535,10 +11535,10 @@
         <v>24</v>
       </c>
       <c r="H247" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>36.9</v>
+        <v>36.89</v>
       </c>
       <c r="J247" t="n">
         <v>1357.9</v>
@@ -11580,7 +11580,7 @@
         <v>23</v>
       </c>
       <c r="H248" t="n">
-        <v>0.5212</v>
+        <v>0.5233</v>
       </c>
       <c r="I248" t="n">
         <v>37.57</v>
@@ -11783,44 +11783,44 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C253" t="n">
-        <v>1360</v>
+        <v>1188</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SIUE</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G253" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H253" t="n">
-        <v>0.5098</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="I253" t="n">
-        <v>37.09</v>
+        <v>36.31</v>
       </c>
       <c r="J253" t="n">
-        <v>1362</v>
+        <v>1461.8</v>
       </c>
       <c r="K253" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="L253" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="M253" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
     </row>
     <row r="254">
@@ -11828,44 +11828,44 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C254" t="n">
-        <v>1188</v>
+        <v>1360</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SIUE</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G254" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H254" t="n">
-        <v>0.5094</v>
+        <v>0.5098</v>
       </c>
       <c r="I254" t="n">
-        <v>36.3</v>
+        <v>37.09</v>
       </c>
       <c r="J254" t="n">
-        <v>1461.8</v>
+        <v>1362</v>
       </c>
       <c r="K254" t="n">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="L254" t="n">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="M254" t="n">
-        <v>259</v>
+        <v>229</v>
       </c>
     </row>
     <row r="255">
@@ -12008,44 +12008,44 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="C258" t="n">
-        <v>1478</v>
+        <v>1380</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Le Moyne</t>
+          <t>Southern Univ</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>swac</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G258" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H258" t="n">
-        <v>0.4857</v>
+        <v>0.487</v>
       </c>
       <c r="I258" t="n">
-        <v>29.81</v>
+        <v>33.49</v>
       </c>
       <c r="J258" t="n">
-        <v>1336.2</v>
+        <v>1377.9</v>
       </c>
       <c r="K258" t="n">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="L258" t="n">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="M258" t="n">
-        <v>327</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259">
@@ -12053,44 +12053,44 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C259" t="n">
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Southern Univ</t>
+          <t>Le Moyne</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>swac</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G259" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H259" t="n">
-        <v>0.4854</v>
+        <v>0.4845</v>
       </c>
       <c r="I259" t="n">
-        <v>33.49</v>
+        <v>29.8</v>
       </c>
       <c r="J259" t="n">
-        <v>1377.9</v>
+        <v>1336.2</v>
       </c>
       <c r="K259" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="L259" t="n">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="M259" t="n">
-        <v>280</v>
+        <v>327</v>
       </c>
     </row>
     <row r="260">
@@ -12165,10 +12165,10 @@
         <v>22</v>
       </c>
       <c r="H261" t="n">
-        <v>0.4805</v>
+        <v>0.4826</v>
       </c>
       <c r="I261" t="n">
-        <v>35.24</v>
+        <v>35.25</v>
       </c>
       <c r="J261" t="n">
         <v>1384.3</v>
@@ -12210,10 +12210,10 @@
         <v>23</v>
       </c>
       <c r="H262" t="n">
-        <v>0.4775</v>
+        <v>0.4797</v>
       </c>
       <c r="I262" t="n">
-        <v>33.76</v>
+        <v>33.77</v>
       </c>
       <c r="J262" t="n">
         <v>1391.8</v>
@@ -12255,7 +12255,7 @@
         <v>23</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4761</v>
+        <v>0.4768</v>
       </c>
       <c r="I263" t="n">
         <v>33.45</v>
@@ -12300,7 +12300,7 @@
         <v>23</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4759</v>
+        <v>0.4757</v>
       </c>
       <c r="I264" t="n">
         <v>33.83</v>
@@ -12345,7 +12345,7 @@
         <v>23</v>
       </c>
       <c r="H265" t="n">
-        <v>0.4716</v>
+        <v>0.4715</v>
       </c>
       <c r="I265" t="n">
         <v>35.38</v>
@@ -12390,7 +12390,7 @@
         <v>27</v>
       </c>
       <c r="H266" t="n">
-        <v>0.463</v>
+        <v>0.4629</v>
       </c>
       <c r="I266" t="n">
         <v>30.55</v>
@@ -12435,7 +12435,7 @@
         <v>23</v>
       </c>
       <c r="H267" t="n">
-        <v>0.4627</v>
+        <v>0.4626</v>
       </c>
       <c r="I267" t="n">
         <v>33.53</v>
@@ -12480,7 +12480,7 @@
         <v>23</v>
       </c>
       <c r="H268" t="n">
-        <v>0.462</v>
+        <v>0.4619</v>
       </c>
       <c r="I268" t="n">
         <v>33.46</v>
@@ -12615,10 +12615,10 @@
         <v>21</v>
       </c>
       <c r="H271" t="n">
-        <v>0.458</v>
+        <v>0.4596</v>
       </c>
       <c r="I271" t="n">
-        <v>29.2</v>
+        <v>29.21</v>
       </c>
       <c r="J271" t="n">
         <v>1328.3</v>
@@ -12660,7 +12660,7 @@
         <v>22</v>
       </c>
       <c r="H272" t="n">
-        <v>0.4565</v>
+        <v>0.4564</v>
       </c>
       <c r="I272" t="n">
         <v>32.15</v>
@@ -12795,7 +12795,7 @@
         <v>22</v>
       </c>
       <c r="H275" t="n">
-        <v>0.4468</v>
+        <v>0.4473</v>
       </c>
       <c r="I275" t="n">
         <v>31.05</v>
@@ -12885,7 +12885,7 @@
         <v>21</v>
       </c>
       <c r="H277" t="n">
-        <v>0.4416</v>
+        <v>0.4412</v>
       </c>
       <c r="I277" t="n">
         <v>32.97</v>
@@ -12930,7 +12930,7 @@
         <v>22</v>
       </c>
       <c r="H278" t="n">
-        <v>0.4398</v>
+        <v>0.4397</v>
       </c>
       <c r="I278" t="n">
         <v>32.14</v>
@@ -13043,44 +13043,44 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C281" t="n">
-        <v>1444</v>
+        <v>1131</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>W Michigan</t>
+          <t>Boston Univ</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>mac</t>
+          <t>patriot</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G281" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H281" t="n">
-        <v>0.4335</v>
+        <v>0.4345</v>
       </c>
       <c r="I281" t="n">
-        <v>31.28</v>
+        <v>32.61</v>
       </c>
       <c r="J281" t="n">
-        <v>1337.9</v>
+        <v>1346.8</v>
       </c>
       <c r="K281" t="n">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="L281" t="n">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="M281" t="n">
-        <v>290</v>
+        <v>277</v>
       </c>
     </row>
     <row r="282">
@@ -13088,44 +13088,44 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C282" t="n">
-        <v>1357</v>
+        <v>1444</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Sacred Heart</t>
+          <t>W Michigan</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="F282" t="n">
         <v>123</v>
       </c>
       <c r="G282" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H282" t="n">
-        <v>0.4334</v>
+        <v>0.4335</v>
       </c>
       <c r="I282" t="n">
-        <v>30.98</v>
+        <v>31.28</v>
       </c>
       <c r="J282" t="n">
-        <v>1351.6</v>
+        <v>1337.9</v>
       </c>
       <c r="K282" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="L282" t="n">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="M282" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="283">
@@ -13133,44 +13133,44 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C283" t="n">
-        <v>1131</v>
+        <v>1357</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Boston Univ</t>
+          <t>Sacred Heart</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>patriot</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G283" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H283" t="n">
-        <v>0.4324</v>
+        <v>0.4333</v>
       </c>
       <c r="I283" t="n">
-        <v>32.61</v>
+        <v>30.98</v>
       </c>
       <c r="J283" t="n">
-        <v>1346.8</v>
+        <v>1351.6</v>
       </c>
       <c r="K283" t="n">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="L283" t="n">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="M283" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
     </row>
     <row r="284">
@@ -13200,7 +13200,7 @@
         <v>23</v>
       </c>
       <c r="H284" t="n">
-        <v>0.4193</v>
+        <v>0.4192</v>
       </c>
       <c r="I284" t="n">
         <v>30.32</v>
@@ -13313,44 +13313,44 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C287" t="n">
-        <v>1148</v>
+        <v>1260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Central Conn</t>
+          <t>Loyola-Chicago</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>a_ten</t>
         </is>
       </c>
       <c r="F287" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G287" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H287" t="n">
-        <v>0.4149</v>
+        <v>0.4164</v>
       </c>
       <c r="I287" t="n">
-        <v>30.13</v>
+        <v>32.8</v>
       </c>
       <c r="J287" t="n">
-        <v>1455.5</v>
+        <v>1402.1</v>
       </c>
       <c r="K287" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L287" t="n">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="M287" t="n">
-        <v>291</v>
+        <v>220</v>
       </c>
     </row>
     <row r="288">
@@ -13358,44 +13358,44 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C288" t="n">
-        <v>1184</v>
+        <v>1148</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>E Kentucky</t>
+          <t>Central Conn</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F288" t="n">
         <v>121</v>
       </c>
       <c r="G288" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H288" t="n">
-        <v>0.4145</v>
+        <v>0.4148</v>
       </c>
       <c r="I288" t="n">
-        <v>29.36</v>
+        <v>30.13</v>
       </c>
       <c r="J288" t="n">
-        <v>1325</v>
+        <v>1455.5</v>
       </c>
       <c r="K288" t="n">
+        <v>289</v>
+      </c>
+      <c r="L288" t="n">
+        <v>306</v>
+      </c>
+      <c r="M288" t="n">
         <v>291</v>
-      </c>
-      <c r="L288" t="n">
-        <v>297</v>
-      </c>
-      <c r="M288" t="n">
-        <v>294</v>
       </c>
     </row>
     <row r="289">
@@ -13403,44 +13403,44 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C289" t="n">
-        <v>1260</v>
+        <v>1184</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Loyola-Chicago</t>
+          <t>E Kentucky</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>a_ten</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G289" t="n">
         <v>24</v>
       </c>
       <c r="H289" t="n">
-        <v>0.4139</v>
+        <v>0.4144</v>
       </c>
       <c r="I289" t="n">
-        <v>32.8</v>
+        <v>29.36</v>
       </c>
       <c r="J289" t="n">
-        <v>1402.1</v>
+        <v>1325</v>
       </c>
       <c r="K289" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L289" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="M289" t="n">
-        <v>220</v>
+        <v>294</v>
       </c>
     </row>
     <row r="290">
@@ -13470,7 +13470,7 @@
         <v>22</v>
       </c>
       <c r="H290" t="n">
-        <v>0.4119</v>
+        <v>0.4124</v>
       </c>
       <c r="I290" t="n">
         <v>31.38</v>
@@ -13515,7 +13515,7 @@
         <v>24</v>
       </c>
       <c r="H291" t="n">
-        <v>0.4074</v>
+        <v>0.4073</v>
       </c>
       <c r="I291" t="n">
         <v>30.08</v>
@@ -13560,7 +13560,7 @@
         <v>22</v>
       </c>
       <c r="H292" t="n">
-        <v>0.4072</v>
+        <v>0.4071</v>
       </c>
       <c r="I292" t="n">
         <v>27.3</v>
@@ -13605,10 +13605,10 @@
         <v>21</v>
       </c>
       <c r="H293" t="n">
-        <v>0.4004</v>
+        <v>0.4013</v>
       </c>
       <c r="I293" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="J293" t="n">
         <v>1371</v>
@@ -13650,7 +13650,7 @@
         <v>22</v>
       </c>
       <c r="H294" t="n">
-        <v>0.3984</v>
+        <v>0.399</v>
       </c>
       <c r="I294" t="n">
         <v>27.15</v>
@@ -13673,44 +13673,44 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C295" t="n">
-        <v>1239</v>
+        <v>1337</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Pepperdine</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F295" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G295" t="n">
         <v>23</v>
       </c>
       <c r="H295" t="n">
-        <v>0.3928</v>
+        <v>0.3932</v>
       </c>
       <c r="I295" t="n">
-        <v>29.54</v>
+        <v>30.76</v>
       </c>
       <c r="J295" t="n">
-        <v>1364.2</v>
+        <v>1310.7</v>
       </c>
       <c r="K295" t="n">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="L295" t="n">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="M295" t="n">
-        <v>293</v>
+        <v>261</v>
       </c>
     </row>
     <row r="296">
@@ -13718,44 +13718,44 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C296" t="n">
-        <v>1337</v>
+        <v>1239</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Pepperdine</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F296" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G296" t="n">
         <v>23</v>
       </c>
       <c r="H296" t="n">
-        <v>0.3914</v>
+        <v>0.3928</v>
       </c>
       <c r="I296" t="n">
-        <v>30.76</v>
+        <v>29.54</v>
       </c>
       <c r="J296" t="n">
-        <v>1310.7</v>
+        <v>1364.2</v>
       </c>
       <c r="K296" t="n">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="L296" t="n">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="M296" t="n">
-        <v>261</v>
+        <v>293</v>
       </c>
     </row>
     <row r="297">
@@ -13785,10 +13785,10 @@
         <v>22</v>
       </c>
       <c r="H297" t="n">
-        <v>0.39</v>
+        <v>0.3916</v>
       </c>
       <c r="I297" t="n">
-        <v>24.42</v>
+        <v>24.43</v>
       </c>
       <c r="J297" t="n">
         <v>1288.6</v>
@@ -13875,7 +13875,7 @@
         <v>25</v>
       </c>
       <c r="H299" t="n">
-        <v>0.3819</v>
+        <v>0.3835</v>
       </c>
       <c r="I299" t="n">
         <v>27.72</v>
@@ -13920,7 +13920,7 @@
         <v>24</v>
       </c>
       <c r="H300" t="n">
-        <v>0.3801</v>
+        <v>0.38</v>
       </c>
       <c r="I300" t="n">
         <v>29.47</v>
@@ -13965,7 +13965,7 @@
         <v>22</v>
       </c>
       <c r="H301" t="n">
-        <v>0.379</v>
+        <v>0.3789</v>
       </c>
       <c r="I301" t="n">
         <v>27.33</v>
@@ -14010,7 +14010,7 @@
         <v>22</v>
       </c>
       <c r="H302" t="n">
-        <v>0.3783</v>
+        <v>0.3782</v>
       </c>
       <c r="I302" t="n">
         <v>29.48</v>
@@ -14055,10 +14055,10 @@
         <v>23</v>
       </c>
       <c r="H303" t="n">
-        <v>0.3744</v>
+        <v>0.3765</v>
       </c>
       <c r="I303" t="n">
-        <v>28.58</v>
+        <v>28.59</v>
       </c>
       <c r="J303" t="n">
         <v>1328.3</v>
@@ -14100,7 +14100,7 @@
         <v>24</v>
       </c>
       <c r="H304" t="n">
-        <v>0.3727</v>
+        <v>0.3734</v>
       </c>
       <c r="I304" t="n">
         <v>26.91</v>
@@ -14123,7 +14123,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C305" t="n">
         <v>1151</v>
@@ -14190,7 +14190,7 @@
         <v>23</v>
       </c>
       <c r="H306" t="n">
-        <v>0.3698</v>
+        <v>0.3697</v>
       </c>
       <c r="I306" t="n">
         <v>26.95</v>
@@ -14235,7 +14235,7 @@
         <v>23</v>
       </c>
       <c r="H307" t="n">
-        <v>0.3676</v>
+        <v>0.3682</v>
       </c>
       <c r="I307" t="n">
         <v>28.4</v>
@@ -14280,7 +14280,7 @@
         <v>22</v>
       </c>
       <c r="H308" t="n">
-        <v>0.3639</v>
+        <v>0.3644</v>
       </c>
       <c r="I308" t="n">
         <v>25.01</v>
@@ -14325,7 +14325,7 @@
         <v>23</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3638</v>
+        <v>0.3639</v>
       </c>
       <c r="I309" t="n">
         <v>25.18</v>
@@ -14370,10 +14370,10 @@
         <v>24</v>
       </c>
       <c r="H310" t="n">
-        <v>0.3537</v>
+        <v>0.3559</v>
       </c>
       <c r="I310" t="n">
-        <v>27.63</v>
+        <v>27.64</v>
       </c>
       <c r="J310" t="n">
         <v>1288.1</v>
@@ -14415,10 +14415,10 @@
         <v>21</v>
       </c>
       <c r="H311" t="n">
-        <v>0.3536</v>
+        <v>0.3557</v>
       </c>
       <c r="I311" t="n">
-        <v>27.6</v>
+        <v>27.61</v>
       </c>
       <c r="J311" t="n">
         <v>1273.7</v>
@@ -14460,7 +14460,7 @@
         <v>24</v>
       </c>
       <c r="H312" t="n">
-        <v>0.353</v>
+        <v>0.3529</v>
       </c>
       <c r="I312" t="n">
         <v>26.64</v>
@@ -14505,7 +14505,7 @@
         <v>22</v>
       </c>
       <c r="H313" t="n">
-        <v>0.3515</v>
+        <v>0.352</v>
       </c>
       <c r="I313" t="n">
         <v>22.68</v>
@@ -14550,7 +14550,7 @@
         <v>22</v>
       </c>
       <c r="H314" t="n">
-        <v>0.3492</v>
+        <v>0.3477</v>
       </c>
       <c r="I314" t="n">
         <v>26.22</v>
@@ -14640,7 +14640,7 @@
         <v>24</v>
       </c>
       <c r="H316" t="n">
-        <v>0.3425</v>
+        <v>0.3424</v>
       </c>
       <c r="I316" t="n">
         <v>24.74</v>
@@ -14685,10 +14685,10 @@
         <v>24</v>
       </c>
       <c r="H317" t="n">
-        <v>0.3386</v>
+        <v>0.3407</v>
       </c>
       <c r="I317" t="n">
-        <v>26.37</v>
+        <v>26.38</v>
       </c>
       <c r="J317" t="n">
         <v>1276.5</v>
@@ -14730,7 +14730,7 @@
         <v>23</v>
       </c>
       <c r="H318" t="n">
-        <v>0.3362</v>
+        <v>0.3361</v>
       </c>
       <c r="I318" t="n">
         <v>24.07</v>
@@ -14798,7 +14798,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C320" t="n">
         <v>1197</v>
@@ -14820,7 +14820,7 @@
         <v>24</v>
       </c>
       <c r="H320" t="n">
-        <v>0.3309</v>
+        <v>0.3308</v>
       </c>
       <c r="I320" t="n">
         <v>24.66</v>
@@ -14843,7 +14843,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C321" t="n">
         <v>1391</v>
@@ -14865,10 +14865,10 @@
         <v>22</v>
       </c>
       <c r="H321" t="n">
-        <v>0.3269</v>
+        <v>0.3262</v>
       </c>
       <c r="I321" t="n">
-        <v>24.67</v>
+        <v>24.66</v>
       </c>
       <c r="J321" t="n">
         <v>1302.3</v>
@@ -14910,7 +14910,7 @@
         <v>24</v>
       </c>
       <c r="H322" t="n">
-        <v>0.3245</v>
+        <v>0.3244</v>
       </c>
       <c r="I322" t="n">
         <v>23.74</v>
@@ -14955,7 +14955,7 @@
         <v>25</v>
       </c>
       <c r="H323" t="n">
-        <v>0.3233</v>
+        <v>0.3232</v>
       </c>
       <c r="I323" t="n">
         <v>24.61</v>
@@ -15045,7 +15045,7 @@
         <v>23</v>
       </c>
       <c r="H325" t="n">
-        <v>0.3113</v>
+        <v>0.3112</v>
       </c>
       <c r="I325" t="n">
         <v>22.96</v>
@@ -15135,7 +15135,7 @@
         <v>22</v>
       </c>
       <c r="H327" t="n">
-        <v>0.3071</v>
+        <v>0.307</v>
       </c>
       <c r="I327" t="n">
         <v>22.4</v>
@@ -15225,7 +15225,7 @@
         <v>24</v>
       </c>
       <c r="H329" t="n">
-        <v>0.2988</v>
+        <v>0.2987</v>
       </c>
       <c r="I329" t="n">
         <v>23.12</v>
@@ -15270,7 +15270,7 @@
         <v>23</v>
       </c>
       <c r="H330" t="n">
-        <v>0.298</v>
+        <v>0.2984</v>
       </c>
       <c r="I330" t="n">
         <v>22.8</v>
@@ -15315,7 +15315,7 @@
         <v>25</v>
       </c>
       <c r="H331" t="n">
-        <v>0.2873</v>
+        <v>0.2874</v>
       </c>
       <c r="I331" t="n">
         <v>23.4</v>
@@ -15360,7 +15360,7 @@
         <v>22</v>
       </c>
       <c r="H332" t="n">
-        <v>0.2869</v>
+        <v>0.2868</v>
       </c>
       <c r="I332" t="n">
         <v>21.03</v>
@@ -15405,10 +15405,10 @@
         <v>21</v>
       </c>
       <c r="H333" t="n">
-        <v>0.2836</v>
+        <v>0.2857</v>
       </c>
       <c r="I333" t="n">
-        <v>20.81</v>
+        <v>20.82</v>
       </c>
       <c r="J333" t="n">
         <v>1311.3</v>
@@ -15428,44 +15428,44 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C334" t="n">
-        <v>1312</v>
+        <v>1221</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NJIT</t>
+          <t>Holy Cross</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>aec</t>
+          <t>patriot</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G334" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H334" t="n">
-        <v>0.2795</v>
+        <v>0.2814</v>
       </c>
       <c r="I334" t="n">
-        <v>21.09</v>
+        <v>20.86</v>
       </c>
       <c r="J334" t="n">
-        <v>1310</v>
+        <v>1292.2</v>
       </c>
       <c r="K334" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L334" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M334" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="335">
@@ -15473,44 +15473,44 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C335" t="n">
-        <v>1221</v>
+        <v>1312</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Holy Cross</t>
+          <t>NJIT</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>patriot</t>
+          <t>aec</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G335" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H335" t="n">
-        <v>0.2793</v>
+        <v>0.2794</v>
       </c>
       <c r="I335" t="n">
-        <v>20.85</v>
+        <v>21.09</v>
       </c>
       <c r="J335" t="n">
-        <v>1292.2</v>
+        <v>1310</v>
       </c>
       <c r="K335" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L335" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M335" t="n">
-        <v>333</v>
+        <v>314</v>
       </c>
     </row>
     <row r="336">
@@ -15675,7 +15675,7 @@
         <v>22</v>
       </c>
       <c r="H339" t="n">
-        <v>0.2662</v>
+        <v>0.2661</v>
       </c>
       <c r="I339" t="n">
         <v>19.07</v>
@@ -15698,44 +15698,44 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C340" t="n">
-        <v>1115</v>
+        <v>1427</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Ark Pine Bluff</t>
+          <t>UT San Antonio</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>swac</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G340" t="n">
         <v>22</v>
       </c>
       <c r="H340" t="n">
-        <v>0.2649</v>
+        <v>0.2659</v>
       </c>
       <c r="I340" t="n">
-        <v>20.89</v>
+        <v>20.8</v>
       </c>
       <c r="J340" t="n">
-        <v>1256.8</v>
+        <v>1293.9</v>
       </c>
       <c r="K340" t="n">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="L340" t="n">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="M340" t="n">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="341">
@@ -15743,44 +15743,44 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C341" t="n">
-        <v>1427</v>
+        <v>1288</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>UT San Antonio</t>
+          <t>Morgan St</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G341" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H341" t="n">
-        <v>0.2644</v>
+        <v>0.2659</v>
       </c>
       <c r="I341" t="n">
-        <v>20.79</v>
+        <v>18.8</v>
       </c>
       <c r="J341" t="n">
-        <v>1293.9</v>
+        <v>1273.9</v>
       </c>
       <c r="K341" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L341" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="M341" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
     </row>
     <row r="342">
@@ -15788,44 +15788,44 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C342" t="n">
-        <v>1288</v>
+        <v>1115</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Morgan St</t>
+          <t>Ark Pine Bluff</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>swac</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G342" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H342" t="n">
-        <v>0.2638</v>
+        <v>0.265</v>
       </c>
       <c r="I342" t="n">
-        <v>18.79</v>
+        <v>20.89</v>
       </c>
       <c r="J342" t="n">
-        <v>1273.9</v>
+        <v>1256.8</v>
       </c>
       <c r="K342" t="n">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="L342" t="n">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="M342" t="n">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="343">
@@ -15900,7 +15900,7 @@
         <v>24</v>
       </c>
       <c r="H344" t="n">
-        <v>0.2621</v>
+        <v>0.2622</v>
       </c>
       <c r="I344" t="n">
         <v>21.13</v>
@@ -15945,10 +15945,10 @@
         <v>22</v>
       </c>
       <c r="H345" t="n">
-        <v>0.2579</v>
+        <v>0.2593</v>
       </c>
       <c r="I345" t="n">
-        <v>19.46</v>
+        <v>19.47</v>
       </c>
       <c r="J345" t="n">
         <v>1280</v>
@@ -15990,7 +15990,7 @@
         <v>23</v>
       </c>
       <c r="H346" t="n">
-        <v>0.2489</v>
+        <v>0.2488</v>
       </c>
       <c r="I346" t="n">
         <v>18.57</v>
@@ -16080,10 +16080,10 @@
         <v>22</v>
       </c>
       <c r="H348" t="n">
-        <v>0.2474</v>
+        <v>0.2471</v>
       </c>
       <c r="I348" t="n">
-        <v>17.57</v>
+        <v>17.56</v>
       </c>
       <c r="J348" t="n">
         <v>1257.4</v>
@@ -16125,7 +16125,7 @@
         <v>21</v>
       </c>
       <c r="H349" t="n">
-        <v>0.2423</v>
+        <v>0.2424</v>
       </c>
       <c r="I349" t="n">
         <v>20.02</v>
@@ -16260,7 +16260,7 @@
         <v>25</v>
       </c>
       <c r="H352" t="n">
-        <v>0.2328</v>
+        <v>0.2337</v>
       </c>
       <c r="I352" t="n">
         <v>18.56</v>
@@ -16395,7 +16395,7 @@
         <v>21</v>
       </c>
       <c r="H355" t="n">
-        <v>0.2232</v>
+        <v>0.223</v>
       </c>
       <c r="I355" t="n">
         <v>15.15</v>
@@ -16485,7 +16485,7 @@
         <v>21</v>
       </c>
       <c r="H357" t="n">
-        <v>0.2136</v>
+        <v>0.2141</v>
       </c>
       <c r="I357" t="n">
         <v>16.54</v>
@@ -16530,7 +16530,7 @@
         <v>21</v>
       </c>
       <c r="H358" t="n">
-        <v>0.2073</v>
+        <v>0.2075</v>
       </c>
       <c r="I358" t="n">
         <v>16</v>
@@ -16575,7 +16575,7 @@
         <v>24</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1956</v>
+        <v>0.1973</v>
       </c>
       <c r="I359" t="n">
         <v>15.83</v>
@@ -16643,44 +16643,44 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C361" t="n">
-        <v>1442</v>
+        <v>1164</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>W Illinois</t>
+          <t>Coppin St</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G361" t="n">
         <v>21</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1721</v>
+        <v>0.1718</v>
       </c>
       <c r="I361" t="n">
-        <v>13.47</v>
+        <v>12.53</v>
       </c>
       <c r="J361" t="n">
-        <v>1232.1</v>
+        <v>1185.3</v>
       </c>
       <c r="K361" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L361" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M361" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="362">
@@ -16688,23 +16688,23 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C362" t="n">
-        <v>1164</v>
+        <v>1442</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Coppin St</t>
+          <t>W Illinois</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G362" t="n">
         <v>21</v>
@@ -16713,19 +16713,19 @@
         <v>0.1718</v>
       </c>
       <c r="I362" t="n">
-        <v>12.53</v>
+        <v>13.47</v>
       </c>
       <c r="J362" t="n">
-        <v>1185.3</v>
+        <v>1232.1</v>
       </c>
       <c r="K362" t="n">
+        <v>364</v>
+      </c>
+      <c r="L362" t="n">
+        <v>364</v>
+      </c>
+      <c r="M362" t="n">
         <v>363</v>
-      </c>
-      <c r="L362" t="n">
-        <v>363</v>
-      </c>
-      <c r="M362" t="n">
-        <v>362</v>
       </c>
     </row>
     <row r="363">

--- a/model_rankings_2026.xlsx
+++ b/model_rankings_2026.xlsx
@@ -510,10 +510,10 @@
         <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2126</v>
+        <v>3.2106</v>
       </c>
       <c r="I2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.64</v>
       </c>
       <c r="J2" t="n">
         <v>2286.8</v>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1226</v>
+        <v>3.1311</v>
       </c>
       <c r="I3" t="n">
-        <v>92.45</v>
+        <v>92.47</v>
       </c>
       <c r="J3" t="n">
-        <v>2203.3</v>
+        <v>2216.6</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -600,10 +600,10 @@
         <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1088</v>
+        <v>3.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>92.76000000000001</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>2122.2</v>
@@ -623,44 +623,44 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1235</v>
+        <v>1276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>big_twelve</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0858</v>
+        <v>3.0887</v>
       </c>
       <c r="I5" t="n">
-        <v>93.3</v>
+        <v>91.28</v>
       </c>
       <c r="J5" t="n">
-        <v>2057.2</v>
+        <v>2193.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -668,19 +668,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>big_twelve</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -690,22 +690,22 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>3.065</v>
+        <v>3.0848</v>
       </c>
       <c r="I6" t="n">
-        <v>91.04000000000001</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2180.4</v>
+        <v>2057.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -735,10 +735,10 @@
         <v>27</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0002</v>
+        <v>2.9987</v>
       </c>
       <c r="I7" t="n">
-        <v>91.76000000000001</v>
+        <v>91.75</v>
       </c>
       <c r="J7" t="n">
         <v>2007.2</v>
@@ -780,10 +780,10 @@
         <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9807</v>
+        <v>2.9756</v>
       </c>
       <c r="I8" t="n">
-        <v>90.34999999999999</v>
+        <v>90.34</v>
       </c>
       <c r="J8" t="n">
         <v>2037.1</v>
@@ -825,10 +825,10 @@
         <v>28</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9411</v>
+        <v>2.9357</v>
       </c>
       <c r="I9" t="n">
-        <v>90.77</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>2033.1</v>
@@ -870,10 +870,10 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8088</v>
+        <v>2.8051</v>
       </c>
       <c r="I10" t="n">
-        <v>90.14</v>
+        <v>90.13</v>
       </c>
       <c r="J10" t="n">
         <v>2070.4</v>
@@ -893,7 +893,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>1277</v>
@@ -915,7 +915,7 @@
         <v>27</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7417</v>
+        <v>2.741</v>
       </c>
       <c r="I11" t="n">
         <v>87.69</v>
@@ -938,14 +938,14 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -954,28 +954,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
         <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>2.679</v>
+        <v>2.7049</v>
       </c>
       <c r="I12" t="n">
-        <v>87.84999999999999</v>
+        <v>88.48</v>
       </c>
       <c r="J12" t="n">
-        <v>1963.8</v>
+        <v>1979.4</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -983,14 +983,14 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>1104</v>
+        <v>1435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G13" t="n">
         <v>28</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6625</v>
+        <v>2.674</v>
       </c>
       <c r="I13" t="n">
-        <v>84.94</v>
+        <v>87.84</v>
       </c>
       <c r="J13" t="n">
-        <v>1985.7</v>
+        <v>1963.8</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1028,44 +1028,44 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>1163</v>
+        <v>1104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>big_east</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>144</v>
       </c>
       <c r="G14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6567</v>
+        <v>2.6632</v>
       </c>
       <c r="I14" t="n">
-        <v>87.7</v>
+        <v>84.94</v>
       </c>
       <c r="J14" t="n">
-        <v>2068.6</v>
+        <v>1985.7</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
+        <v>18</v>
+      </c>
+      <c r="M14" t="n">
         <v>11</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1073,7 +1073,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
         <v>1385</v>
@@ -1095,10 +1095,10 @@
         <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6424</v>
+        <v>2.6401</v>
       </c>
       <c r="I15" t="n">
-        <v>88.15000000000001</v>
+        <v>88.13</v>
       </c>
       <c r="J15" t="n">
         <v>2014.7</v>
@@ -1118,44 +1118,44 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>1397</v>
+        <v>1163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>big_east</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G16" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6379</v>
+        <v>2.6325</v>
       </c>
       <c r="I16" t="n">
-        <v>87.81999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="J16" t="n">
-        <v>1945</v>
+        <v>2093.1</v>
       </c>
       <c r="K16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1163,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>1438</v>
@@ -1185,10 +1185,10 @@
         <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5726</v>
+        <v>2.5701</v>
       </c>
       <c r="I17" t="n">
-        <v>87.93000000000001</v>
+        <v>87.92</v>
       </c>
       <c r="J17" t="n">
         <v>1966.7</v>
@@ -1230,10 +1230,10 @@
         <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5562</v>
+        <v>2.5536</v>
       </c>
       <c r="I18" t="n">
-        <v>83.94</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="J18" t="n">
         <v>1988.1</v>
@@ -1275,7 +1275,7 @@
         <v>26</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4988</v>
+        <v>2.499</v>
       </c>
       <c r="I19" t="n">
         <v>85.45</v>
@@ -1320,7 +1320,7 @@
         <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4856</v>
+        <v>2.4863</v>
       </c>
       <c r="I20" t="n">
         <v>85.45999999999999</v>
@@ -1365,7 +1365,7 @@
         <v>27</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4215</v>
+        <v>2.422</v>
       </c>
       <c r="I21" t="n">
         <v>84.81999999999999</v>
@@ -1410,7 +1410,7 @@
         <v>28</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4131</v>
+        <v>2.4124</v>
       </c>
       <c r="I22" t="n">
         <v>82.73</v>
@@ -1433,44 +1433,44 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>1458</v>
+        <v>1429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>mwc</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4079</v>
+        <v>2.4043</v>
       </c>
       <c r="I23" t="n">
-        <v>84.67</v>
+        <v>85.77</v>
       </c>
       <c r="J23" t="n">
-        <v>1882.4</v>
+        <v>1917</v>
       </c>
       <c r="K23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1478,44 +1478,44 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>1388</v>
+        <v>1458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>136</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4045</v>
+        <v>2.4031</v>
       </c>
       <c r="I24" t="n">
-        <v>85.48</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1857.8</v>
+        <v>1882.4</v>
       </c>
       <c r="K24" t="n">
+        <v>25</v>
+      </c>
+      <c r="L24" t="n">
         <v>22</v>
       </c>
-      <c r="L24" t="n">
-        <v>24</v>
-      </c>
       <c r="M24" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1523,44 +1523,44 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>1429</v>
+        <v>1388</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mwc</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G25" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4039</v>
+        <v>2.4021</v>
       </c>
       <c r="I25" t="n">
-        <v>85.77</v>
+        <v>85.47</v>
       </c>
       <c r="J25" t="n">
-        <v>1917</v>
+        <v>1857.8</v>
       </c>
       <c r="K25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -1590,10 +1590,10 @@
         <v>29</v>
       </c>
       <c r="H26" t="n">
-        <v>2.36</v>
+        <v>2.3553</v>
       </c>
       <c r="I26" t="n">
-        <v>83.09</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>1916.7</v>
@@ -1635,7 +1635,7 @@
         <v>29</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3157</v>
+        <v>2.316</v>
       </c>
       <c r="I27" t="n">
         <v>83.89</v>
@@ -1680,10 +1680,10 @@
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2954</v>
+        <v>2.2992</v>
       </c>
       <c r="I28" t="n">
-        <v>81.3</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>1979.2</v>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2582</v>
+        <v>2.2596</v>
       </c>
       <c r="I29" t="n">
         <v>81.51000000000001</v>
@@ -1770,10 +1770,10 @@
         <v>27</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2471</v>
+        <v>2.243</v>
       </c>
       <c r="I30" t="n">
-        <v>81.62</v>
+        <v>81.61</v>
       </c>
       <c r="J30" t="n">
         <v>1813.9</v>
@@ -1815,7 +1815,7 @@
         <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2189</v>
+        <v>2.2196</v>
       </c>
       <c r="I31" t="n">
         <v>81.56</v>
@@ -1860,7 +1860,7 @@
         <v>24</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2115</v>
+        <v>2.2113</v>
       </c>
       <c r="I32" t="n">
         <v>81.67</v>
@@ -1905,10 +1905,10 @@
         <v>28</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1674</v>
+        <v>2.1628</v>
       </c>
       <c r="I33" t="n">
-        <v>78.73999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="J33" t="n">
         <v>1836.2</v>
@@ -1950,7 +1950,7 @@
         <v>27</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1267</v>
+        <v>2.1265</v>
       </c>
       <c r="I34" t="n">
         <v>81.79000000000001</v>
@@ -1995,10 +1995,10 @@
         <v>28</v>
       </c>
       <c r="H35" t="n">
-        <v>2.1144</v>
+        <v>2.1115</v>
       </c>
       <c r="I35" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>1845.1</v>
@@ -2040,10 +2040,10 @@
         <v>25</v>
       </c>
       <c r="H36" t="n">
-        <v>2.0939</v>
+        <v>2.0899</v>
       </c>
       <c r="I36" t="n">
-        <v>81.34999999999999</v>
+        <v>81.34</v>
       </c>
       <c r="J36" t="n">
         <v>1852.8</v>
@@ -2063,44 +2063,44 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C37" t="n">
-        <v>1328</v>
+        <v>1274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G37" t="n">
         <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>2.0801</v>
+        <v>2.0813</v>
       </c>
       <c r="I37" t="n">
-        <v>80.40000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="J37" t="n">
-        <v>1729</v>
+        <v>1794.7</v>
       </c>
       <c r="K37" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
@@ -2108,44 +2108,44 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>1274</v>
+        <v>1328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G38" t="n">
         <v>26</v>
       </c>
       <c r="H38" t="n">
-        <v>2.0792</v>
+        <v>2.0802</v>
       </c>
       <c r="I38" t="n">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>1794.7</v>
+        <v>1729</v>
       </c>
       <c r="K38" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L38" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -2175,7 +2175,7 @@
         <v>26</v>
       </c>
       <c r="H39" t="n">
-        <v>2.0625</v>
+        <v>2.0615</v>
       </c>
       <c r="I39" t="n">
         <v>81.39</v>
@@ -2220,10 +2220,10 @@
         <v>26</v>
       </c>
       <c r="H40" t="n">
-        <v>2.0579</v>
+        <v>2.0546</v>
       </c>
       <c r="I40" t="n">
-        <v>80.98999999999999</v>
+        <v>80.98</v>
       </c>
       <c r="J40" t="n">
         <v>1806.3</v>
@@ -2265,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0539</v>
+        <v>2.0542</v>
       </c>
       <c r="I41" t="n">
         <v>80.66</v>
@@ -2310,10 +2310,10 @@
         <v>27</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0479</v>
+        <v>2.0442</v>
       </c>
       <c r="I42" t="n">
-        <v>78.67</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>1859.5</v>
@@ -2355,7 +2355,7 @@
         <v>28</v>
       </c>
       <c r="H43" t="n">
-        <v>2.0176</v>
+        <v>2.0181</v>
       </c>
       <c r="I43" t="n">
         <v>80.53</v>
@@ -2400,7 +2400,7 @@
         <v>28</v>
       </c>
       <c r="H44" t="n">
-        <v>1.9872</v>
+        <v>1.9892</v>
       </c>
       <c r="I44" t="n">
         <v>79.66</v>
@@ -2445,7 +2445,7 @@
         <v>26</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9719</v>
+        <v>1.9721</v>
       </c>
       <c r="I45" t="n">
         <v>79.09</v>
@@ -2490,7 +2490,7 @@
         <v>25</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9694</v>
+        <v>1.9691</v>
       </c>
       <c r="I46" t="n">
         <v>80.48</v>
@@ -2535,7 +2535,7 @@
         <v>27</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9376</v>
+        <v>1.9374</v>
       </c>
       <c r="I47" t="n">
         <v>77.94</v>
@@ -2580,7 +2580,7 @@
         <v>25</v>
       </c>
       <c r="H48" t="n">
-        <v>1.9105</v>
+        <v>1.9107</v>
       </c>
       <c r="I48" t="n">
         <v>76.58</v>
@@ -2625,10 +2625,10 @@
         <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>1.894</v>
+        <v>1.8925</v>
       </c>
       <c r="I49" t="n">
-        <v>75.05</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>1678.5</v>
@@ -2670,10 +2670,10 @@
         <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>1.8565</v>
+        <v>1.8583</v>
       </c>
       <c r="I50" t="n">
-        <v>77.37</v>
+        <v>77.38</v>
       </c>
       <c r="J50" t="n">
         <v>1828.6</v>
@@ -2715,7 +2715,7 @@
         <v>26</v>
       </c>
       <c r="H51" t="n">
-        <v>1.8466</v>
+        <v>1.8469</v>
       </c>
       <c r="I51" t="n">
         <v>76.81999999999999</v>
@@ -2760,10 +2760,10 @@
         <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>1.837</v>
+        <v>1.8346</v>
       </c>
       <c r="I52" t="n">
-        <v>75.67</v>
+        <v>75.66</v>
       </c>
       <c r="J52" t="n">
         <v>1747.8</v>
@@ -2805,10 +2805,10 @@
         <v>26</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8309</v>
+        <v>1.8297</v>
       </c>
       <c r="I53" t="n">
-        <v>77.15000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="J53" t="n">
         <v>1707.9</v>
@@ -2850,10 +2850,10 @@
         <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>1.8297</v>
+        <v>1.8231</v>
       </c>
       <c r="I54" t="n">
-        <v>75.70999999999999</v>
+        <v>75.69</v>
       </c>
       <c r="J54" t="n">
         <v>1728.9</v>
@@ -2895,7 +2895,7 @@
         <v>24</v>
       </c>
       <c r="H55" t="n">
-        <v>1.7913</v>
+        <v>1.7917</v>
       </c>
       <c r="I55" t="n">
         <v>75.56</v>
@@ -2940,7 +2940,7 @@
         <v>26</v>
       </c>
       <c r="H56" t="n">
-        <v>1.7657</v>
+        <v>1.7653</v>
       </c>
       <c r="I56" t="n">
         <v>75.09</v>
@@ -2985,7 +2985,7 @@
         <v>25</v>
       </c>
       <c r="H57" t="n">
-        <v>1.764</v>
+        <v>1.7627</v>
       </c>
       <c r="I57" t="n">
         <v>75.56</v>
@@ -3030,7 +3030,7 @@
         <v>26</v>
       </c>
       <c r="H58" t="n">
-        <v>1.7614</v>
+        <v>1.7613</v>
       </c>
       <c r="I58" t="n">
         <v>74.90000000000001</v>
@@ -3120,7 +3120,7 @@
         <v>24</v>
       </c>
       <c r="H60" t="n">
-        <v>1.7507</v>
+        <v>1.7509</v>
       </c>
       <c r="I60" t="n">
         <v>75.26000000000001</v>
@@ -3165,10 +3165,10 @@
         <v>24</v>
       </c>
       <c r="H61" t="n">
-        <v>1.6854</v>
+        <v>1.6818</v>
       </c>
       <c r="I61" t="n">
-        <v>73.54000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="J61" t="n">
         <v>1737.5</v>
@@ -3255,7 +3255,7 @@
         <v>28</v>
       </c>
       <c r="H63" t="n">
-        <v>1.6642</v>
+        <v>1.6634</v>
       </c>
       <c r="I63" t="n">
         <v>74.91</v>
@@ -3278,44 +3278,44 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C64" t="n">
-        <v>1321</v>
+        <v>1455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G64" t="n">
         <v>27</v>
       </c>
       <c r="H64" t="n">
-        <v>1.6611</v>
+        <v>1.6598</v>
       </c>
       <c r="I64" t="n">
-        <v>72.19</v>
+        <v>73.58</v>
       </c>
       <c r="J64" t="n">
-        <v>1607</v>
+        <v>1659</v>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L64" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="M64" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
@@ -3323,44 +3323,44 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C65" t="n">
-        <v>1455</v>
+        <v>1321</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Northwestern</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>big_ten</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G65" t="n">
         <v>27</v>
       </c>
       <c r="H65" t="n">
-        <v>1.6586</v>
+        <v>1.6587</v>
       </c>
       <c r="I65" t="n">
-        <v>73.58</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>1659</v>
+        <v>1607</v>
       </c>
       <c r="K65" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="L65" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="M65" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
@@ -3390,7 +3390,7 @@
         <v>26</v>
       </c>
       <c r="H66" t="n">
-        <v>1.658</v>
+        <v>1.6573</v>
       </c>
       <c r="I66" t="n">
         <v>73.14</v>
@@ -3435,10 +3435,10 @@
         <v>24</v>
       </c>
       <c r="H67" t="n">
-        <v>1.6561</v>
+        <v>1.6556</v>
       </c>
       <c r="I67" t="n">
-        <v>73.43000000000001</v>
+        <v>73.42</v>
       </c>
       <c r="J67" t="n">
         <v>1752.3</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="H68" t="n">
-        <v>1.6483</v>
+        <v>1.6485</v>
       </c>
       <c r="I68" t="n">
         <v>72.03</v>
@@ -3525,7 +3525,7 @@
         <v>28</v>
       </c>
       <c r="H69" t="n">
-        <v>1.6415</v>
+        <v>1.6402</v>
       </c>
       <c r="I69" t="n">
         <v>73.34</v>
@@ -3570,7 +3570,7 @@
         <v>26</v>
       </c>
       <c r="H70" t="n">
-        <v>1.6318</v>
+        <v>1.6341</v>
       </c>
       <c r="I70" t="n">
         <v>72.89</v>
@@ -3615,7 +3615,7 @@
         <v>25</v>
       </c>
       <c r="H71" t="n">
-        <v>1.6194</v>
+        <v>1.6193</v>
       </c>
       <c r="I71" t="n">
         <v>71.73999999999999</v>
@@ -3660,7 +3660,7 @@
         <v>21</v>
       </c>
       <c r="H72" t="n">
-        <v>1.6086</v>
+        <v>1.609</v>
       </c>
       <c r="I72" t="n">
         <v>72.66</v>
@@ -3705,10 +3705,10 @@
         <v>25</v>
       </c>
       <c r="H73" t="n">
-        <v>1.6052</v>
+        <v>1.6074</v>
       </c>
       <c r="I73" t="n">
-        <v>71.75</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>1640.5</v>
@@ -3750,10 +3750,10 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.5806</v>
+        <v>1.5826</v>
       </c>
       <c r="I74" t="n">
-        <v>72.75</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>1720.3</v>
@@ -3795,10 +3795,10 @@
         <v>28</v>
       </c>
       <c r="H75" t="n">
-        <v>1.5717</v>
+        <v>1.5749</v>
       </c>
       <c r="I75" t="n">
-        <v>70.87</v>
+        <v>70.88</v>
       </c>
       <c r="J75" t="n">
         <v>1573.9</v>
@@ -3840,10 +3840,10 @@
         <v>25</v>
       </c>
       <c r="H76" t="n">
-        <v>1.5699</v>
+        <v>1.5668</v>
       </c>
       <c r="I76" t="n">
-        <v>69.26000000000001</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>1690</v>
@@ -3885,10 +3885,10 @@
         <v>26</v>
       </c>
       <c r="H77" t="n">
-        <v>1.5312</v>
+        <v>1.5296</v>
       </c>
       <c r="I77" t="n">
-        <v>70.25</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>1780.4</v>
@@ -3930,10 +3930,10 @@
         <v>28</v>
       </c>
       <c r="H78" t="n">
-        <v>1.521</v>
+        <v>1.5233</v>
       </c>
       <c r="I78" t="n">
-        <v>70.89</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J78" t="n">
         <v>1719.1</v>
@@ -3953,44 +3953,44 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C79" t="n">
-        <v>1425</v>
+        <v>1160</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>big_ten</t>
+          <t>big_twelve</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H79" t="n">
         <v>1.5072</v>
       </c>
       <c r="I79" t="n">
-        <v>70.41</v>
+        <v>68.78</v>
       </c>
       <c r="J79" t="n">
-        <v>1743</v>
+        <v>1613.1</v>
       </c>
       <c r="K79" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L79" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M79" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80">
@@ -3998,44 +3998,44 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
+        <v>76</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1425</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>big_ten</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>128</v>
+      </c>
+      <c r="G80" t="n">
+        <v>23</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.5057</v>
+      </c>
+      <c r="I80" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1743</v>
+      </c>
+      <c r="K80" t="n">
         <v>79</v>
       </c>
-      <c r="C80" t="n">
-        <v>1160</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>big_twelve</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>127</v>
-      </c>
-      <c r="G80" t="n">
-        <v>24</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1.5071</v>
-      </c>
-      <c r="I80" t="n">
-        <v>68.78</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1613.1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>76</v>
-      </c>
       <c r="L80" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M80" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81">
@@ -4043,44 +4043,44 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>1207</v>
+        <v>1465</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Cal Baptist</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>big_east</t>
+          <t>wac</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H81" t="n">
         <v>1.4533</v>
       </c>
       <c r="I81" t="n">
-        <v>68.17</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>1586.2</v>
+        <v>1607.9</v>
       </c>
       <c r="K81" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="L81" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="M81" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82">
@@ -4088,44 +4088,44 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C82" t="n">
-        <v>1465</v>
+        <v>1207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cal Baptist</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>wac</t>
+          <t>big_east</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H82" t="n">
-        <v>1.451</v>
+        <v>1.4505</v>
       </c>
       <c r="I82" t="n">
-        <v>67</v>
+        <v>68.16</v>
       </c>
       <c r="J82" t="n">
-        <v>1607.9</v>
+        <v>1586.2</v>
       </c>
       <c r="K82" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="L82" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="M82" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
@@ -4155,7 +4155,7 @@
         <v>24</v>
       </c>
       <c r="H83" t="n">
-        <v>1.4468</v>
+        <v>1.448</v>
       </c>
       <c r="I83" t="n">
         <v>67.5</v>
@@ -4200,10 +4200,10 @@
         <v>24</v>
       </c>
       <c r="H84" t="n">
-        <v>1.4462</v>
+        <v>1.4473</v>
       </c>
       <c r="I84" t="n">
-        <v>67.70999999999999</v>
+        <v>67.72</v>
       </c>
       <c r="J84" t="n">
         <v>1675</v>
@@ -4245,7 +4245,7 @@
         <v>26</v>
       </c>
       <c r="H85" t="n">
-        <v>1.4443</v>
+        <v>1.4445</v>
       </c>
       <c r="I85" t="n">
         <v>67.40000000000001</v>
@@ -4268,7 +4268,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C86" t="n">
         <v>1344</v>
@@ -4290,10 +4290,10 @@
         <v>24</v>
       </c>
       <c r="H86" t="n">
-        <v>1.4333</v>
+        <v>1.4306</v>
       </c>
       <c r="I86" t="n">
-        <v>67.77</v>
+        <v>67.75</v>
       </c>
       <c r="J86" t="n">
         <v>1573.5</v>
@@ -4335,7 +4335,7 @@
         <v>25</v>
       </c>
       <c r="H87" t="n">
-        <v>1.4252</v>
+        <v>1.4255</v>
       </c>
       <c r="I87" t="n">
         <v>67.94</v>
@@ -4380,7 +4380,7 @@
         <v>23</v>
       </c>
       <c r="H88" t="n">
-        <v>1.4142</v>
+        <v>1.415</v>
       </c>
       <c r="I88" t="n">
         <v>66.95999999999999</v>
@@ -4425,7 +4425,7 @@
         <v>25</v>
       </c>
       <c r="H89" t="n">
-        <v>1.4132</v>
+        <v>1.4125</v>
       </c>
       <c r="I89" t="n">
         <v>68.23999999999999</v>
@@ -4470,7 +4470,7 @@
         <v>25</v>
       </c>
       <c r="H90" t="n">
-        <v>1.4115</v>
+        <v>1.4118</v>
       </c>
       <c r="I90" t="n">
         <v>67.77</v>
@@ -4515,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4085</v>
+        <v>1.4086</v>
       </c>
       <c r="I91" t="n">
         <v>68.31999999999999</v>
@@ -4560,10 +4560,10 @@
         <v>24</v>
       </c>
       <c r="H92" t="n">
-        <v>1.4067</v>
+        <v>1.4079</v>
       </c>
       <c r="I92" t="n">
-        <v>68.18000000000001</v>
+        <v>68.19</v>
       </c>
       <c r="J92" t="n">
         <v>1709.3</v>
@@ -4605,10 +4605,10 @@
         <v>24</v>
       </c>
       <c r="H93" t="n">
-        <v>1.4021</v>
+        <v>1.3994</v>
       </c>
       <c r="I93" t="n">
-        <v>66.38</v>
+        <v>66.37</v>
       </c>
       <c r="J93" t="n">
         <v>1603.3</v>
@@ -4628,44 +4628,44 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>1139</v>
+        <v>1393</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>big_east</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G94" t="n">
         <v>24</v>
       </c>
       <c r="H94" t="n">
-        <v>1.3854</v>
+        <v>1.3855</v>
       </c>
       <c r="I94" t="n">
-        <v>66.45</v>
+        <v>66.89</v>
       </c>
       <c r="J94" t="n">
-        <v>1626.2</v>
+        <v>1583.1</v>
       </c>
       <c r="K94" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L94" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M94" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95">
@@ -4673,44 +4673,44 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C95" t="n">
-        <v>1393</v>
+        <v>1139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>acc</t>
+          <t>big_east</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G95" t="n">
         <v>24</v>
       </c>
       <c r="H95" t="n">
-        <v>1.384</v>
+        <v>1.3852</v>
       </c>
       <c r="I95" t="n">
-        <v>66.89</v>
+        <v>66.45</v>
       </c>
       <c r="J95" t="n">
-        <v>1583.1</v>
+        <v>1626.2</v>
       </c>
       <c r="K95" t="n">
+        <v>84</v>
+      </c>
+      <c r="L95" t="n">
         <v>86</v>
       </c>
-      <c r="L95" t="n">
-        <v>83</v>
-      </c>
       <c r="M95" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96">
@@ -4740,7 +4740,7 @@
         <v>26</v>
       </c>
       <c r="H96" t="n">
-        <v>1.3785</v>
+        <v>1.3773</v>
       </c>
       <c r="I96" t="n">
         <v>65.53</v>
@@ -4785,10 +4785,10 @@
         <v>25</v>
       </c>
       <c r="H97" t="n">
-        <v>1.3703</v>
+        <v>1.372</v>
       </c>
       <c r="I97" t="n">
-        <v>67.05</v>
+        <v>67.06</v>
       </c>
       <c r="J97" t="n">
         <v>1655.8</v>
@@ -4830,7 +4830,7 @@
         <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>1.3623</v>
+        <v>1.3626</v>
       </c>
       <c r="I98" t="n">
         <v>66.68000000000001</v>
@@ -4875,10 +4875,10 @@
         <v>24</v>
       </c>
       <c r="H99" t="n">
-        <v>1.3326</v>
+        <v>1.3343</v>
       </c>
       <c r="I99" t="n">
-        <v>65.45</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>1536.9</v>
@@ -4920,7 +4920,7 @@
         <v>26</v>
       </c>
       <c r="H100" t="n">
-        <v>1.3206</v>
+        <v>1.3201</v>
       </c>
       <c r="I100" t="n">
         <v>63.19</v>
@@ -4965,7 +4965,7 @@
         <v>24</v>
       </c>
       <c r="H101" t="n">
-        <v>1.3191</v>
+        <v>1.3193</v>
       </c>
       <c r="I101" t="n">
         <v>66.15000000000001</v>
@@ -5010,7 +5010,7 @@
         <v>25</v>
       </c>
       <c r="H102" t="n">
-        <v>1.3055</v>
+        <v>1.3073</v>
       </c>
       <c r="I102" t="n">
         <v>61.9</v>
@@ -5055,7 +5055,7 @@
         <v>23</v>
       </c>
       <c r="H103" t="n">
-        <v>1.2943</v>
+        <v>1.2946</v>
       </c>
       <c r="I103" t="n">
         <v>64.03</v>
@@ -5100,7 +5100,7 @@
         <v>26</v>
       </c>
       <c r="H104" t="n">
-        <v>1.2712</v>
+        <v>1.2715</v>
       </c>
       <c r="I104" t="n">
         <v>64.95999999999999</v>
@@ -5145,7 +5145,7 @@
         <v>27</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2603</v>
+        <v>1.2586</v>
       </c>
       <c r="I105" t="n">
         <v>64.42</v>
@@ -5190,10 +5190,10 @@
         <v>26</v>
       </c>
       <c r="H106" t="n">
-        <v>1.2572</v>
+        <v>1.2557</v>
       </c>
       <c r="I106" t="n">
-        <v>63.45</v>
+        <v>63.44</v>
       </c>
       <c r="J106" t="n">
         <v>1593.8</v>
@@ -5235,10 +5235,10 @@
         <v>22</v>
       </c>
       <c r="H107" t="n">
-        <v>1.2563</v>
+        <v>1.255</v>
       </c>
       <c r="I107" t="n">
-        <v>63.92</v>
+        <v>63.91</v>
       </c>
       <c r="J107" t="n">
         <v>1567.9</v>
@@ -5303,44 +5303,44 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>St Joseph's PA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>a_ten</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G109" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H109" t="n">
-        <v>1.2423</v>
+        <v>1.2434</v>
       </c>
       <c r="I109" t="n">
-        <v>63.9</v>
+        <v>63.17</v>
       </c>
       <c r="J109" t="n">
-        <v>1550</v>
+        <v>1659.5</v>
       </c>
       <c r="K109" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="L109" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="M109" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110">
@@ -5348,44 +5348,44 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
+        <v>104</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1376</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>128</v>
+      </c>
+      <c r="G110" t="n">
+        <v>24</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.2424</v>
+      </c>
+      <c r="I110" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1550</v>
+      </c>
+      <c r="K110" t="n">
         <v>108</v>
       </c>
-      <c r="C110" t="n">
-        <v>1386</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>St Joseph's PA</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>a_ten</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>141</v>
-      </c>
-      <c r="G110" t="n">
-        <v>28</v>
-      </c>
-      <c r="H110" t="n">
-        <v>1.2417</v>
-      </c>
-      <c r="I110" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="J110" t="n">
-        <v>1659.5</v>
-      </c>
-      <c r="K110" t="n">
-        <v>121</v>
-      </c>
       <c r="L110" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="M110" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111">
@@ -5463,7 +5463,7 @@
         <v>1.2204</v>
       </c>
       <c r="I112" t="n">
-        <v>63.15</v>
+        <v>63.16</v>
       </c>
       <c r="J112" t="n">
         <v>1743.5</v>
@@ -5505,10 +5505,10 @@
         <v>24</v>
       </c>
       <c r="H113" t="n">
-        <v>1.1993</v>
+        <v>1.196</v>
       </c>
       <c r="I113" t="n">
-        <v>61.94</v>
+        <v>61.93</v>
       </c>
       <c r="J113" t="n">
         <v>1567.8</v>
@@ -5550,7 +5550,7 @@
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>1.1953</v>
+        <v>1.1952</v>
       </c>
       <c r="I114" t="n">
         <v>62.19</v>
@@ -5595,10 +5595,10 @@
         <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>1.1884</v>
+        <v>1.1919</v>
       </c>
       <c r="I115" t="n">
-        <v>62.21</v>
+        <v>62.22</v>
       </c>
       <c r="J115" t="n">
         <v>1537.5</v>
@@ -5640,7 +5640,7 @@
         <v>24</v>
       </c>
       <c r="H116" t="n">
-        <v>1.1875</v>
+        <v>1.1842</v>
       </c>
       <c r="I116" t="n">
         <v>61.9</v>
@@ -5685,7 +5685,7 @@
         <v>23</v>
       </c>
       <c r="H117" t="n">
-        <v>1.1827</v>
+        <v>1.1828</v>
       </c>
       <c r="I117" t="n">
         <v>61.09</v>
@@ -5730,7 +5730,7 @@
         <v>27</v>
       </c>
       <c r="H118" t="n">
-        <v>1.1813</v>
+        <v>1.1826</v>
       </c>
       <c r="I118" t="n">
         <v>61.64</v>
@@ -5775,7 +5775,7 @@
         <v>23</v>
       </c>
       <c r="H119" t="n">
-        <v>1.1729</v>
+        <v>1.1731</v>
       </c>
       <c r="I119" t="n">
         <v>60.16</v>
@@ -5820,7 +5820,7 @@
         <v>23</v>
       </c>
       <c r="H120" t="n">
-        <v>1.1708</v>
+        <v>1.1709</v>
       </c>
       <c r="I120" t="n">
         <v>61.04</v>
@@ -5843,44 +5843,44 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C121" t="n">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>S Illinois</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>mvc</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G121" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H121" t="n">
-        <v>1.1539</v>
+        <v>1.1545</v>
       </c>
       <c r="I121" t="n">
-        <v>61.78</v>
+        <v>59.39</v>
       </c>
       <c r="J121" t="n">
-        <v>1568.1</v>
+        <v>1478.8</v>
       </c>
       <c r="K121" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L121" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M121" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122">
@@ -5888,44 +5888,44 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C122" t="n">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>S Illinois</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>mvc</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G122" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H122" t="n">
-        <v>1.153</v>
+        <v>1.154</v>
       </c>
       <c r="I122" t="n">
-        <v>59.38</v>
+        <v>61.78</v>
       </c>
       <c r="J122" t="n">
-        <v>1478.8</v>
+        <v>1568.1</v>
       </c>
       <c r="K122" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L122" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M122" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123">
@@ -5955,10 +5955,10 @@
         <v>26</v>
       </c>
       <c r="H123" t="n">
-        <v>1.149</v>
+        <v>1.1495</v>
       </c>
       <c r="I123" t="n">
-        <v>59.33</v>
+        <v>59.34</v>
       </c>
       <c r="J123" t="n">
         <v>1560.1</v>
@@ -6000,7 +6000,7 @@
         <v>25</v>
       </c>
       <c r="H124" t="n">
-        <v>1.1469</v>
+        <v>1.1472</v>
       </c>
       <c r="I124" t="n">
         <v>59.63</v>
@@ -6045,7 +6045,7 @@
         <v>24</v>
       </c>
       <c r="H125" t="n">
-        <v>1.1285</v>
+        <v>1.1283</v>
       </c>
       <c r="I125" t="n">
         <v>60.8</v>
@@ -6135,10 +6135,10 @@
         <v>27</v>
       </c>
       <c r="H127" t="n">
-        <v>1.1233</v>
+        <v>1.1267</v>
       </c>
       <c r="I127" t="n">
-        <v>58.74</v>
+        <v>58.75</v>
       </c>
       <c r="J127" t="n">
         <v>1470.5</v>
@@ -6225,7 +6225,7 @@
         <v>24</v>
       </c>
       <c r="H129" t="n">
-        <v>1.1168</v>
+        <v>1.1167</v>
       </c>
       <c r="I129" t="n">
         <v>60.9</v>
@@ -6270,7 +6270,7 @@
         <v>24</v>
       </c>
       <c r="H130" t="n">
-        <v>1.1154</v>
+        <v>1.1155</v>
       </c>
       <c r="I130" t="n">
         <v>61.12</v>
@@ -6405,7 +6405,7 @@
         <v>25</v>
       </c>
       <c r="H133" t="n">
-        <v>1.0712</v>
+        <v>1.0715</v>
       </c>
       <c r="I133" t="n">
         <v>59.05</v>
@@ -6450,7 +6450,7 @@
         <v>24</v>
       </c>
       <c r="H134" t="n">
-        <v>1.07</v>
+        <v>1.0701</v>
       </c>
       <c r="I134" t="n">
         <v>58.9</v>
@@ -6540,7 +6540,7 @@
         <v>23</v>
       </c>
       <c r="H136" t="n">
-        <v>1.0642</v>
+        <v>1.0643</v>
       </c>
       <c r="I136" t="n">
         <v>59.36</v>
@@ -6630,7 +6630,7 @@
         <v>26</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0505</v>
+        <v>1.0507</v>
       </c>
       <c r="I138" t="n">
         <v>54.82</v>
@@ -6653,7 +6653,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C139" t="n">
         <v>1456</v>
@@ -6675,10 +6675,10 @@
         <v>22</v>
       </c>
       <c r="H139" t="n">
-        <v>1.0282</v>
+        <v>1.0255</v>
       </c>
       <c r="I139" t="n">
-        <v>55.74</v>
+        <v>55.73</v>
       </c>
       <c r="J139" t="n">
         <v>1530.8</v>
@@ -6810,7 +6810,7 @@
         <v>24</v>
       </c>
       <c r="H142" t="n">
-        <v>1.0085</v>
+        <v>1.0086</v>
       </c>
       <c r="I142" t="n">
         <v>55.74</v>
@@ -6900,7 +6900,7 @@
         <v>24</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9986</v>
+        <v>0.9987</v>
       </c>
       <c r="I144" t="n">
         <v>55.08</v>
@@ -6945,7 +6945,7 @@
         <v>24</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9931</v>
+        <v>0.9932</v>
       </c>
       <c r="I145" t="n">
         <v>55.37</v>
@@ -6990,7 +6990,7 @@
         <v>22</v>
       </c>
       <c r="H146" t="n">
-        <v>0.9866</v>
+        <v>0.9867</v>
       </c>
       <c r="I146" t="n">
         <v>55.71</v>
@@ -7035,7 +7035,7 @@
         <v>22</v>
       </c>
       <c r="H147" t="n">
-        <v>0.985</v>
+        <v>0.9823</v>
       </c>
       <c r="I147" t="n">
         <v>54.38</v>
@@ -7080,10 +7080,10 @@
         <v>22</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9685</v>
+        <v>0.9656</v>
       </c>
       <c r="I148" t="n">
-        <v>56.75</v>
+        <v>56.74</v>
       </c>
       <c r="J148" t="n">
         <v>1543.6</v>
@@ -7170,7 +7170,7 @@
         <v>23</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9502</v>
       </c>
       <c r="I150" t="n">
         <v>52.37</v>
@@ -7215,7 +7215,7 @@
         <v>22</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9476</v>
+        <v>0.9466</v>
       </c>
       <c r="I151" t="n">
         <v>54.85</v>
@@ -7260,7 +7260,7 @@
         <v>25</v>
       </c>
       <c r="H152" t="n">
-        <v>0.9363</v>
+        <v>0.9364</v>
       </c>
       <c r="I152" t="n">
         <v>51.7</v>
@@ -7283,44 +7283,44 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C153" t="n">
-        <v>1450</v>
+        <v>1398</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Washington St</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G153" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H153" t="n">
-        <v>0.9111</v>
+        <v>0.9112</v>
       </c>
       <c r="I153" t="n">
-        <v>54.21</v>
+        <v>52.38</v>
       </c>
       <c r="J153" t="n">
-        <v>1458.2</v>
+        <v>1466.9</v>
       </c>
       <c r="K153" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="L153" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="M153" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
     </row>
     <row r="154">
@@ -7328,44 +7328,44 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C154" t="n">
-        <v>1398</v>
+        <v>1364</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>UC Santa Barbara</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>big_west</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G154" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9111</v>
+        <v>0.9077</v>
       </c>
       <c r="I154" t="n">
-        <v>52.38</v>
+        <v>53.56</v>
       </c>
       <c r="J154" t="n">
-        <v>1466.9</v>
+        <v>1493.9</v>
       </c>
       <c r="K154" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="L154" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="M154" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155">
@@ -7373,44 +7373,44 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C155" t="n">
-        <v>1364</v>
+        <v>1450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>UC Santa Barbara</t>
+          <t>Washington St</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>big_west</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G155" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9076</v>
       </c>
       <c r="I155" t="n">
-        <v>53.56</v>
+        <v>54.19</v>
       </c>
       <c r="J155" t="n">
-        <v>1493.9</v>
+        <v>1458.2</v>
       </c>
       <c r="K155" t="n">
+        <v>146</v>
+      </c>
+      <c r="L155" t="n">
+        <v>137</v>
+      </c>
+      <c r="M155" t="n">
         <v>143</v>
-      </c>
-      <c r="L155" t="n">
-        <v>130</v>
-      </c>
-      <c r="M155" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="156">
@@ -7440,7 +7440,7 @@
         <v>25</v>
       </c>
       <c r="H156" t="n">
-        <v>0.905</v>
+        <v>0.9049</v>
       </c>
       <c r="I156" t="n">
         <v>53.63</v>
@@ -7485,7 +7485,7 @@
         <v>26</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9002</v>
+        <v>0.9005</v>
       </c>
       <c r="I157" t="n">
         <v>50.52</v>
@@ -7575,7 +7575,7 @@
         <v>25</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8759</v>
+        <v>0.8764</v>
       </c>
       <c r="I159" t="n">
         <v>53.87</v>
@@ -7620,7 +7620,7 @@
         <v>24</v>
       </c>
       <c r="H160" t="n">
-        <v>0.8747</v>
+        <v>0.8746</v>
       </c>
       <c r="I160" t="n">
         <v>52.03</v>
@@ -7665,7 +7665,7 @@
         <v>23</v>
       </c>
       <c r="H161" t="n">
-        <v>0.8699</v>
+        <v>0.8697</v>
       </c>
       <c r="I161" t="n">
         <v>51.99</v>
@@ -7755,7 +7755,7 @@
         <v>23</v>
       </c>
       <c r="H163" t="n">
-        <v>0.8656</v>
+        <v>0.8655</v>
       </c>
       <c r="I163" t="n">
         <v>52.26</v>
@@ -7800,7 +7800,7 @@
         <v>23</v>
       </c>
       <c r="H164" t="n">
-        <v>0.862</v>
+        <v>0.8622</v>
       </c>
       <c r="I164" t="n">
         <v>52.13</v>
@@ -7823,44 +7823,44 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C165" t="n">
-        <v>1373</v>
+        <v>1158</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Col Charleston</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G165" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H165" t="n">
-        <v>0.8575</v>
+        <v>0.8576</v>
       </c>
       <c r="I165" t="n">
-        <v>50.74</v>
+        <v>53.13</v>
       </c>
       <c r="J165" t="n">
-        <v>1478</v>
+        <v>1578.3</v>
       </c>
       <c r="K165" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="L165" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="M165" t="n">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="166">
@@ -7868,44 +7868,44 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C166" t="n">
-        <v>1158</v>
+        <v>1373</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Col Charleston</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G166" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H166" t="n">
-        <v>0.8559</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>53.12</v>
+        <v>50.74</v>
       </c>
       <c r="J166" t="n">
-        <v>1578.3</v>
+        <v>1478</v>
       </c>
       <c r="K166" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="L166" t="n">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="M166" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="167">
@@ -7935,10 +7935,10 @@
         <v>23</v>
       </c>
       <c r="H167" t="n">
-        <v>0.8535</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>52.9</v>
+        <v>52.91</v>
       </c>
       <c r="J167" t="n">
         <v>1489.7</v>
@@ -7980,7 +7980,7 @@
         <v>22</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8444</v>
       </c>
       <c r="I168" t="n">
         <v>52.4</v>
@@ -8025,7 +8025,7 @@
         <v>28</v>
       </c>
       <c r="H169" t="n">
-        <v>0.8434</v>
+        <v>0.8403</v>
       </c>
       <c r="I169" t="n">
         <v>51.33</v>
@@ -8070,7 +8070,7 @@
         <v>25</v>
       </c>
       <c r="H170" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8385</v>
       </c>
       <c r="I170" t="n">
         <v>49.36</v>
@@ -8205,10 +8205,10 @@
         <v>19</v>
       </c>
       <c r="H173" t="n">
-        <v>0.8343</v>
+        <v>0.8378</v>
       </c>
       <c r="I173" t="n">
-        <v>52.56</v>
+        <v>52.57</v>
       </c>
       <c r="J173" t="n">
         <v>1488.6</v>
@@ -8250,7 +8250,7 @@
         <v>27</v>
       </c>
       <c r="H174" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8275</v>
       </c>
       <c r="I174" t="n">
         <v>50.26</v>
@@ -8295,7 +8295,7 @@
         <v>26</v>
       </c>
       <c r="H175" t="n">
-        <v>0.8248</v>
+        <v>0.8247</v>
       </c>
       <c r="I175" t="n">
         <v>50.84</v>
@@ -8318,44 +8318,44 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C176" t="n">
-        <v>1333</v>
+        <v>1200</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Oregon St</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>a_ten</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G176" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H176" t="n">
-        <v>0.8224</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>51.63</v>
+        <v>51.12</v>
       </c>
       <c r="J176" t="n">
-        <v>1551.5</v>
+        <v>1464.9</v>
       </c>
       <c r="K176" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L176" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="M176" t="n">
-        <v>126</v>
+        <v>198</v>
       </c>
     </row>
     <row r="177">
@@ -8363,44 +8363,44 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
+        <v>167</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Oregon St</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>wcc</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>126</v>
+      </c>
+      <c r="G177" t="n">
+        <v>25</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.8208</v>
+      </c>
+      <c r="I177" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1551.5</v>
+      </c>
+      <c r="K177" t="n">
         <v>170</v>
       </c>
-      <c r="C177" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Fordham</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>a_ten</t>
-        </is>
-      </c>
-      <c r="F177" t="n">
-        <v>129</v>
-      </c>
-      <c r="G177" t="n">
-        <v>23</v>
-      </c>
-      <c r="H177" t="n">
-        <v>0.8221000000000001</v>
-      </c>
-      <c r="I177" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="J177" t="n">
-        <v>1464.9</v>
-      </c>
-      <c r="K177" t="n">
-        <v>174</v>
-      </c>
       <c r="L177" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="M177" t="n">
-        <v>198</v>
+        <v>126</v>
       </c>
     </row>
     <row r="178">
@@ -8430,7 +8430,7 @@
         <v>23</v>
       </c>
       <c r="H178" t="n">
-        <v>0.8203</v>
+        <v>0.8187</v>
       </c>
       <c r="I178" t="n">
         <v>51.28</v>
@@ -8475,7 +8475,7 @@
         <v>24</v>
       </c>
       <c r="H179" t="n">
-        <v>0.8114</v>
+        <v>0.8116</v>
       </c>
       <c r="I179" t="n">
         <v>50.85</v>
@@ -8520,7 +8520,7 @@
         <v>25</v>
       </c>
       <c r="H180" t="n">
-        <v>0.8015</v>
+        <v>0.8013</v>
       </c>
       <c r="I180" t="n">
         <v>49.96</v>
@@ -8565,10 +8565,10 @@
         <v>23</v>
       </c>
       <c r="H181" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>50.46</v>
+        <v>50.47</v>
       </c>
       <c r="J181" t="n">
         <v>1472</v>
@@ -8588,44 +8588,44 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C182" t="n">
-        <v>1324</v>
+        <v>1346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Oakland</t>
+          <t>Quinnipiac</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>horizon</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G182" t="n">
         <v>24</v>
       </c>
       <c r="H182" t="n">
-        <v>0.7897</v>
+        <v>0.7925</v>
       </c>
       <c r="I182" t="n">
-        <v>50.7</v>
+        <v>47.94</v>
       </c>
       <c r="J182" t="n">
-        <v>1512.3</v>
+        <v>1509.4</v>
       </c>
       <c r="K182" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="L182" t="n">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="M182" t="n">
-        <v>177</v>
+        <v>225</v>
       </c>
     </row>
     <row r="183">
@@ -8633,44 +8633,44 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C183" t="n">
-        <v>1346</v>
+        <v>1324</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Quinnipiac</t>
+          <t>Oakland</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>horizon</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G183" t="n">
         <v>24</v>
       </c>
       <c r="H183" t="n">
-        <v>0.7892</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>47.92</v>
+        <v>50.7</v>
       </c>
       <c r="J183" t="n">
-        <v>1509.4</v>
+        <v>1512.3</v>
       </c>
       <c r="K183" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="L183" t="n">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="M183" t="n">
-        <v>225</v>
+        <v>177</v>
       </c>
     </row>
     <row r="184">
@@ -8700,7 +8700,7 @@
         <v>25</v>
       </c>
       <c r="H184" t="n">
-        <v>0.7815</v>
+        <v>0.78</v>
       </c>
       <c r="I184" t="n">
         <v>49.44</v>
@@ -8723,44 +8723,44 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C185" t="n">
-        <v>1375</v>
+        <v>1394</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>South Alabama</t>
+          <t>TAM C. Christi</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>sun_belt</t>
+          <t>southland</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G185" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H185" t="n">
-        <v>0.777</v>
+        <v>0.7783</v>
       </c>
       <c r="I185" t="n">
-        <v>48.37</v>
+        <v>46.18</v>
       </c>
       <c r="J185" t="n">
-        <v>1548.1</v>
+        <v>1378.5</v>
       </c>
       <c r="K185" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L185" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="M185" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
     </row>
     <row r="186">
@@ -8768,44 +8768,44 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C186" t="n">
-        <v>1394</v>
+        <v>1375</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TAM C. Christi</t>
+          <t>South Alabama</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>southland</t>
+          <t>sun_belt</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G186" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H186" t="n">
-        <v>0.775</v>
+        <v>0.7752</v>
       </c>
       <c r="I186" t="n">
-        <v>46.16</v>
+        <v>48.36</v>
       </c>
       <c r="J186" t="n">
-        <v>1378.5</v>
+        <v>1548.1</v>
       </c>
       <c r="K186" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L186" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="M186" t="n">
-        <v>199</v>
+        <v>163</v>
       </c>
     </row>
     <row r="187">
@@ -8813,7 +8813,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C187" t="n">
         <v>1404</v>
@@ -8835,7 +8835,7 @@
         <v>24</v>
       </c>
       <c r="H187" t="n">
-        <v>0.7715</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="I187" t="n">
         <v>43.86</v>
@@ -8880,10 +8880,10 @@
         <v>25</v>
       </c>
       <c r="H188" t="n">
-        <v>0.7639</v>
+        <v>0.7618</v>
       </c>
       <c r="I188" t="n">
-        <v>49.74</v>
+        <v>49.73</v>
       </c>
       <c r="J188" t="n">
         <v>1515.3</v>
@@ -8970,7 +8970,7 @@
         <v>25</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7598</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="I190" t="n">
         <v>47.42</v>
@@ -8993,44 +8993,44 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C191" t="n">
-        <v>1144</v>
+        <v>1202</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>caa</t>
+          <t>southern</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G191" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H191" t="n">
         <v>0.7461</v>
       </c>
       <c r="I191" t="n">
-        <v>48.2</v>
+        <v>48.36</v>
       </c>
       <c r="J191" t="n">
-        <v>1405.6</v>
+        <v>1542.9</v>
       </c>
       <c r="K191" t="n">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="L191" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="M191" t="n">
-        <v>205</v>
+        <v>152</v>
       </c>
     </row>
     <row r="192">
@@ -9038,44 +9038,44 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C192" t="n">
-        <v>1202</v>
+        <v>1144</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>southern</t>
+          <t>caa</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G192" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H192" t="n">
-        <v>0.7459</v>
+        <v>0.7453</v>
       </c>
       <c r="I192" t="n">
-        <v>48.36</v>
+        <v>48.2</v>
       </c>
       <c r="J192" t="n">
-        <v>1542.9</v>
+        <v>1405.6</v>
       </c>
       <c r="K192" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="L192" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="M192" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="193">
@@ -9105,10 +9105,10 @@
         <v>24</v>
       </c>
       <c r="H193" t="n">
-        <v>0.7375</v>
+        <v>0.7358</v>
       </c>
       <c r="I193" t="n">
-        <v>48.11</v>
+        <v>48.1</v>
       </c>
       <c r="J193" t="n">
         <v>1505</v>
@@ -9128,44 +9128,44 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C194" t="n">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>ivy</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G194" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H194" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7347</v>
       </c>
       <c r="I194" t="n">
-        <v>47.64</v>
+        <v>48.16</v>
       </c>
       <c r="J194" t="n">
-        <v>1452.6</v>
+        <v>1466.3</v>
       </c>
       <c r="K194" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="L194" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="M194" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
     </row>
     <row r="195">
@@ -9173,44 +9173,44 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C195" t="n">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ivy</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G195" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H195" t="n">
-        <v>0.7346</v>
+        <v>0.7337</v>
       </c>
       <c r="I195" t="n">
-        <v>48.16</v>
+        <v>47.63</v>
       </c>
       <c r="J195" t="n">
-        <v>1466.3</v>
+        <v>1452.6</v>
       </c>
       <c r="K195" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="L195" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="M195" t="n">
-        <v>219</v>
+        <v>150</v>
       </c>
     </row>
     <row r="196">
@@ -9285,7 +9285,7 @@
         <v>25</v>
       </c>
       <c r="H197" t="n">
-        <v>0.7225</v>
+        <v>0.7228</v>
       </c>
       <c r="I197" t="n">
         <v>43.62</v>
@@ -9308,7 +9308,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C198" t="n">
         <v>1469</v>
@@ -9330,7 +9330,7 @@
         <v>23</v>
       </c>
       <c r="H198" t="n">
-        <v>0.7159</v>
+        <v>0.7155</v>
       </c>
       <c r="I198" t="n">
         <v>45.67</v>
@@ -9375,7 +9375,7 @@
         <v>25</v>
       </c>
       <c r="H199" t="n">
-        <v>0.7143</v>
+        <v>0.7149</v>
       </c>
       <c r="I199" t="n">
         <v>46.87</v>
@@ -9420,7 +9420,7 @@
         <v>24</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6984</v>
+        <v>0.6985</v>
       </c>
       <c r="I200" t="n">
         <v>43.89</v>
@@ -9465,10 +9465,10 @@
         <v>22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.6967</v>
+        <v>0.695</v>
       </c>
       <c r="I201" t="n">
-        <v>46.47</v>
+        <v>46.46</v>
       </c>
       <c r="J201" t="n">
         <v>1494.4</v>
@@ -9510,10 +9510,10 @@
         <v>24</v>
       </c>
       <c r="H202" t="n">
-        <v>0.6927</v>
+        <v>0.6938</v>
       </c>
       <c r="I202" t="n">
-        <v>45.98</v>
+        <v>45.99</v>
       </c>
       <c r="J202" t="n">
         <v>1504</v>
@@ -9555,7 +9555,7 @@
         <v>27</v>
       </c>
       <c r="H203" t="n">
-        <v>0.6876</v>
+        <v>0.6862</v>
       </c>
       <c r="I203" t="n">
         <v>45.2</v>
@@ -9600,10 +9600,10 @@
         <v>21</v>
       </c>
       <c r="H204" t="n">
-        <v>0.6849</v>
+        <v>0.6812</v>
       </c>
       <c r="I204" t="n">
-        <v>44.92</v>
+        <v>44.91</v>
       </c>
       <c r="J204" t="n">
         <v>1441.4</v>
@@ -9623,44 +9623,44 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C205" t="n">
-        <v>1254</v>
+        <v>1464</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Youngstown St</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>horizon</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G205" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H205" t="n">
-        <v>0.6811</v>
+        <v>0.6802</v>
       </c>
       <c r="I205" t="n">
-        <v>43.87</v>
+        <v>42.81</v>
       </c>
       <c r="J205" t="n">
-        <v>1418.2</v>
+        <v>1410.2</v>
       </c>
       <c r="K205" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="L205" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M205" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="206">
@@ -9668,44 +9668,44 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C206" t="n">
-        <v>1252</v>
+        <v>1198</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Lipscomb</t>
+          <t>Florida Intl</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>cusa</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G206" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H206" t="n">
-        <v>0.6807</v>
+        <v>0.6798</v>
       </c>
       <c r="I206" t="n">
-        <v>45.25</v>
+        <v>45.17</v>
       </c>
       <c r="J206" t="n">
-        <v>1481</v>
+        <v>1385.5</v>
       </c>
       <c r="K206" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L206" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M206" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="207">
@@ -9713,44 +9713,44 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C207" t="n">
-        <v>1464</v>
+        <v>1252</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Youngstown St</t>
+          <t>Lipscomb</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>horizon</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H207" t="n">
-        <v>0.6801</v>
+        <v>0.6795</v>
       </c>
       <c r="I207" t="n">
-        <v>42.81</v>
+        <v>45.24</v>
       </c>
       <c r="J207" t="n">
-        <v>1410.2</v>
+        <v>1481</v>
       </c>
       <c r="K207" t="n">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L207" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="M207" t="n">
-        <v>237</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208">
@@ -9758,44 +9758,44 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C208" t="n">
-        <v>1198</v>
+        <v>1254</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Florida Intl</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>cusa</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G208" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H208" t="n">
-        <v>0.6801</v>
+        <v>0.6791</v>
       </c>
       <c r="I208" t="n">
-        <v>45.17</v>
+        <v>43.86</v>
       </c>
       <c r="J208" t="n">
-        <v>1385.5</v>
+        <v>1418.2</v>
       </c>
       <c r="K208" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L208" t="n">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="M208" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209">
@@ -9803,44 +9803,44 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C209" t="n">
-        <v>1241</v>
+        <v>1441</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>W Carolina</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>sun_belt</t>
+          <t>southern</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G209" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H209" t="n">
-        <v>0.6765</v>
+        <v>0.6752</v>
       </c>
       <c r="I209" t="n">
-        <v>45.68</v>
+        <v>44.05</v>
       </c>
       <c r="J209" t="n">
-        <v>1507.6</v>
+        <v>1381.5</v>
       </c>
       <c r="K209" t="n">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="L209" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="M209" t="n">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="210">
@@ -9848,44 +9848,44 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C210" t="n">
-        <v>1441</v>
+        <v>1241</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>W Carolina</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>southern</t>
+          <t>sun_belt</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G210" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6751</v>
+        <v>0.6748</v>
       </c>
       <c r="I210" t="n">
-        <v>44.05</v>
+        <v>45.67</v>
       </c>
       <c r="J210" t="n">
-        <v>1381.5</v>
+        <v>1507.6</v>
       </c>
       <c r="K210" t="n">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="L210" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="M210" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
     </row>
     <row r="211">
@@ -9960,7 +9960,7 @@
         <v>28</v>
       </c>
       <c r="H212" t="n">
-        <v>0.6661</v>
+        <v>0.6663</v>
       </c>
       <c r="I212" t="n">
         <v>43.33</v>
@@ -10005,7 +10005,7 @@
         <v>24</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6619</v>
+        <v>0.662</v>
       </c>
       <c r="I213" t="n">
         <v>44.39</v>
@@ -10050,7 +10050,7 @@
         <v>24</v>
       </c>
       <c r="H214" t="n">
-        <v>0.6589</v>
+        <v>0.6587</v>
       </c>
       <c r="I214" t="n">
         <v>43.15</v>
@@ -10140,7 +10140,7 @@
         <v>23</v>
       </c>
       <c r="H216" t="n">
-        <v>0.6462</v>
+        <v>0.6463</v>
       </c>
       <c r="I216" t="n">
         <v>42.9</v>
@@ -10163,44 +10163,44 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C217" t="n">
-        <v>1285</v>
+        <v>1389</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>St Peter's</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>big_sky</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G217" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H217" t="n">
-        <v>0.6388</v>
+        <v>0.6384</v>
       </c>
       <c r="I217" t="n">
-        <v>42.64</v>
+        <v>40.3</v>
       </c>
       <c r="J217" t="n">
-        <v>1469.4</v>
+        <v>1438.5</v>
       </c>
       <c r="K217" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="L217" t="n">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M217" t="n">
-        <v>187</v>
+        <v>246</v>
       </c>
     </row>
     <row r="218">
@@ -10208,44 +10208,44 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C218" t="n">
-        <v>1389</v>
+        <v>1285</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>St Peter's</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>big_sky</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G218" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H218" t="n">
-        <v>0.6377</v>
+        <v>0.6383</v>
       </c>
       <c r="I218" t="n">
-        <v>40.3</v>
+        <v>42.63</v>
       </c>
       <c r="J218" t="n">
-        <v>1438.5</v>
+        <v>1469.4</v>
       </c>
       <c r="K218" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="L218" t="n">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="M218" t="n">
-        <v>246</v>
+        <v>187</v>
       </c>
     </row>
     <row r="219">
@@ -10275,10 +10275,10 @@
         <v>22</v>
       </c>
       <c r="H219" t="n">
-        <v>0.6351</v>
+        <v>0.6349</v>
       </c>
       <c r="I219" t="n">
-        <v>40.84</v>
+        <v>40.83</v>
       </c>
       <c r="J219" t="n">
         <v>1450.8</v>
@@ -10298,44 +10298,44 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C220" t="n">
-        <v>1453</v>
+        <v>1470</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>WI Green Bay</t>
+          <t>Tarleton St</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>horizon</t>
+          <t>wac</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G220" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H220" t="n">
-        <v>0.6324</v>
+        <v>0.6323</v>
       </c>
       <c r="I220" t="n">
-        <v>41.86</v>
+        <v>40.42</v>
       </c>
       <c r="J220" t="n">
-        <v>1381.1</v>
+        <v>1389.6</v>
       </c>
       <c r="K220" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="L220" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="M220" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="221">
@@ -10343,44 +10343,44 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C221" t="n">
-        <v>1470</v>
+        <v>1453</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Tarleton St</t>
+          <t>WI Green Bay</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>wac</t>
+          <t>horizon</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G221" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H221" t="n">
-        <v>0.6313</v>
+        <v>0.6323</v>
       </c>
       <c r="I221" t="n">
-        <v>40.42</v>
+        <v>41.86</v>
       </c>
       <c r="J221" t="n">
-        <v>1389.6</v>
+        <v>1381.1</v>
       </c>
       <c r="K221" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="L221" t="n">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="M221" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="222">
@@ -10410,7 +10410,7 @@
         <v>23</v>
       </c>
       <c r="H222" t="n">
-        <v>0.6274</v>
+        <v>0.6277</v>
       </c>
       <c r="I222" t="n">
         <v>43.17</v>
@@ -10455,7 +10455,7 @@
         <v>23</v>
       </c>
       <c r="H223" t="n">
-        <v>0.6249</v>
+        <v>0.6244</v>
       </c>
       <c r="I223" t="n">
         <v>43.25</v>
@@ -10500,7 +10500,7 @@
         <v>23</v>
       </c>
       <c r="H224" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="I224" t="n">
         <v>39.47</v>
@@ -10545,7 +10545,7 @@
         <v>23</v>
       </c>
       <c r="H225" t="n">
-        <v>0.6157</v>
+        <v>0.6156</v>
       </c>
       <c r="I225" t="n">
         <v>40.26</v>
@@ -10590,7 +10590,7 @@
         <v>27</v>
       </c>
       <c r="H226" t="n">
-        <v>0.6121</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="I226" t="n">
         <v>41.74</v>
@@ -10635,7 +10635,7 @@
         <v>25</v>
       </c>
       <c r="H227" t="n">
-        <v>0.6106</v>
+        <v>0.6112</v>
       </c>
       <c r="I227" t="n">
         <v>42.17</v>
@@ -10815,7 +10815,7 @@
         <v>23</v>
       </c>
       <c r="H231" t="n">
-        <v>0.5913</v>
+        <v>0.5915</v>
       </c>
       <c r="I231" t="n">
         <v>35.5</v>
@@ -10860,7 +10860,7 @@
         <v>24</v>
       </c>
       <c r="H232" t="n">
-        <v>0.5883</v>
+        <v>0.5887</v>
       </c>
       <c r="I232" t="n">
         <v>40.71</v>
@@ -10905,7 +10905,7 @@
         <v>25</v>
       </c>
       <c r="H233" t="n">
-        <v>0.5881</v>
+        <v>0.5886</v>
       </c>
       <c r="I233" t="n">
         <v>39.36</v>
@@ -10950,7 +10950,7 @@
         <v>21</v>
       </c>
       <c r="H234" t="n">
-        <v>0.5859</v>
+        <v>0.5871</v>
       </c>
       <c r="I234" t="n">
         <v>40.86</v>
@@ -10995,10 +10995,10 @@
         <v>25</v>
       </c>
       <c r="H235" t="n">
-        <v>0.5797</v>
+        <v>0.5808</v>
       </c>
       <c r="I235" t="n">
-        <v>41.23</v>
+        <v>41.24</v>
       </c>
       <c r="J235" t="n">
         <v>1374.8</v>
@@ -11040,7 +11040,7 @@
         <v>23</v>
       </c>
       <c r="H236" t="n">
-        <v>0.5719</v>
+        <v>0.572</v>
       </c>
       <c r="I236" t="n">
         <v>39.92</v>
@@ -11063,44 +11063,44 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C237" t="n">
-        <v>1233</v>
+        <v>1479</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Iona</t>
+          <t>Mercyhurst</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G237" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H237" t="n">
-        <v>0.5699</v>
+        <v>0.5712</v>
       </c>
       <c r="I237" t="n">
-        <v>39.69</v>
+        <v>34.38</v>
       </c>
       <c r="J237" t="n">
-        <v>1492.1</v>
+        <v>1378.3</v>
       </c>
       <c r="K237" t="n">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="L237" t="n">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="M237" t="n">
-        <v>241</v>
+        <v>311</v>
       </c>
     </row>
     <row r="238">
@@ -11108,44 +11108,44 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C238" t="n">
-        <v>1339</v>
+        <v>1233</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Iona</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G238" t="n">
         <v>24</v>
       </c>
       <c r="H238" t="n">
-        <v>0.5697</v>
+        <v>0.57</v>
       </c>
       <c r="I238" t="n">
-        <v>40</v>
+        <v>39.69</v>
       </c>
       <c r="J238" t="n">
-        <v>1416.8</v>
+        <v>1492.1</v>
       </c>
       <c r="K238" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="L238" t="n">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="M238" t="n">
-        <v>192</v>
+        <v>241</v>
       </c>
     </row>
     <row r="239">
@@ -11153,44 +11153,44 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="C239" t="n">
-        <v>1479</v>
+        <v>1339</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Mercyhurst</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G239" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5693</v>
+        <v>0.5692</v>
       </c>
       <c r="I239" t="n">
-        <v>34.37</v>
+        <v>40</v>
       </c>
       <c r="J239" t="n">
-        <v>1378.3</v>
+        <v>1416.8</v>
       </c>
       <c r="K239" t="n">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="L239" t="n">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="M239" t="n">
-        <v>311</v>
+        <v>192</v>
       </c>
     </row>
     <row r="240">
@@ -11220,7 +11220,7 @@
         <v>23</v>
       </c>
       <c r="H240" t="n">
-        <v>0.5512</v>
+        <v>0.5513</v>
       </c>
       <c r="I240" t="n">
         <v>39.33</v>
@@ -11288,44 +11288,44 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C242" t="n">
-        <v>1195</v>
+        <v>1421</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>FGCU</t>
+          <t>UNC Asheville</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>big_south</t>
         </is>
       </c>
       <c r="F242" t="n">
         <v>124</v>
       </c>
       <c r="G242" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H242" t="n">
-        <v>0.5422</v>
+        <v>0.543</v>
       </c>
       <c r="I242" t="n">
-        <v>38.82</v>
+        <v>36.3</v>
       </c>
       <c r="J242" t="n">
-        <v>1400.1</v>
+        <v>1383.4</v>
       </c>
       <c r="K242" t="n">
+        <v>239</v>
+      </c>
+      <c r="L242" t="n">
+        <v>246</v>
+      </c>
+      <c r="M242" t="n">
         <v>247</v>
-      </c>
-      <c r="L242" t="n">
-        <v>244</v>
-      </c>
-      <c r="M242" t="n">
-        <v>248</v>
       </c>
     </row>
     <row r="243">
@@ -11333,44 +11333,44 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C243" t="n">
-        <v>1421</v>
+        <v>1195</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>UNC Asheville</t>
+          <t>FGCU</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>big_south</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F243" t="n">
         <v>124</v>
       </c>
       <c r="G243" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H243" t="n">
-        <v>0.5417</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="I243" t="n">
-        <v>36.3</v>
+        <v>38.82</v>
       </c>
       <c r="J243" t="n">
-        <v>1383.4</v>
+        <v>1400.1</v>
       </c>
       <c r="K243" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L243" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M243" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="244">
@@ -11400,7 +11400,7 @@
         <v>24</v>
       </c>
       <c r="H244" t="n">
-        <v>0.5391</v>
+        <v>0.5392</v>
       </c>
       <c r="I244" t="n">
         <v>37.36</v>
@@ -11423,44 +11423,44 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C245" t="n">
-        <v>1347</v>
+        <v>1311</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Radford</t>
+          <t>Nicholls St</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>big_south</t>
+          <t>southland</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G245" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H245" t="n">
-        <v>0.5373</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>36.26</v>
+        <v>37.24</v>
       </c>
       <c r="J245" t="n">
-        <v>1376.6</v>
+        <v>1364.3</v>
       </c>
       <c r="K245" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L245" t="n">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="M245" t="n">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="246">
@@ -11468,44 +11468,44 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C246" t="n">
-        <v>1311</v>
+        <v>1347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Nicholls St</t>
+          <t>Radford</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>southland</t>
+          <t>big_south</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G246" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H246" t="n">
-        <v>0.5366</v>
+        <v>0.5373</v>
       </c>
       <c r="I246" t="n">
-        <v>37.23</v>
+        <v>36.26</v>
       </c>
       <c r="J246" t="n">
-        <v>1364.3</v>
+        <v>1376.6</v>
       </c>
       <c r="K246" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L246" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="M246" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="247">
@@ -11535,10 +11535,10 @@
         <v>24</v>
       </c>
       <c r="H247" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="I247" t="n">
-        <v>36.89</v>
+        <v>36.9</v>
       </c>
       <c r="J247" t="n">
         <v>1357.9</v>
@@ -11580,7 +11580,7 @@
         <v>23</v>
       </c>
       <c r="H248" t="n">
-        <v>0.5233</v>
+        <v>0.5231</v>
       </c>
       <c r="I248" t="n">
         <v>37.57</v>
@@ -11670,7 +11670,7 @@
         <v>24</v>
       </c>
       <c r="H250" t="n">
-        <v>0.5188</v>
+        <v>0.5189</v>
       </c>
       <c r="I250" t="n">
         <v>38.7</v>
@@ -11715,7 +11715,7 @@
         <v>23</v>
       </c>
       <c r="H251" t="n">
-        <v>0.5142</v>
+        <v>0.5143</v>
       </c>
       <c r="I251" t="n">
         <v>37.49</v>
@@ -11760,7 +11760,7 @@
         <v>21</v>
       </c>
       <c r="H252" t="n">
-        <v>0.5131</v>
+        <v>0.5139</v>
       </c>
       <c r="I252" t="n">
         <v>34.98</v>
@@ -11783,44 +11783,44 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C253" t="n">
-        <v>1188</v>
+        <v>1157</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SIUE</t>
+          <t>Coastal Car</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>sun_belt</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G253" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H253" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5121</v>
       </c>
       <c r="I253" t="n">
-        <v>36.31</v>
+        <v>37.02</v>
       </c>
       <c r="J253" t="n">
-        <v>1461.8</v>
+        <v>1428.2</v>
       </c>
       <c r="K253" t="n">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="L253" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="M253" t="n">
-        <v>259</v>
+        <v>208</v>
       </c>
     </row>
     <row r="254">
@@ -11828,44 +11828,44 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C254" t="n">
-        <v>1360</v>
+        <v>1188</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SIUE</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>wcc</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G254" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H254" t="n">
-        <v>0.5098</v>
+        <v>0.5108</v>
       </c>
       <c r="I254" t="n">
-        <v>37.09</v>
+        <v>36.31</v>
       </c>
       <c r="J254" t="n">
-        <v>1362</v>
+        <v>1461.8</v>
       </c>
       <c r="K254" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="L254" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="M254" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
     </row>
     <row r="255">
@@ -11873,44 +11873,44 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C255" t="n">
-        <v>1157</v>
+        <v>1360</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Coastal Car</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>sun_belt</t>
+          <t>wcc</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G255" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H255" t="n">
-        <v>0.5092</v>
+        <v>0.5099</v>
       </c>
       <c r="I255" t="n">
-        <v>37.01</v>
+        <v>37.09</v>
       </c>
       <c r="J255" t="n">
-        <v>1428.2</v>
+        <v>1362</v>
       </c>
       <c r="K255" t="n">
+        <v>234</v>
+      </c>
+      <c r="L255" t="n">
+        <v>224</v>
+      </c>
+      <c r="M255" t="n">
         <v>229</v>
-      </c>
-      <c r="L255" t="n">
-        <v>247</v>
-      </c>
-      <c r="M255" t="n">
-        <v>208</v>
       </c>
     </row>
     <row r="256">
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="H256" t="n">
-        <v>0.498</v>
+        <v>0.4981</v>
       </c>
       <c r="I256" t="n">
         <v>36.77</v>
@@ -11985,7 +11985,7 @@
         <v>21</v>
       </c>
       <c r="H257" t="n">
-        <v>0.4909</v>
+        <v>0.491</v>
       </c>
       <c r="I257" t="n">
         <v>36.64</v>
@@ -12030,7 +12030,7 @@
         <v>26</v>
       </c>
       <c r="H258" t="n">
-        <v>0.487</v>
+        <v>0.4871</v>
       </c>
       <c r="I258" t="n">
         <v>33.49</v>
@@ -12075,7 +12075,7 @@
         <v>22</v>
       </c>
       <c r="H259" t="n">
-        <v>0.4845</v>
+        <v>0.4844</v>
       </c>
       <c r="I259" t="n">
         <v>29.8</v>
@@ -12120,7 +12120,7 @@
         <v>23</v>
       </c>
       <c r="H260" t="n">
-        <v>0.4845</v>
+        <v>0.4841</v>
       </c>
       <c r="I260" t="n">
         <v>35.95</v>
@@ -12165,7 +12165,7 @@
         <v>22</v>
       </c>
       <c r="H261" t="n">
-        <v>0.4826</v>
+        <v>0.4818</v>
       </c>
       <c r="I261" t="n">
         <v>35.25</v>
@@ -12233,7 +12233,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C263" t="n">
         <v>1287</v>
@@ -12255,10 +12255,10 @@
         <v>23</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4768</v>
+        <v>0.4781</v>
       </c>
       <c r="I263" t="n">
-        <v>33.45</v>
+        <v>33.46</v>
       </c>
       <c r="J263" t="n">
         <v>1409.9</v>
@@ -12300,10 +12300,10 @@
         <v>23</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4757</v>
+        <v>0.4751</v>
       </c>
       <c r="I264" t="n">
-        <v>33.83</v>
+        <v>33.82</v>
       </c>
       <c r="J264" t="n">
         <v>1390.4</v>
@@ -12345,7 +12345,7 @@
         <v>23</v>
       </c>
       <c r="H265" t="n">
-        <v>0.4715</v>
+        <v>0.4692</v>
       </c>
       <c r="I265" t="n">
         <v>35.38</v>
@@ -12435,7 +12435,7 @@
         <v>23</v>
       </c>
       <c r="H267" t="n">
-        <v>0.4626</v>
+        <v>0.4627</v>
       </c>
       <c r="I267" t="n">
         <v>33.53</v>
@@ -12480,7 +12480,7 @@
         <v>23</v>
       </c>
       <c r="H268" t="n">
-        <v>0.4619</v>
+        <v>0.462</v>
       </c>
       <c r="I268" t="n">
         <v>33.46</v>
@@ -12503,44 +12503,44 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="C269" t="n">
-        <v>1226</v>
+        <v>1447</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Idaho St</t>
+          <t>Wagner</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>big_sky</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G269" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H269" t="n">
-        <v>0.4604</v>
+        <v>0.4608</v>
       </c>
       <c r="I269" t="n">
-        <v>33.42</v>
+        <v>29.21</v>
       </c>
       <c r="J269" t="n">
-        <v>1332.5</v>
+        <v>1328.3</v>
       </c>
       <c r="K269" t="n">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="L269" t="n">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="M269" t="n">
-        <v>253</v>
+        <v>323</v>
       </c>
     </row>
     <row r="270">
@@ -12548,44 +12548,44 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C270" t="n">
-        <v>1431</v>
+        <v>1226</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>UTEP</t>
+          <t>Idaho St</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>cusa</t>
+          <t>big_sky</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G270" t="n">
         <v>24</v>
       </c>
       <c r="H270" t="n">
-        <v>0.46</v>
+        <v>0.4605</v>
       </c>
       <c r="I270" t="n">
-        <v>33.7</v>
+        <v>33.42</v>
       </c>
       <c r="J270" t="n">
-        <v>1398.4</v>
+        <v>1332.5</v>
       </c>
       <c r="K270" t="n">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="L270" t="n">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="M270" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="271">
@@ -12593,44 +12593,44 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="C271" t="n">
-        <v>1447</v>
+        <v>1431</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Wagner</t>
+          <t>UTEP</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>cusa</t>
         </is>
       </c>
       <c r="F271" t="n">
         <v>124</v>
       </c>
       <c r="G271" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H271" t="n">
-        <v>0.4596</v>
+        <v>0.4597</v>
       </c>
       <c r="I271" t="n">
-        <v>29.21</v>
+        <v>33.7</v>
       </c>
       <c r="J271" t="n">
-        <v>1328.3</v>
+        <v>1398.4</v>
       </c>
       <c r="K271" t="n">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="L271" t="n">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="M271" t="n">
-        <v>323</v>
+        <v>240</v>
       </c>
     </row>
     <row r="272">
@@ -12660,7 +12660,7 @@
         <v>22</v>
       </c>
       <c r="H272" t="n">
-        <v>0.4564</v>
+        <v>0.4565</v>
       </c>
       <c r="I272" t="n">
         <v>32.15</v>
@@ -12705,7 +12705,7 @@
         <v>24</v>
       </c>
       <c r="H273" t="n">
-        <v>0.4504</v>
+        <v>0.4516</v>
       </c>
       <c r="I273" t="n">
         <v>31.92</v>
@@ -12750,7 +12750,7 @@
         <v>24</v>
       </c>
       <c r="H274" t="n">
-        <v>0.4475</v>
+        <v>0.4476</v>
       </c>
       <c r="I274" t="n">
         <v>32.63</v>
@@ -12795,7 +12795,7 @@
         <v>22</v>
       </c>
       <c r="H275" t="n">
-        <v>0.4473</v>
+        <v>0.4474</v>
       </c>
       <c r="I275" t="n">
         <v>31.05</v>
@@ -12840,7 +12840,7 @@
         <v>24</v>
       </c>
       <c r="H276" t="n">
-        <v>0.4432</v>
+        <v>0.4433</v>
       </c>
       <c r="I276" t="n">
         <v>34.35</v>
@@ -12863,44 +12863,44 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C277" t="n">
-        <v>1149</v>
+        <v>1303</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Charleston So</t>
+          <t>NE Omaha</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>big_south</t>
+          <t>summit</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G277" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H277" t="n">
-        <v>0.4412</v>
+        <v>0.4409</v>
       </c>
       <c r="I277" t="n">
-        <v>32.97</v>
+        <v>32.14</v>
       </c>
       <c r="J277" t="n">
-        <v>1324.7</v>
+        <v>1373.9</v>
       </c>
       <c r="K277" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="L277" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="M277" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="278">
@@ -12908,44 +12908,44 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C278" t="n">
-        <v>1303</v>
+        <v>1149</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NE Omaha</t>
+          <t>Charleston So</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>summit</t>
+          <t>big_south</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G278" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H278" t="n">
-        <v>0.4397</v>
+        <v>0.4408</v>
       </c>
       <c r="I278" t="n">
-        <v>32.14</v>
+        <v>32.96</v>
       </c>
       <c r="J278" t="n">
-        <v>1373.9</v>
+        <v>1324.7</v>
       </c>
       <c r="K278" t="n">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="L278" t="n">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="M278" t="n">
-        <v>244</v>
+        <v>285</v>
       </c>
     </row>
     <row r="279">
@@ -13020,7 +13020,7 @@
         <v>23</v>
       </c>
       <c r="H280" t="n">
-        <v>0.4348</v>
+        <v>0.4349</v>
       </c>
       <c r="I280" t="n">
         <v>32.99</v>
@@ -13065,7 +13065,7 @@
         <v>25</v>
       </c>
       <c r="H281" t="n">
-        <v>0.4345</v>
+        <v>0.434</v>
       </c>
       <c r="I281" t="n">
         <v>32.61</v>
@@ -13155,7 +13155,7 @@
         <v>26</v>
       </c>
       <c r="H283" t="n">
-        <v>0.4333</v>
+        <v>0.4334</v>
       </c>
       <c r="I283" t="n">
         <v>30.98</v>
@@ -13200,7 +13200,7 @@
         <v>23</v>
       </c>
       <c r="H284" t="n">
-        <v>0.4192</v>
+        <v>0.4193</v>
       </c>
       <c r="I284" t="n">
         <v>30.32</v>
@@ -13290,7 +13290,7 @@
         <v>22</v>
       </c>
       <c r="H286" t="n">
-        <v>0.4174</v>
+        <v>0.4175</v>
       </c>
       <c r="I286" t="n">
         <v>32.23</v>
@@ -13335,7 +13335,7 @@
         <v>24</v>
       </c>
       <c r="H287" t="n">
-        <v>0.4164</v>
+        <v>0.4154</v>
       </c>
       <c r="I287" t="n">
         <v>32.8</v>
@@ -13358,44 +13358,44 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C288" t="n">
-        <v>1148</v>
+        <v>1184</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Central Conn</t>
+          <t>E Kentucky</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>nec</t>
+          <t>a_sun</t>
         </is>
       </c>
       <c r="F288" t="n">
         <v>121</v>
       </c>
       <c r="G288" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H288" t="n">
-        <v>0.4148</v>
+        <v>0.4145</v>
       </c>
       <c r="I288" t="n">
-        <v>30.13</v>
+        <v>29.36</v>
       </c>
       <c r="J288" t="n">
-        <v>1455.5</v>
+        <v>1325</v>
       </c>
       <c r="K288" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L288" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="M288" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="289">
@@ -13403,44 +13403,44 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C289" t="n">
-        <v>1184</v>
+        <v>1148</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>E Kentucky</t>
+          <t>Central Conn</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>a_sun</t>
+          <t>nec</t>
         </is>
       </c>
       <c r="F289" t="n">
         <v>121</v>
       </c>
       <c r="G289" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H289" t="n">
         <v>0.4144</v>
       </c>
       <c r="I289" t="n">
-        <v>29.36</v>
+        <v>30.12</v>
       </c>
       <c r="J289" t="n">
-        <v>1325</v>
+        <v>1455.5</v>
       </c>
       <c r="K289" t="n">
+        <v>289</v>
+      </c>
+      <c r="L289" t="n">
+        <v>306</v>
+      </c>
+      <c r="M289" t="n">
         <v>291</v>
-      </c>
-      <c r="L289" t="n">
-        <v>297</v>
-      </c>
-      <c r="M289" t="n">
-        <v>294</v>
       </c>
     </row>
     <row r="290">
@@ -13470,7 +13470,7 @@
         <v>22</v>
       </c>
       <c r="H290" t="n">
-        <v>0.4124</v>
+        <v>0.4109</v>
       </c>
       <c r="I290" t="n">
         <v>31.38</v>
@@ -13493,44 +13493,44 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="C291" t="n">
-        <v>1250</v>
+        <v>1313</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>Norfolk St</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>patriot</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G291" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H291" t="n">
-        <v>0.4073</v>
+        <v>0.4083</v>
       </c>
       <c r="I291" t="n">
-        <v>30.08</v>
+        <v>27.3</v>
       </c>
       <c r="J291" t="n">
-        <v>1325.5</v>
+        <v>1369.1</v>
       </c>
       <c r="K291" t="n">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="L291" t="n">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="M291" t="n">
-        <v>283</v>
+        <v>316</v>
       </c>
     </row>
     <row r="292">
@@ -13538,44 +13538,44 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C292" t="n">
-        <v>1313</v>
+        <v>1250</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Norfolk St</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>patriot</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G292" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H292" t="n">
-        <v>0.4071</v>
+        <v>0.405</v>
       </c>
       <c r="I292" t="n">
-        <v>27.3</v>
+        <v>30.07</v>
       </c>
       <c r="J292" t="n">
-        <v>1369.1</v>
+        <v>1325.5</v>
       </c>
       <c r="K292" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="L292" t="n">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="M292" t="n">
-        <v>316</v>
+        <v>283</v>
       </c>
     </row>
     <row r="293">
@@ -13605,7 +13605,7 @@
         <v>21</v>
       </c>
       <c r="H293" t="n">
-        <v>0.4013</v>
+        <v>0.4004</v>
       </c>
       <c r="I293" t="n">
         <v>31.48</v>
@@ -13650,7 +13650,7 @@
         <v>22</v>
       </c>
       <c r="H294" t="n">
-        <v>0.399</v>
+        <v>0.3978</v>
       </c>
       <c r="I294" t="n">
         <v>27.15</v>
@@ -13695,10 +13695,10 @@
         <v>23</v>
       </c>
       <c r="H295" t="n">
-        <v>0.3932</v>
+        <v>0.3937</v>
       </c>
       <c r="I295" t="n">
-        <v>30.76</v>
+        <v>30.77</v>
       </c>
       <c r="J295" t="n">
         <v>1310.7</v>
@@ -13740,7 +13740,7 @@
         <v>23</v>
       </c>
       <c r="H296" t="n">
-        <v>0.3928</v>
+        <v>0.3929</v>
       </c>
       <c r="I296" t="n">
         <v>29.54</v>
@@ -13830,7 +13830,7 @@
         <v>16</v>
       </c>
       <c r="H298" t="n">
-        <v>0.3873</v>
+        <v>0.3874</v>
       </c>
       <c r="I298" t="n">
         <v>29.99</v>
@@ -13875,7 +13875,7 @@
         <v>25</v>
       </c>
       <c r="H299" t="n">
-        <v>0.3835</v>
+        <v>0.3836</v>
       </c>
       <c r="I299" t="n">
         <v>27.72</v>
@@ -13898,44 +13898,44 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C300" t="n">
-        <v>1174</v>
+        <v>1367</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>SC Upstate</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>cusa</t>
+          <t>big_south</t>
         </is>
       </c>
       <c r="F300" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G300" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H300" t="n">
-        <v>0.38</v>
+        <v>0.3784</v>
       </c>
       <c r="I300" t="n">
-        <v>29.47</v>
+        <v>27.33</v>
       </c>
       <c r="J300" t="n">
-        <v>1379.6</v>
+        <v>1288.4</v>
       </c>
       <c r="K300" t="n">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="L300" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M300" t="n">
-        <v>264</v>
+        <v>304</v>
       </c>
     </row>
     <row r="301">
@@ -13943,44 +13943,44 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C301" t="n">
-        <v>1367</v>
+        <v>1123</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>SC Upstate</t>
+          <t>Ball St</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>big_south</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="F301" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G301" t="n">
         <v>22</v>
       </c>
       <c r="H301" t="n">
-        <v>0.3789</v>
+        <v>0.3783</v>
       </c>
       <c r="I301" t="n">
-        <v>27.33</v>
+        <v>29.48</v>
       </c>
       <c r="J301" t="n">
-        <v>1288.4</v>
+        <v>1325.1</v>
       </c>
       <c r="K301" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="L301" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="M301" t="n">
-        <v>304</v>
+        <v>273</v>
       </c>
     </row>
     <row r="302">
@@ -13988,44 +13988,44 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
+        <v>294</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1174</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>cusa</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>124</v>
+      </c>
+      <c r="G302" t="n">
+        <v>24</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="I302" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1379.6</v>
+      </c>
+      <c r="K302" t="n">
+        <v>287</v>
+      </c>
+      <c r="L302" t="n">
         <v>293</v>
       </c>
-      <c r="C302" t="n">
-        <v>1123</v>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Ball St</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>mac</t>
-        </is>
-      </c>
-      <c r="F302" t="n">
-        <v>123</v>
-      </c>
-      <c r="G302" t="n">
-        <v>22</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0.3782</v>
-      </c>
-      <c r="I302" t="n">
-        <v>29.48</v>
-      </c>
-      <c r="J302" t="n">
-        <v>1325.1</v>
-      </c>
-      <c r="K302" t="n">
-        <v>299</v>
-      </c>
-      <c r="L302" t="n">
-        <v>294</v>
-      </c>
       <c r="M302" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="303">
@@ -14055,7 +14055,7 @@
         <v>23</v>
       </c>
       <c r="H303" t="n">
-        <v>0.3765</v>
+        <v>0.3766</v>
       </c>
       <c r="I303" t="n">
         <v>28.59</v>
@@ -14100,7 +14100,7 @@
         <v>24</v>
       </c>
       <c r="H304" t="n">
-        <v>0.3734</v>
+        <v>0.3735</v>
       </c>
       <c r="I304" t="n">
         <v>26.91</v>
@@ -14123,44 +14123,44 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C305" t="n">
-        <v>1151</v>
+        <v>1262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Chattanooga</t>
+          <t>MA Lowell</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>southern</t>
+          <t>aec</t>
         </is>
       </c>
       <c r="F305" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G305" t="n">
         <v>23</v>
       </c>
       <c r="H305" t="n">
-        <v>0.3711</v>
+        <v>0.3698</v>
       </c>
       <c r="I305" t="n">
-        <v>29.2</v>
+        <v>26.95</v>
       </c>
       <c r="J305" t="n">
-        <v>1392.1</v>
+        <v>1350.1</v>
       </c>
       <c r="K305" t="n">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="L305" t="n">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="M305" t="n">
-        <v>262</v>
+        <v>306</v>
       </c>
     </row>
     <row r="306">
@@ -14168,44 +14168,44 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C306" t="n">
-        <v>1262</v>
+        <v>1151</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>MA Lowell</t>
+          <t>Chattanooga</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>aec</t>
+          <t>southern</t>
         </is>
       </c>
       <c r="F306" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G306" t="n">
         <v>23</v>
       </c>
       <c r="H306" t="n">
-        <v>0.3697</v>
+        <v>0.3688</v>
       </c>
       <c r="I306" t="n">
-        <v>26.95</v>
+        <v>29.19</v>
       </c>
       <c r="J306" t="n">
-        <v>1350.1</v>
+        <v>1392.1</v>
       </c>
       <c r="K306" t="n">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="L306" t="n">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="M306" t="n">
-        <v>306</v>
+        <v>262</v>
       </c>
     </row>
     <row r="307">
@@ -14235,7 +14235,7 @@
         <v>23</v>
       </c>
       <c r="H307" t="n">
-        <v>0.3682</v>
+        <v>0.3686</v>
       </c>
       <c r="I307" t="n">
         <v>28.4</v>
@@ -14258,7 +14258,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C308" t="n">
         <v>1481</v>
@@ -14280,10 +14280,10 @@
         <v>22</v>
       </c>
       <c r="H308" t="n">
-        <v>0.3644</v>
+        <v>0.3648</v>
       </c>
       <c r="I308" t="n">
-        <v>25.01</v>
+        <v>25.02</v>
       </c>
       <c r="J308" t="n">
         <v>1377.5</v>
@@ -14370,7 +14370,7 @@
         <v>24</v>
       </c>
       <c r="H310" t="n">
-        <v>0.3559</v>
+        <v>0.3564</v>
       </c>
       <c r="I310" t="n">
         <v>27.64</v>
@@ -14415,7 +14415,7 @@
         <v>21</v>
       </c>
       <c r="H311" t="n">
-        <v>0.3557</v>
+        <v>0.3559</v>
       </c>
       <c r="I311" t="n">
         <v>27.61</v>
@@ -14460,7 +14460,7 @@
         <v>24</v>
       </c>
       <c r="H312" t="n">
-        <v>0.3529</v>
+        <v>0.3531</v>
       </c>
       <c r="I312" t="n">
         <v>26.64</v>
@@ -14505,7 +14505,7 @@
         <v>22</v>
       </c>
       <c r="H313" t="n">
-        <v>0.352</v>
+        <v>0.3521</v>
       </c>
       <c r="I313" t="n">
         <v>22.68</v>
@@ -14550,7 +14550,7 @@
         <v>22</v>
       </c>
       <c r="H314" t="n">
-        <v>0.3477</v>
+        <v>0.3482</v>
       </c>
       <c r="I314" t="n">
         <v>26.22</v>
@@ -14595,7 +14595,7 @@
         <v>23</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3444</v>
+        <v>0.3445</v>
       </c>
       <c r="I315" t="n">
         <v>25.87</v>
@@ -14640,7 +14640,7 @@
         <v>24</v>
       </c>
       <c r="H316" t="n">
-        <v>0.3424</v>
+        <v>0.3425</v>
       </c>
       <c r="I316" t="n">
         <v>24.74</v>
@@ -14685,7 +14685,7 @@
         <v>24</v>
       </c>
       <c r="H317" t="n">
-        <v>0.3407</v>
+        <v>0.3409</v>
       </c>
       <c r="I317" t="n">
         <v>26.38</v>
@@ -14730,7 +14730,7 @@
         <v>23</v>
       </c>
       <c r="H318" t="n">
-        <v>0.3361</v>
+        <v>0.3363</v>
       </c>
       <c r="I318" t="n">
         <v>24.07</v>
@@ -14753,44 +14753,44 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
+        <v>318</v>
+      </c>
+      <c r="C319" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Florida A&amp;M</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>swac</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>130</v>
+      </c>
+      <c r="G319" t="n">
+        <v>24</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="I319" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="J319" t="n">
+        <v>1297.6</v>
+      </c>
+      <c r="K319" t="n">
         <v>312</v>
       </c>
-      <c r="C319" t="n">
-        <v>1477</v>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>East Texas A&amp;M</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>southland</t>
-        </is>
-      </c>
-      <c r="F319" t="n">
-        <v>119</v>
-      </c>
-      <c r="G319" t="n">
-        <v>25</v>
-      </c>
-      <c r="H319" t="n">
-        <v>0.3311</v>
-      </c>
-      <c r="I319" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="J319" t="n">
-        <v>1287.1</v>
-      </c>
-      <c r="K319" t="n">
-        <v>304</v>
-      </c>
       <c r="L319" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="M319" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="320">
@@ -14798,44 +14798,44 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C320" t="n">
-        <v>1197</v>
+        <v>1477</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Florida A&amp;M</t>
+          <t>East Texas A&amp;M</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>swac</t>
+          <t>southland</t>
         </is>
       </c>
       <c r="F320" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="G320" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H320" t="n">
-        <v>0.3308</v>
+        <v>0.3307</v>
       </c>
       <c r="I320" t="n">
-        <v>24.66</v>
+        <v>25.47</v>
       </c>
       <c r="J320" t="n">
-        <v>1297.6</v>
+        <v>1287.1</v>
       </c>
       <c r="K320" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="L320" t="n">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="M320" t="n">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="321">
@@ -14865,7 +14865,7 @@
         <v>22</v>
       </c>
       <c r="H321" t="n">
-        <v>0.3262</v>
+        <v>0.3263</v>
       </c>
       <c r="I321" t="n">
         <v>24.66</v>
@@ -14910,7 +14910,7 @@
         <v>24</v>
       </c>
       <c r="H322" t="n">
-        <v>0.3244</v>
+        <v>0.3245</v>
       </c>
       <c r="I322" t="n">
         <v>23.74</v>
@@ -14955,7 +14955,7 @@
         <v>25</v>
       </c>
       <c r="H323" t="n">
-        <v>0.3232</v>
+        <v>0.3233</v>
       </c>
       <c r="I323" t="n">
         <v>24.61</v>
@@ -15000,7 +15000,7 @@
         <v>23</v>
       </c>
       <c r="H324" t="n">
-        <v>0.3216</v>
+        <v>0.3217</v>
       </c>
       <c r="I324" t="n">
         <v>25.02</v>
@@ -15045,7 +15045,7 @@
         <v>23</v>
       </c>
       <c r="H325" t="n">
-        <v>0.3112</v>
+        <v>0.3114</v>
       </c>
       <c r="I325" t="n">
         <v>22.96</v>
@@ -15068,44 +15068,44 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
+        <v>330</v>
+      </c>
+      <c r="C326" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>IUPUI</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>119</v>
+      </c>
+      <c r="G326" t="n">
+        <v>22</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="I326" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="J326" t="n">
+        <v>1214.7</v>
+      </c>
+      <c r="K326" t="n">
+        <v>320</v>
+      </c>
+      <c r="L326" t="n">
         <v>317</v>
       </c>
-      <c r="C326" t="n">
-        <v>1156</v>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Cleveland St</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>horizon</t>
-        </is>
-      </c>
-      <c r="F326" t="n">
-        <v>121</v>
-      </c>
-      <c r="G326" t="n">
-        <v>23</v>
-      </c>
-      <c r="H326" t="n">
-        <v>0.3071</v>
-      </c>
-      <c r="I326" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="J326" t="n">
-        <v>1358.6</v>
-      </c>
-      <c r="K326" t="n">
-        <v>317</v>
-      </c>
-      <c r="L326" t="n">
-        <v>320</v>
-      </c>
       <c r="M326" t="n">
-        <v>288</v>
+        <v>343</v>
       </c>
     </row>
     <row r="327">
@@ -15113,14 +15113,14 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C327" t="n">
-        <v>1237</v>
+        <v>1156</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>IUPUI</t>
+          <t>Cleveland St</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -15129,28 +15129,28 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G327" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H327" t="n">
-        <v>0.307</v>
+        <v>0.3072</v>
       </c>
       <c r="I327" t="n">
-        <v>22.4</v>
+        <v>24.67</v>
       </c>
       <c r="J327" t="n">
-        <v>1214.7</v>
+        <v>1358.6</v>
       </c>
       <c r="K327" t="n">
+        <v>317</v>
+      </c>
+      <c r="L327" t="n">
         <v>320</v>
       </c>
-      <c r="L327" t="n">
-        <v>317</v>
-      </c>
       <c r="M327" t="n">
-        <v>343</v>
+        <v>288</v>
       </c>
     </row>
     <row r="328">
@@ -15180,7 +15180,7 @@
         <v>22</v>
       </c>
       <c r="H328" t="n">
-        <v>0.2999</v>
+        <v>0.2997</v>
       </c>
       <c r="I328" t="n">
         <v>22.13</v>
@@ -15203,44 +15203,44 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
+        <v>328</v>
+      </c>
+      <c r="C329" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>CS Bakersfield</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>big_west</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>124</v>
+      </c>
+      <c r="G329" t="n">
+        <v>23</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="I329" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="J329" t="n">
+        <v>1310.2</v>
+      </c>
+      <c r="K329" t="n">
+        <v>330</v>
+      </c>
+      <c r="L329" t="n">
         <v>326</v>
       </c>
-      <c r="C329" t="n">
-        <v>1183</v>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>E Illinois</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>ovc</t>
-        </is>
-      </c>
-      <c r="F329" t="n">
-        <v>122</v>
-      </c>
-      <c r="G329" t="n">
-        <v>24</v>
-      </c>
-      <c r="H329" t="n">
-        <v>0.2987</v>
-      </c>
-      <c r="I329" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="J329" t="n">
-        <v>1288.9</v>
-      </c>
-      <c r="K329" t="n">
-        <v>319</v>
-      </c>
-      <c r="L329" t="n">
-        <v>323</v>
-      </c>
       <c r="M329" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="330">
@@ -15248,44 +15248,44 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C330" t="n">
-        <v>1167</v>
+        <v>1183</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>CS Bakersfield</t>
+          <t>E Illinois</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>big_west</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G330" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H330" t="n">
-        <v>0.2984</v>
+        <v>0.2976</v>
       </c>
       <c r="I330" t="n">
-        <v>22.8</v>
+        <v>23.12</v>
       </c>
       <c r="J330" t="n">
-        <v>1310.2</v>
+        <v>1288.9</v>
       </c>
       <c r="K330" t="n">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="L330" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M330" t="n">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="331">
@@ -15315,7 +15315,7 @@
         <v>25</v>
       </c>
       <c r="H331" t="n">
-        <v>0.2874</v>
+        <v>0.2881</v>
       </c>
       <c r="I331" t="n">
         <v>23.4</v>
@@ -15360,7 +15360,7 @@
         <v>22</v>
       </c>
       <c r="H332" t="n">
-        <v>0.2868</v>
+        <v>0.287</v>
       </c>
       <c r="I332" t="n">
         <v>21.03</v>
@@ -15405,7 +15405,7 @@
         <v>21</v>
       </c>
       <c r="H333" t="n">
-        <v>0.2857</v>
+        <v>0.2858</v>
       </c>
       <c r="I333" t="n">
         <v>20.82</v>
@@ -15450,7 +15450,7 @@
         <v>24</v>
       </c>
       <c r="H334" t="n">
-        <v>0.2814</v>
+        <v>0.2819</v>
       </c>
       <c r="I334" t="n">
         <v>20.86</v>
@@ -15495,7 +15495,7 @@
         <v>23</v>
       </c>
       <c r="H335" t="n">
-        <v>0.2794</v>
+        <v>0.2795</v>
       </c>
       <c r="I335" t="n">
         <v>21.09</v>
@@ -15540,7 +15540,7 @@
         <v>24</v>
       </c>
       <c r="H336" t="n">
-        <v>0.2742</v>
+        <v>0.2755</v>
       </c>
       <c r="I336" t="n">
         <v>23.61</v>
@@ -15585,7 +15585,7 @@
         <v>22</v>
       </c>
       <c r="H337" t="n">
-        <v>0.2715</v>
+        <v>0.2718</v>
       </c>
       <c r="I337" t="n">
         <v>19.58</v>
@@ -15630,7 +15630,7 @@
         <v>24</v>
       </c>
       <c r="H338" t="n">
-        <v>0.2687</v>
+        <v>0.2679</v>
       </c>
       <c r="I338" t="n">
         <v>21.65</v>
@@ -15675,7 +15675,7 @@
         <v>22</v>
       </c>
       <c r="H339" t="n">
-        <v>0.2661</v>
+        <v>0.2665</v>
       </c>
       <c r="I339" t="n">
         <v>19.07</v>
@@ -15698,44 +15698,44 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C340" t="n">
-        <v>1427</v>
+        <v>1288</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>UT San Antonio</t>
+          <t>Morgan St</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>aac</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G340" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H340" t="n">
-        <v>0.2659</v>
+        <v>0.2664</v>
       </c>
       <c r="I340" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="J340" t="n">
-        <v>1293.9</v>
+        <v>1273.9</v>
       </c>
       <c r="K340" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L340" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="M340" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
     </row>
     <row r="341">
@@ -15743,44 +15743,44 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C341" t="n">
-        <v>1288</v>
+        <v>1427</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Morgan St</t>
+          <t>UT San Antonio</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>aac</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G341" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H341" t="n">
-        <v>0.2659</v>
+        <v>0.266</v>
       </c>
       <c r="I341" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="J341" t="n">
-        <v>1273.9</v>
+        <v>1293.9</v>
       </c>
       <c r="K341" t="n">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L341" t="n">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="M341" t="n">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="342">
@@ -15810,7 +15810,7 @@
         <v>22</v>
       </c>
       <c r="H342" t="n">
-        <v>0.265</v>
+        <v>0.2652</v>
       </c>
       <c r="I342" t="n">
         <v>20.89</v>
@@ -15855,7 +15855,7 @@
         <v>21</v>
       </c>
       <c r="H343" t="n">
-        <v>0.2629</v>
+        <v>0.2631</v>
       </c>
       <c r="I343" t="n">
         <v>20.56</v>
@@ -15900,7 +15900,7 @@
         <v>24</v>
       </c>
       <c r="H344" t="n">
-        <v>0.2622</v>
+        <v>0.2624</v>
       </c>
       <c r="I344" t="n">
         <v>21.13</v>
@@ -15945,7 +15945,7 @@
         <v>22</v>
       </c>
       <c r="H345" t="n">
-        <v>0.2593</v>
+        <v>0.2595</v>
       </c>
       <c r="I345" t="n">
         <v>19.47</v>
@@ -15968,44 +15968,44 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C346" t="n">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>S Carolina St</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>maac</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F346" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G346" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H346" t="n">
-        <v>0.2488</v>
+        <v>0.2475</v>
       </c>
       <c r="I346" t="n">
-        <v>18.57</v>
+        <v>17.56</v>
       </c>
       <c r="J346" t="n">
-        <v>1284.7</v>
+        <v>1257.4</v>
       </c>
       <c r="K346" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L346" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M346" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="347">
@@ -16013,14 +16013,14 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C347" t="n">
-        <v>1145</v>
+        <v>1351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Canisius</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -16035,22 +16035,22 @@
         <v>23</v>
       </c>
       <c r="H347" t="n">
-        <v>0.2476</v>
+        <v>0.2472</v>
       </c>
       <c r="I347" t="n">
-        <v>19.6</v>
+        <v>18.56</v>
       </c>
       <c r="J347" t="n">
-        <v>1289.6</v>
+        <v>1284.7</v>
       </c>
       <c r="K347" t="n">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="L347" t="n">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="M347" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
     </row>
     <row r="348">
@@ -16058,44 +16058,44 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C348" t="n">
-        <v>1354</v>
+        <v>1145</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>S Carolina St</t>
+          <t>Canisius</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>maac</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G348" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H348" t="n">
-        <v>0.2471</v>
+        <v>0.2462</v>
       </c>
       <c r="I348" t="n">
-        <v>17.56</v>
+        <v>19.59</v>
       </c>
       <c r="J348" t="n">
-        <v>1257.4</v>
+        <v>1289.6</v>
       </c>
       <c r="K348" t="n">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="L348" t="n">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="M348" t="n">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="349">
@@ -16170,10 +16170,10 @@
         <v>21</v>
       </c>
       <c r="H350" t="n">
-        <v>0.2386</v>
+        <v>0.2392</v>
       </c>
       <c r="I350" t="n">
-        <v>18.18</v>
+        <v>18.19</v>
       </c>
       <c r="J350" t="n">
         <v>1324.7</v>
@@ -16238,7 +16238,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C352" t="n">
         <v>1238</v>
@@ -16373,44 +16373,44 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C355" t="n">
-        <v>1175</v>
+        <v>1108</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Delaware St</t>
+          <t>Alcorn St</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>swac</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G355" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H355" t="n">
-        <v>0.223</v>
+        <v>0.2239</v>
       </c>
       <c r="I355" t="n">
-        <v>15.15</v>
+        <v>16.91</v>
       </c>
       <c r="J355" t="n">
-        <v>1254</v>
+        <v>1270.1</v>
       </c>
       <c r="K355" t="n">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="L355" t="n">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="M355" t="n">
-        <v>364</v>
+        <v>345</v>
       </c>
     </row>
     <row r="356">
@@ -16418,44 +16418,44 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C356" t="n">
-        <v>1108</v>
+        <v>1175</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Alcorn St</t>
+          <t>Delaware St</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>swac</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G356" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H356" t="n">
-        <v>0.2224</v>
+        <v>0.2232</v>
       </c>
       <c r="I356" t="n">
-        <v>16.9</v>
+        <v>15.15</v>
       </c>
       <c r="J356" t="n">
-        <v>1270.1</v>
+        <v>1254</v>
       </c>
       <c r="K356" t="n">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="L356" t="n">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="M356" t="n">
-        <v>345</v>
+        <v>364</v>
       </c>
     </row>
     <row r="357">
@@ -16485,7 +16485,7 @@
         <v>21</v>
       </c>
       <c r="H357" t="n">
-        <v>0.2141</v>
+        <v>0.2127</v>
       </c>
       <c r="I357" t="n">
         <v>16.54</v>
@@ -16530,7 +16530,7 @@
         <v>21</v>
       </c>
       <c r="H358" t="n">
-        <v>0.2075</v>
+        <v>0.2076</v>
       </c>
       <c r="I358" t="n">
         <v>16</v>
@@ -16643,44 +16643,44 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C361" t="n">
-        <v>1164</v>
+        <v>1442</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Coppin St</t>
+          <t>W Illinois</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>meac</t>
+          <t>ovc</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G361" t="n">
         <v>21</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1718</v>
+        <v>0.1731</v>
       </c>
       <c r="I361" t="n">
-        <v>12.53</v>
+        <v>13.47</v>
       </c>
       <c r="J361" t="n">
-        <v>1185.3</v>
+        <v>1232.1</v>
       </c>
       <c r="K361" t="n">
+        <v>364</v>
+      </c>
+      <c r="L361" t="n">
+        <v>364</v>
+      </c>
+      <c r="M361" t="n">
         <v>363</v>
-      </c>
-      <c r="L361" t="n">
-        <v>363</v>
-      </c>
-      <c r="M361" t="n">
-        <v>362</v>
       </c>
     </row>
     <row r="362">
@@ -16688,23 +16688,23 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C362" t="n">
-        <v>1442</v>
+        <v>1164</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>W Illinois</t>
+          <t>Coppin St</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>ovc</t>
+          <t>meac</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G362" t="n">
         <v>21</v>
@@ -16713,19 +16713,19 @@
         <v>0.1718</v>
       </c>
       <c r="I362" t="n">
-        <v>13.47</v>
+        <v>12.53</v>
       </c>
       <c r="J362" t="n">
-        <v>1232.1</v>
+        <v>1185.3</v>
       </c>
       <c r="K362" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L362" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M362" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="363">
@@ -16890,7 +16890,7 @@
         <v>24</v>
       </c>
       <c r="H366" t="n">
-        <v>0.1226</v>
+        <v>0.1239</v>
       </c>
       <c r="I366" t="n">
         <v>9.539999999999999</v>
